--- a/docs/downloads/2026-10-01/bursa-report-2026-10-01.xlsx
+++ b/docs/downloads/2026-10-01/bursa-report-2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-01" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-01'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-01'!$A$1:$M$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,13 +38,13 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
+      <color rgb="00D03B3B"/>
+    </font>
+    <font>
       <color rgb="00898781"/>
     </font>
-    <font>
-      <color rgb="00D03B3B"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -54,11 +54,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F3E4E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EEEAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,31 +69,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -550,57 +536,49 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>7192</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>GIIB</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0.008399999999999999</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>34237000</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>73.06999999999999</v>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>🎯 SAR 转多</t>
-        </is>
-      </c>
-      <c r="M2" s="8" t="inlineStr">
-        <is>
-          <t>SAR转多，但RSI达73.07已超买，现价0.6高于50日均线0.495约21%，短线偏热。</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0138</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ZETRIX</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>42381800</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H2" t="n">
+        <v>23.37</v>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -610,42 +588,33 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E3" s="10" t="n">
+          <t>0475.KL</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="E3" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="11" t="n">
-        <v>23449100</v>
-      </c>
-      <c r="G3" s="12" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H3" t="n">
-        <v>78.19</v>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>0.332</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>0.197</v>
-      </c>
+      <c r="F3" s="4" t="n">
+        <v>39977100</v>
+      </c>
+      <c r="G3" s="5" t="n"/>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="14" t="inlineStr"/>
+      <c r="M3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -655,42 +624,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ASTRO</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>13524400</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>11.21</v>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>32900100</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1.13</v>
       </c>
       <c r="H4" t="n">
-        <v>57.27</v>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="K4" s="9" t="n">
-        <v>0.06</v>
+        <v>72.5</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.234</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="14" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -700,42 +669,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>5834600</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>0.2</v>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>23120100</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.99</v>
       </c>
       <c r="H5" t="n">
-        <v>71.20999999999999</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="K5" s="9" t="n">
-        <v>0.234</v>
+        <v>62.49</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.472</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="14" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -745,42 +714,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DFX</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>0.2222</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>4340100</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>5.48</v>
+          <t>JAKS</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>18842500</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.36</v>
       </c>
       <c r="H6" t="n">
-        <v>69.81</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>0.08699999999999999</v>
+        <v>83.31999999999999</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.123</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="14" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -790,42 +759,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>-0.0449</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>2020700</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>0.22</v>
+          <t>ASTRO</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>17624600</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>14.61</v>
       </c>
       <c r="H7" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>0.447</v>
-      </c>
-      <c r="K7" s="9" t="n">
-        <v>0.414</v>
+        <v>51.74</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.06</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="14" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -835,42 +804,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0145</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JAKS</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>0.205</v>
+          <t>TFP</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.03</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>1428000</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>0.03</v>
+        <v>-0.4545</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>13189400</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>3.4</v>
       </c>
       <c r="H8" t="n">
-        <v>82.38</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K8" s="9" t="n">
-        <v>0.123</v>
+        <v>23.73</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.07099999999999999</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="14" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -880,42 +849,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>0.0039</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>686200</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H9" t="n">
-        <v>76.45999999999999</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>4.844</v>
-      </c>
-      <c r="K9" s="9" t="n">
-        <v>4.566</v>
-      </c>
+          <t>Evocom Berhad</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>13059000</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="14" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -925,45 +887,2651 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>0131</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DFX</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.2222</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>12897000</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="H10" t="n">
+        <v>69.81</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0345</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SUNLOGY</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>10287800</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H11" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>7526400</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H12" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>4.848</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>4.567</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7215</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>5081000</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H13" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>4370400</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H14" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0111</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>3967000</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H15" t="n">
+        <v>62.21</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>-0.0698</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>3103700</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H16" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>1.332</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>3054700</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5205</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SENDAI</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>3041800</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H18" t="n">
+        <v>64.17</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>7155</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SKPRES</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>-0.0141</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>2822600</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H19" t="n">
+        <v>62.85</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.005699999999999999</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>2750000</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H20" t="n">
+        <v>56.03</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>1.744</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>1.562</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0353</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>WESTRVR</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>2572200</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>77.72</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0367</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ENPRO</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>2196200</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H22" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>-0.0135</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>1854700</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H23" t="n">
+        <v>30.31</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.0449</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>1828600</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H24" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>3.609</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>1655700</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H25" t="n">
+        <v>68.34999999999999</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>-0.0109</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>1609700</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H26" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1551000</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0469</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>GTA</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>1472300</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H28" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>1466900</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H29" t="n">
+        <v>46.78</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1448700</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H30" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0193</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>KINERGY</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1365400</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H31" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>UEMS</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>1280300</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1253600</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H33" t="n">
+        <v>51.53</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>2.201</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0181</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AEMULUS</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1214600</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H34" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>5352</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>MTTSL</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>-0.018</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>515900</v>
-      </c>
-      <c r="G10" s="12" t="n">
+      <c r="D35" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>-0.009000000000000001</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>1201900</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H35" t="n">
+        <v>40.81</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>L&amp;G</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H36" t="n">
+        <v>60.58</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1194700</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H37" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>6.686</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>6.556</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1180700</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H38" t="n">
+        <v>37.88</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>1168700</v>
+      </c>
+      <c r="G39" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H10" t="n">
-        <v>39.73</v>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="H39" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J10" s="9" t="n">
-        <v>1.162</v>
-      </c>
-      <c r="K10" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" s="14" t="inlineStr"/>
+      <c r="J39" s="2" t="n">
+        <v>4.807</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>4.938</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>1083900</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H40" t="n">
+        <v>37.78</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>10.128</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>-0.0263</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>1066200</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>1053400</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H42" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>1041200</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H43" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>1015900</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>56.16</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0396</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ADNEX</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1002400</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H45" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>960000</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H46" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>951100</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H47" t="n">
+        <v>44.18</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>1.356</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>1.298</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>934000</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H48" t="n">
+        <v>61.18</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>920000</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H49" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>908800</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H50" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>903200</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H51" t="n">
+        <v>62.53</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>2.912</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>873400</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H52" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>7.852</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>8.214</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>862000</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H53" t="n">
+        <v>47.24</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>848500</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H54" t="n">
+        <v>81.98999999999999</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>2.537</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>818700</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H55" t="n">
+        <v>62.68</v>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>5.697</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>5.192</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>802200</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H56" t="n">
+        <v>65.11</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>773100</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H57" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>726700</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H58" t="n">
+        <v>86.44</v>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>1.126</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>726000</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H59" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>678500</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H60" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>7.747</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>647100</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H61" t="n">
+        <v>51.87</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>2.566</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>2.546</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>626300</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>64.37</v>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>617500</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H63" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>575400</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H64" t="n">
+        <v>64.84</v>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>2.801</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>2.659</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>526800</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H65" t="n">
+        <v>40.29</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>5.666</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>5.745</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>522000</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H66" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>2.982</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>3.037</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1287</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>EXSIMHB</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>505300</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H67" t="n">
+        <v>64.61</v>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H68" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-01/bursa-report-2026-10-01.xlsx
+++ b/docs/downloads/2026-10-01/bursa-report-2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-01" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-01'!$A$1:$M$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-01'!$A$1:$M$126</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -96,8 +96,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:M126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.51</v>
+        <v>0.505</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1093400</v>
+        <v>1356100</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.76</v>
+        <v>2.18</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>64.61</v>
+        <v>61.7</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多，现价0.51高于50日均线0.468，RSI 64.61接近超买区，信号偏积极但需留意短线过热。</t>
+          <t>SAR转多，现价0.505高于50日均线0.468，RSI 61.7偏强但未超买，信号可靠性中等偏上。</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>0.0313</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>69097600</v>
+        <v>84627800</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="H3" t="n">
         <v>21.74</v>
@@ -655,39 +655,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>-0.0244</v>
+        <v>0.285</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>0.0179</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>55546700</v>
+        <v>77209300</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>1.05</v>
+        <v>2.66</v>
       </c>
       <c r="H4" t="n">
-        <v>78</v>
-      </c>
-      <c r="I4" s="16" t="inlineStr">
+        <v>72.5</v>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.16</v>
+        <v>0.241</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.123</v>
+        <v>0.234</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -700,31 +700,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0475.KL</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E5" s="17" t="n">
-        <v>0</v>
+        <v>0.2</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>50407200</v>
-      </c>
-      <c r="G5" s="12" t="n"/>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="n"/>
-      <c r="K5" s="9" t="n"/>
+        <v>72214600</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H5" t="n">
+        <v>78</v>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0.123</v>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
     </row>
@@ -736,40 +745,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>0475.KL</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>0.0357</v>
+        <v>0.23</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>41307200</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="H6" t="n">
-        <v>73.68000000000001</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>0.242</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>0.234</v>
-      </c>
+        <v>53847700</v>
+      </c>
+      <c r="G6" s="12" t="n"/>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="9" t="n"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
     </row>
@@ -796,15 +796,15 @@
         <v>0.0412</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>26059000</v>
+        <v>31634400</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="H7" t="n">
         <v>62.49</v>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -837,14 +837,14 @@
       <c r="D8" s="9" t="n">
         <v>0.04</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="16" t="n">
         <v>-0.2727</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>18846300</v>
+        <v>19736600</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>4.85</v>
+        <v>5.08</v>
       </c>
       <c r="H8" t="n">
         <v>28.04</v>
@@ -886,15 +886,15 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>18027800</v>
+        <v>18047800</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>14.95</v>
+        <v>14.96</v>
       </c>
       <c r="H9" t="n">
         <v>51.74</v>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I9" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -916,33 +916,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.12</v>
+        <v>5.23</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0.0435</v>
+        <v>0.0097</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>15653800</v>
+        <v>18038900</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
+        <v>0.79</v>
+      </c>
+      <c r="H10" t="n">
+        <v>77.26000000000001</v>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>4.847</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>4.567</v>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
     </row>
@@ -954,40 +961,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5.2</v>
+        <v>0.12</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.0039</v>
+        <v>0.0435</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>15355100</v>
+        <v>16074700</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="H11" t="n">
-        <v>76.45999999999999</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="n">
-        <v>4.844</v>
-      </c>
-      <c r="K11" s="9" t="n">
-        <v>4.566</v>
-      </c>
+        <v>0.51</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="9" t="n"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
     </row>
@@ -1008,19 +1008,19 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.465</v>
+        <v>0.46</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.0449</v>
+        <v>0.0337</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>14278800</v>
+        <v>15945800</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="H12" t="n">
-        <v>55.68</v>
+        <v>54.57</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0.415</v>
@@ -1059,15 +1059,15 @@
         <v>0.2222</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>13643200</v>
+        <v>14389100</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>17.21</v>
+        <v>18.15</v>
       </c>
       <c r="H13" t="n">
         <v>69.81</v>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="I13" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1089,39 +1089,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0.0423</v>
+        <v>0.55</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>-0.0265</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>9793200</v>
+        <v>11832000</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1.32</v>
+        <v>0.78</v>
       </c>
       <c r="H14" t="n">
-        <v>71.03</v>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
+        <v>56.14</v>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.335</v>
+        <v>0.534</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.313</v>
+        <v>0.489</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1134,39 +1134,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>-0.0128</v>
+        <v>0.365</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0.0282</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>6131000</v>
+        <v>11395100</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.13</v>
+        <v>1.53</v>
       </c>
       <c r="H15" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
+        <v>69.59</v>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.337</v>
+        <v>0.334</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.203</v>
+        <v>0.313</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1179,39 +1179,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>-0.0625</v>
+        <v>0.6</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>5829200</v>
+        <v>10608500</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.15</v>
+        <v>0.41</v>
       </c>
       <c r="H16" t="n">
-        <v>47.73</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
+        <v>73.06999999999999</v>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.157</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.147</v>
+        <v>0.495</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1224,39 +1224,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.285</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>5671900</v>
+        <v>8323200</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.37</v>
+        <v>1.18</v>
       </c>
       <c r="H17" t="n">
-        <v>58.78</v>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.15</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.535</v>
+        <v>0.295</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.489</v>
+        <v>0.31</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1269,39 +1269,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>-0.0294</v>
+        <v>0.385</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>-0.0128</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>5115700</v>
+        <v>7136500</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1.6</v>
+        <v>0.16</v>
       </c>
       <c r="H18" t="n">
-        <v>62.21</v>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
+        <v>75.7</v>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.152</v>
+        <v>0.337</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.141</v>
+        <v>0.203</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0.0083</v>
+        <v>1.75</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>5114900</v>
+        <v>6388700</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="H19" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.3</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.742</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.496</v>
+        <v>1.562</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1359,39 +1359,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>-0.0114</v>
+        <v>0.15</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>-0.0625</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>3938100</v>
+        <v>6077600</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="H20" t="n">
-        <v>53.37</v>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
+        <v>47.73</v>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1.742</v>
+        <v>0.157</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1.561</v>
+        <v>0.147</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1404,39 +1404,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SENDAI</t>
+          <t>HUBLINE</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0.0179</v>
+        <v>0.03</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>3860800</v>
+        <v>5712800</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>2.09</v>
+        <v>4.24</v>
       </c>
       <c r="H21" t="n">
-        <v>64.17</v>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.42</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.263</v>
+        <v>0.032</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.268</v>
+        <v>0.032</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1449,39 +1449,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>-0.062</v>
+        <v>0.77</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>3703900</v>
+        <v>5295200</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>2.49</v>
+        <v>0.4</v>
       </c>
       <c r="H22" t="n">
-        <v>38.75</v>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.12</v>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1.275</v>
+        <v>0.773</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>1.332</v>
+        <v>0.774</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1494,39 +1494,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0.0365</v>
+        <v>0.165</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>-0.0294</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>3639500</v>
+        <v>5135700</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.29</v>
+        <v>1.6</v>
       </c>
       <c r="H23" t="n">
-        <v>56.55</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.21</v>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>3.607</v>
+        <v>0.152</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>2.501</v>
+        <v>0.141</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1539,39 +1539,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0.0252</v>
+        <v>0.295</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>3592000</v>
+        <v>5079000</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.48</v>
       </c>
       <c r="H24" t="n">
-        <v>68.34999999999999</v>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.25</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1.128</v>
+        <v>0.295</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1.029</v>
+        <v>0.296</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1584,39 +1584,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>SENDAI</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.45</v>
+        <v>0.285</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.0179</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>3460600</v>
+        <v>4774500</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1.49</v>
+        <v>2.59</v>
       </c>
       <c r="H25" t="n">
-        <v>76.95</v>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
+        <v>64.17</v>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.388</v>
+        <v>0.263</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.35</v>
+        <v>0.268</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1629,39 +1629,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.61</v>
+        <v>1.2</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>0.0167</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>3365200</v>
+        <v>4752600</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.33</v>
+        <v>1.25</v>
       </c>
       <c r="H26" t="n">
-        <v>51.26</v>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
+        <v>66.34</v>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.607</v>
+        <v>1.126</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.607</v>
+        <v>1.029</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1674,39 +1674,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.19</v>
+        <v>0.615</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>0.0857</v>
+        <v>0.025</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>3130300</v>
+        <v>4284600</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.62</v>
+        <v>0.41</v>
       </c>
       <c r="H27" t="n">
-        <v>67.62</v>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
+        <v>53.53</v>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.165</v>
+        <v>0.608</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.165</v>
+        <v>0.607</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1719,39 +1719,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0.0141</v>
+        <v>0.52</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>-0.0095</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>2872000</v>
+        <v>4135200</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.38</v>
+        <v>0.11</v>
       </c>
       <c r="H28" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.26</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.335</v>
+        <v>0.604</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.315</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1764,28 +1764,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>-0.001</v>
+        <v>2.07</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>2780900</v>
+        <v>4124300</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="H29" t="n">
-        <v>36.39</v>
+        <v>44.66</v>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>10.126</v>
+        <v>2.113</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>10.28</v>
+        <v>2.069</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1809,28 +1809,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E30" s="17" t="n">
-        <v>0</v>
+        <v>3.68</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0.0337</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>2623500</v>
+        <v>4074800</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1.28</v>
+        <v>0.33</v>
       </c>
       <c r="H30" t="n">
-        <v>49.25</v>
+        <v>56.39</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.295</v>
+        <v>3.606</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.296</v>
+        <v>2.501</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1854,39 +1854,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E31" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2598600</v>
+        <v>3929200</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="H31" t="n">
-        <v>48.12</v>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.2</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.773</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.774</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1899,39 +1899,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.765</v>
+        <v>0.19</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.0066</v>
+        <v>0.0857</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2549200</v>
+        <v>3924200</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.39</v>
+        <v>0.77</v>
       </c>
       <c r="H32" t="n">
-        <v>46.78</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.62</v>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.771</v>
+        <v>0.165</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.771</v>
+        <v>0.165</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>0.0063</v>
+        <v>0.365</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>2471300</v>
+        <v>3868200</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.22</v>
+        <v>0.62</v>
       </c>
       <c r="H33" t="n">
-        <v>62.36</v>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.24</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.733</v>
+        <v>0.367</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.694</v>
+        <v>0.367</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1989,39 +1989,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.26</v>
+        <v>0.455</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>0.0196</v>
+        <v>0.0225</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>2418300</v>
+        <v>3829200</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.29</v>
+        <v>1.64</v>
       </c>
       <c r="H34" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.72</v>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.264</v>
+        <v>0.389</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.224</v>
+        <v>0.35</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2034,28 +2034,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>-0.0135</v>
+        <v>1.21</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>-0.062</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>2109200</v>
+        <v>3794800</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.48</v>
+        <v>2.55</v>
       </c>
       <c r="H35" t="n">
-        <v>30.31</v>
+        <v>38.75</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.782</v>
+        <v>1.275</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.838</v>
+        <v>1.332</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2079,39 +2079,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>0</v>
+        <v>9.970000000000001</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>-0.002</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>2091600</v>
+        <v>3742100</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="H36" t="n">
-        <v>66.25</v>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.89</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.28</v>
+        <v>10.125</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.272</v>
+        <v>10.28</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2124,39 +2124,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.425</v>
+        <v>0.355</v>
       </c>
       <c r="E37" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>2065000</v>
+        <v>3301600</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="H37" t="n">
-        <v>57.09</v>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
+        <v>62.52</v>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.406</v>
+        <v>0.335</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.404</v>
+        <v>0.315</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2169,28 +2169,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>0</v>
+        <v>0.73</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>2052700</v>
+        <v>3243000</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.32</v>
+        <v>0.74</v>
       </c>
       <c r="H38" t="n">
-        <v>30.06</v>
+        <v>30.31</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.55</v>
+        <v>0.782</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.584</v>
+        <v>0.838</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2214,39 +2214,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0.0156</v>
+        <v>0.76</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>2042800</v>
+        <v>3159200</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.21</v>
+        <v>0.49</v>
       </c>
       <c r="H39" t="n">
-        <v>56.16</v>
-      </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.51</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.636</v>
+        <v>0.77</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.583</v>
+        <v>0.771</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2259,39 +2259,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.28</v>
+        <v>0.79</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>1992300</v>
+        <v>2919400</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="H40" t="n">
-        <v>50.77</v>
-      </c>
-      <c r="I40" s="16" t="inlineStr">
+        <v>61.75</v>
+      </c>
+      <c r="I40" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>2.281</v>
+        <v>0.733</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>2.201</v>
+        <v>0.694</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2313,19 +2313,19 @@
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>-0.018</v>
+        <v>1.08</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>-0.027</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1979600</v>
+        <v>2902700</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.29</v>
+        <v>0.42</v>
       </c>
       <c r="H41" t="n">
-        <v>39.73</v>
+        <v>38.71</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>1.162</v>
+        <v>1.161</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>1.15</v>
@@ -2349,39 +2349,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>0.0198</v>
+        <v>4.65</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>-0.0106</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1788700</v>
+        <v>2695900</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.65</v>
+        <v>0.15</v>
       </c>
       <c r="H42" t="n">
-        <v>76.95999999999999</v>
-      </c>
-      <c r="I42" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.01</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.426</v>
+        <v>4.804</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.415</v>
+        <v>4.937</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2394,39 +2394,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.365</v>
+        <v>2.28</v>
       </c>
       <c r="E43" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1784200</v>
+        <v>2652400</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="H43" t="n">
-        <v>48.24</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.77</v>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.367</v>
+        <v>2.281</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.367</v>
+        <v>2.201</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2439,39 +2439,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>0</v>
+        <v>1.16</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>-0.0645</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1777500</v>
+        <v>2587600</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="H44" t="n">
-        <v>45.42</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.75</v>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.522</v>
+        <v>0.969</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.532</v>
+        <v>0.766</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2484,39 +2484,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>-0.0054</v>
+        <v>0.865</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>1753400</v>
+        <v>2518700</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.35</v>
+        <v>0.13</v>
       </c>
       <c r="H45" t="n">
-        <v>61.21</v>
-      </c>
-      <c r="I45" s="16" t="inlineStr">
+        <v>46.8</v>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.894</v>
+        <v>0.868</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.854</v>
+        <v>0.87</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2529,28 +2529,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>-0.0062</v>
+        <v>0.255</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>1747900</v>
+        <v>2441500</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.12</v>
+        <v>0.29</v>
       </c>
       <c r="H46" t="n">
-        <v>47.32</v>
+        <v>50.12</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.264</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.224</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2574,39 +2574,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="E47" s="15" t="n">
-        <v>-0.0064</v>
+        <v>3.07</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1723800</v>
+        <v>2432500</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.1</v>
+        <v>0.67</v>
       </c>
       <c r="H47" t="n">
-        <v>29.36</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.23</v>
+      </c>
+      <c r="I47" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>4.806</v>
+        <v>2.906</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>4.937</v>
+        <v>2.719</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2619,39 +2619,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>2.76</v>
+        <v>0.645</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1662400</v>
+        <v>2428800</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
       <c r="H48" t="n">
-        <v>81.98999999999999</v>
-      </c>
-      <c r="I48" s="16" t="inlineStr">
+        <v>55.14</v>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>2.537</v>
+        <v>0.636</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>2.18</v>
+        <v>0.582</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2664,39 +2664,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>-0.0077</v>
+        <v>0.425</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1632700</v>
+        <v>2388100</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.13</v>
+        <v>0.42</v>
       </c>
       <c r="H49" t="n">
-        <v>43.19</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.09</v>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>1.355</v>
+        <v>0.406</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>1.298</v>
+        <v>0.404</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2709,36 +2709,40 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v>-0.0185</v>
+        <v>0.34</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1623900</v>
+        <v>2348700</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.09</v>
+        <v>1.77</v>
       </c>
       <c r="H50" t="n">
-        <v>15.91</v>
+        <v>31.63</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J50" s="9" t="n"/>
-      <c r="K50" s="9" t="n"/>
+      <c r="J50" s="9" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>0.391</v>
+      </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
     </row>
@@ -2750,39 +2754,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>0.0132</v>
+        <v>0.515</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1614800</v>
+        <v>2188500</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.45</v>
+        <v>0.34</v>
       </c>
       <c r="H51" t="n">
-        <v>60.63</v>
-      </c>
-      <c r="I51" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.06</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>2.907</v>
+        <v>0.55</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>2.719</v>
+        <v>0.584</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2804,19 +2808,19 @@
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.54</v>
+        <v>0.535</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>0.0189</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1581800</v>
+        <v>2158000</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="H52" t="n">
-        <v>60.11</v>
+        <v>58.93</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2840,33 +2844,40 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E53" s="17" t="n">
-        <v>0</v>
+        <v>0.3</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1559000</v>
+        <v>2152600</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I53" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J53" s="9" t="n"/>
-      <c r="K53" s="9" t="n"/>
+        <v>0.33</v>
+      </c>
+      <c r="H53" t="n">
+        <v>68.88</v>
+      </c>
+      <c r="I53" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>0.272</v>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
     </row>
@@ -2878,39 +2889,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>6.96</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>-0.0156</v>
+        <v>0.22</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1548500</v>
+        <v>2087200</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="H54" t="n">
-        <v>58.37</v>
-      </c>
-      <c r="I54" s="16" t="inlineStr">
+        <v>54.54</v>
+      </c>
+      <c r="I54" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>6.673</v>
+        <v>0.215</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>6.554</v>
+        <v>0.213</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2923,28 +2934,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0.0294</v>
+        <v>1.29</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1483200</v>
+        <v>2028800</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>1.12</v>
+        <v>0.16</v>
       </c>
       <c r="H55" t="n">
-        <v>40.8</v>
+        <v>43.19</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2952,10 +2963,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.358</v>
+        <v>1.355</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.391</v>
+        <v>1.298</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2968,39 +2979,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.65</v>
+        <v>0.51</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1459100</v>
+        <v>1948600</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.44</v>
+        <v>0.71</v>
       </c>
       <c r="H56" t="n">
-        <v>61.18</v>
-      </c>
-      <c r="I56" s="16" t="inlineStr">
+        <v>76.33</v>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.608</v>
+        <v>0.425</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.61</v>
+        <v>0.415</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3013,39 +3024,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E57" s="15" t="n">
-        <v>-0.0395</v>
+        <v>0.29</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1458400</v>
+        <v>1919300</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="H57" t="n">
-        <v>43.92</v>
-      </c>
-      <c r="I57" s="16" t="inlineStr">
+        <v>52.59</v>
+      </c>
+      <c r="I57" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.375</v>
+        <v>0.286</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.371</v>
+        <v>0.277</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3058,40 +3069,33 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0.018</v>
+        <v>0.475</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1432500</v>
+        <v>1861900</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H58" t="n">
-        <v>69.34999999999999</v>
-      </c>
-      <c r="I58" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J58" s="9" t="n">
-        <v>0.498</v>
-      </c>
-      <c r="K58" s="9" t="n">
-        <v>0.415</v>
-      </c>
+        <v>0.11</v>
+      </c>
+      <c r="I58" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="n"/>
+      <c r="K58" s="9" t="n"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
     </row>
@@ -3103,39 +3107,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0396</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ADNEX</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>0.0118</v>
+        <v>0.44</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1431200</v>
+        <v>1857800</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>3.3</v>
+        <v>8.73</v>
       </c>
       <c r="H59" t="n">
-        <v>56.98</v>
-      </c>
-      <c r="I59" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.18</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.418</v>
+        <v>0.44</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.415</v>
+        <v>0.434</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3148,39 +3152,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>-0.0125</v>
+        <v>0.92</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1376100</v>
+        <v>1819000</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.12</v>
+        <v>0.36</v>
       </c>
       <c r="H60" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.45</v>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.407</v>
+        <v>0.895</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.411</v>
+        <v>0.854</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3193,39 +3197,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.865</v>
+        <v>0.51</v>
       </c>
       <c r="E61" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1375900</v>
+        <v>1804100</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="H61" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.42</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.868</v>
+        <v>0.522</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.87</v>
+        <v>0.532</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3238,39 +3242,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E62" s="15" t="n">
-        <v>-0.009899999999999999</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1279600</v>
+        <v>1795500</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="H62" t="n">
-        <v>56.72</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.7</v>
+      </c>
+      <c r="I62" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.196</v>
+        <v>0.497</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.18</v>
+        <v>0.415</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3283,39 +3287,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="E63" s="15" t="n">
-        <v>-0.0027</v>
+        <v>6.9</v>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>-0.024</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1277000</v>
+        <v>1775500</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.12</v>
+        <v>0.52</v>
       </c>
       <c r="H63" t="n">
-        <v>25.34</v>
-      </c>
-      <c r="I63" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.73</v>
+      </c>
+      <c r="I63" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>7.854</v>
+        <v>6.668</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>8.214</v>
+        <v>6.552</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3328,40 +3332,36 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0.0068</v>
+        <v>0.265</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1206800</v>
+        <v>1722300</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="H64" t="n">
-        <v>63.06</v>
-      </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J64" s="9" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="K64" s="9" t="n">
-        <v>0.624</v>
-      </c>
+        <v>15.91</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="n"/>
+      <c r="K64" s="9" t="n"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
     </row>
@@ -3373,39 +3373,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>1.1</v>
+        <v>0.65</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>0.028</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1181600</v>
+        <v>1713300</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="H65" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
+        <v>61.18</v>
+      </c>
+      <c r="I65" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>1.003</v>
+        <v>0.608</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.831</v>
+        <v>0.61</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3418,39 +3418,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E66" s="15" t="n">
-        <v>-0.0192</v>
+        <v>0.245</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1180900</v>
+        <v>1699100</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>1.39</v>
+        <v>0.06</v>
       </c>
       <c r="H66" t="n">
-        <v>37.88</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.55</v>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.26</v>
+        <v>0.268</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.265</v>
+        <v>0.32</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3463,39 +3463,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>0</v>
+        <v>2.76</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>0.0036</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1150400</v>
+        <v>1662400</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="H67" t="n">
-        <v>27.67</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.98999999999999</v>
+      </c>
+      <c r="I67" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.239</v>
+        <v>2.537</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.242</v>
+        <v>2.18</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3508,39 +3508,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E68" s="15" t="n">
-        <v>-0.0172</v>
+        <v>7.46</v>
+      </c>
+      <c r="E68" s="16" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1144100</v>
+        <v>1612400</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="H68" t="n">
-        <v>35.15</v>
-      </c>
-      <c r="I68" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.83</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.295</v>
+        <v>7.852</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.31</v>
+        <v>8.214</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3553,39 +3553,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>0.0216</v>
+        <v>0.305</v>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1109200</v>
+        <v>1612100</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.37</v>
+        <v>0.08</v>
       </c>
       <c r="H69" t="n">
-        <v>86.44</v>
-      </c>
-      <c r="I69" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.62</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>1.126</v>
+        <v>0.303</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.93</v>
+        <v>0.292</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3598,39 +3598,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E70" s="15" t="n">
-        <v>-0.0364</v>
+        <v>0.79</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1105600</v>
+        <v>1605600</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.35</v>
+        <v>0.26</v>
       </c>
       <c r="H70" t="n">
-        <v>74.76000000000001</v>
-      </c>
-      <c r="I70" s="16" t="inlineStr">
+        <v>64.37</v>
+      </c>
+      <c r="I70" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>2.406</v>
+        <v>0.77</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>1.862</v>
+        <v>0.756</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3643,39 +3643,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>0.015</v>
+        <v>0.37</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1101100</v>
+        <v>1587700</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>0.15</v>
       </c>
       <c r="H71" t="n">
-        <v>49.33</v>
-      </c>
-      <c r="I71" s="16" t="inlineStr">
+        <v>46.98</v>
+      </c>
+      <c r="I71" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.68</v>
+        <v>0.375</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.666</v>
+        <v>0.371</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3688,39 +3688,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>-0.0274</v>
+        <v>5.83</v>
+      </c>
+      <c r="E72" s="16" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1097900</v>
+        <v>1574900</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.79</v>
+        <v>0.11</v>
       </c>
       <c r="H72" t="n">
-        <v>35</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.28</v>
+      </c>
+      <c r="I72" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.382</v>
+        <v>5.692</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.391</v>
+        <v>5.191</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3733,39 +3733,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0398</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GDGROUP</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0.0132</v>
+        <v>0.74</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1060000</v>
+        <v>1559400</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>1.3</v>
+        <v>0.03</v>
       </c>
       <c r="H73" t="n">
-        <v>59.67</v>
-      </c>
-      <c r="I73" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.24</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.378</v>
+        <v>0.737</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.38</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0396</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>ADNEX</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.58</v>
+        <v>0.43</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>0.0265</v>
+        <v>0.0118</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1057300</v>
+        <v>1477200</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.36</v>
+        <v>3.41</v>
       </c>
       <c r="H74" t="n">
-        <v>53.14</v>
-      </c>
-      <c r="I74" s="16" t="inlineStr">
+        <v>56.98</v>
+      </c>
+      <c r="I74" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.57</v>
+        <v>0.418</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.575</v>
+        <v>0.415</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3823,33 +3823,40 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>0.0357</v>
+        <v>2.92</v>
+      </c>
+      <c r="E75" s="16" t="n">
+        <v>-0.0331</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1053800</v>
+        <v>1428400</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I75" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J75" s="9" t="n"/>
-      <c r="K75" s="9" t="n"/>
+        <v>0.45</v>
+      </c>
+      <c r="H75" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="I75" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="K75" s="9" t="n">
+        <v>1.862</v>
+      </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
     </row>
@@ -3861,39 +3868,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="E76" s="15" t="n">
-        <v>-0.0017</v>
+        <v>0.255</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>-0.0377</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1034600</v>
+        <v>1417900</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="H76" t="n">
-        <v>61.82</v>
-      </c>
-      <c r="I76" s="16" t="inlineStr">
+        <v>64.37</v>
+      </c>
+      <c r="I76" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>5.695</v>
+        <v>0.234</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>5.192</v>
+        <v>0.211</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3906,28 +3913,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.525</v>
+        <v>0.4</v>
       </c>
       <c r="E77" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1016200</v>
+        <v>1394200</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="H77" t="n">
-        <v>28.71</v>
+        <v>42.45</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3935,10 +3942,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.604</v>
+        <v>0.407</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.411</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3951,39 +3958,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.79</v>
+        <v>0.735</v>
       </c>
       <c r="E78" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1012500</v>
+        <v>1382000</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="H78" t="n">
-        <v>64.37</v>
-      </c>
-      <c r="I78" s="16" t="inlineStr">
+        <v>62.32</v>
+      </c>
+      <c r="I78" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.77</v>
+        <v>0.696</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.756</v>
+        <v>0.624</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -3996,39 +4003,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>0</v>
+        <v>1.4</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>936200</v>
+        <v>1373600</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.24</v>
+        <v>0.46</v>
       </c>
       <c r="H79" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>85.89</v>
+      </c>
+      <c r="I79" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.582</v>
+        <v>1.124</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.586</v>
+        <v>0.929</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4041,39 +4048,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="E80" s="15" t="n">
-        <v>-0.0013</v>
+        <v>0.2</v>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>933800</v>
+        <v>1361900</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H80" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="I80" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.72</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>7.8</v>
+        <v>0.196</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>7.747</v>
+        <v>0.18</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4086,39 +4093,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>1.1</v>
+        <v>0.675</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>0.0092</v>
+        <v>0.015</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>932800</v>
+        <v>1347000</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="H81" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="I81" s="16" t="inlineStr">
+        <v>49.33</v>
+      </c>
+      <c r="I81" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>1.027</v>
+        <v>0.68</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.868</v>
+        <v>0.666</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4131,39 +4138,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="E82" s="15" t="n">
-        <v>-0.0023</v>
+        <v>1.1</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>0.028</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>930900</v>
+        <v>1341600</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="H82" t="n">
-        <v>76.61</v>
-      </c>
-      <c r="I82" s="16" t="inlineStr">
+        <v>74.3</v>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>3.765</v>
+        <v>1.003</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>3.305</v>
+        <v>0.831</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4176,39 +4183,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E83" s="15" t="n">
-        <v>-0.0403</v>
+        <v>7.77</v>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>-0.0026</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>877500</v>
+        <v>1317300</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="H83" t="n">
-        <v>77.95</v>
-      </c>
-      <c r="I83" s="16" t="inlineStr">
+        <v>49.28</v>
+      </c>
+      <c r="I83" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.971</v>
+        <v>7.799</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.767</v>
+        <v>7.747</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4221,39 +4228,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>0.0212</v>
+        <v>4.29</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>870500</v>
+        <v>1306100</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="H84" t="n">
-        <v>39.99</v>
-      </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.51000000000001</v>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>5.665</v>
+        <v>3.76</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>5.745</v>
+        <v>3.304</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4266,39 +4273,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E85" s="15" t="n">
-        <v>-0.004</v>
+        <v>2.91</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>843900</v>
+        <v>1291200</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="H85" t="n">
-        <v>45.17</v>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.09</v>
+      </c>
+      <c r="I85" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>2.564</v>
+        <v>2.704</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>2.455</v>
+        <v>2.534</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4311,39 +4318,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>0.0097</v>
+        <v>0.38</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>843300</v>
+        <v>1238300</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="H86" t="n">
-        <v>46.14</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.25</v>
+      </c>
+      <c r="I86" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>1.07</v>
+        <v>0.378</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1.026</v>
+        <v>0.38</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4356,39 +4363,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E87" s="17" t="n">
-        <v>0</v>
+        <v>0.58</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0.0265</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>804600</v>
+        <v>1222500</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.02</v>
+        <v>0.42</v>
       </c>
       <c r="H87" t="n">
-        <v>53.24</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.14</v>
+      </c>
+      <c r="I87" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.737</v>
+        <v>0.57</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.575</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4401,39 +4408,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>MAGMA</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E88" s="15" t="n">
-        <v>-0.0069</v>
+        <v>0.28</v>
+      </c>
+      <c r="E88" s="16" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>762500</v>
+        <v>1210300</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.05</v>
+        <v>2.16</v>
       </c>
       <c r="H88" t="n">
-        <v>64.84</v>
-      </c>
-      <c r="I88" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.6</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>2.801</v>
+        <v>0.288</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>2.659</v>
+        <v>0.287</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4446,28 +4453,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>0.0035</v>
+        <v>0.225</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>749600</v>
+        <v>1185800</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.25</v>
+        <v>0.47</v>
       </c>
       <c r="H89" t="n">
-        <v>40.82</v>
+        <v>27.67</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -4475,10 +4482,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>2.979</v>
+        <v>0.239</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>3.036</v>
+        <v>0.242</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4491,39 +4498,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E90" s="17" t="n">
-        <v>0</v>
+        <v>0.255</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>714900</v>
+        <v>1180900</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.08</v>
+        <v>1.39</v>
       </c>
       <c r="H90" t="n">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="I90" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.88</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>2.706</v>
+        <v>0.26</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>2.535</v>
+        <v>0.265</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4536,39 +4543,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="E91" s="15" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.365</v>
+      </c>
+      <c r="E91" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>709900</v>
+        <v>1164900</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.05</v>
+        <v>0.84</v>
       </c>
       <c r="H91" t="n">
-        <v>53.86</v>
-      </c>
-      <c r="I91" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.74</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>2.447</v>
+        <v>0.383</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>2.304</v>
+        <v>0.391</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4581,39 +4588,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>0.0039</v>
+        <v>1.09</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>702700</v>
+        <v>1139200</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="H92" t="n">
-        <v>49.62</v>
-      </c>
-      <c r="I92" s="16" t="inlineStr">
+        <v>74.20999999999999</v>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>2.565</v>
+        <v>1.026</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>2.546</v>
+        <v>0.868</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4626,39 +4633,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>0</v>
+        <v>2.88</v>
+      </c>
+      <c r="E93" s="16" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>700000</v>
+        <v>1129600</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="H93" t="n">
-        <v>41.61</v>
-      </c>
-      <c r="I93" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.41</v>
+      </c>
+      <c r="I93" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.63</v>
+        <v>2.8</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.636</v>
+        <v>2.659</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4671,40 +4678,33 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.295</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>0.0536</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>640500</v>
+        <v>1111200</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="H94" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J94" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="K94" s="9" t="n">
-        <v>0.598</v>
-      </c>
+        <v>0.09</v>
+      </c>
+      <c r="I94" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="n"/>
+      <c r="K94" s="9" t="n"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
     </row>
@@ -4716,39 +4716,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="E95" s="15" t="n">
-        <v>-0.0116</v>
+        <v>5.3</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>515500</v>
+        <v>1072900</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.1</v>
+        <v>0.33</v>
       </c>
       <c r="H95" t="n">
-        <v>42.16</v>
-      </c>
-      <c r="I95" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.68</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>1.759</v>
+        <v>5.664</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>1.794</v>
+        <v>5.745</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4761,45 +4761,1395 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="E96" s="15" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.465</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>512200</v>
+        <v>1059700</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.06</v>
+        <v>0.32</v>
       </c>
       <c r="H96" t="n">
-        <v>37.57</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.92</v>
+      </c>
+      <c r="I96" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>4.483</v>
+        <v>0.443</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>4.511</v>
+        <v>0.438</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E97" s="16" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>1058000</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H97" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="14" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>5180</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>CLMT</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E98" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>1031500</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H98" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="K98" s="9" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="14" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>1028600</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H99" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="K99" s="9" t="n">
+        <v>2.456</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="14" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0358</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ICTZONE</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="E100" s="16" t="n">
+        <v>-0.0408</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>1010200</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H100" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="14" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>-0.0173</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>994100</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H101" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I101" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>1.793</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="14" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>971400</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H102" t="n">
+        <v>39.66</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>2.978</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>3.036</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="14" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>916300</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H103" t="n">
+        <v>49.14</v>
+      </c>
+      <c r="I103" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="K103" s="9" t="n">
+        <v>1.018</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="14" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>909000</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H104" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="K104" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="E105" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>844200</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H105" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="I105" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>13.127</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>13.718</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="14" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>-0.0144</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>841300</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H106" t="n">
+        <v>37.08</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>4.481</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>4.511</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="14" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="E107" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>785800</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H107" t="n">
+        <v>55.28</v>
+      </c>
+      <c r="I107" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>2.448</v>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>2.304</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="14" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>770300</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H108" t="n">
+        <v>49.62</v>
+      </c>
+      <c r="I108" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="K108" s="9" t="n">
+        <v>2.546</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="14" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>733300</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H109" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>1.153</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="14" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="E110" s="16" t="n">
+        <v>-0.009399999999999999</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>707800</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H110" t="n">
+        <v>35.26</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>7.621</v>
+      </c>
+      <c r="K110" s="9" t="n">
+        <v>7.814</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H111" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="14" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="E112" s="16" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>667500</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H112" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>6.263</v>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>6.462</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>3662</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>MFLOUR</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>644200</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H113" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="14" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>640900</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H114" t="n">
+        <v>74.22</v>
+      </c>
+      <c r="I114" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="14" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E115" s="16" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>640500</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H115" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="K115" s="9" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="14" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="E116" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>640300</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H116" t="n">
+        <v>62.24</v>
+      </c>
+      <c r="I116" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>3.802</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>AXIATA</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="E117" s="16" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>632100</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>1.709</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="14" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E118" s="16" t="n">
+        <v>-0.0254</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>622400</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H118" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>3.253</v>
+      </c>
+      <c r="K118" s="9" t="n">
+        <v>3.452</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>IOICORP</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="E119" s="16" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>613100</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H119" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>4.602</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="14" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>-0.0272</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>600400</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H120" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n">
+        <v>1.878</v>
+      </c>
+      <c r="K120" s="9" t="n">
+        <v>1.955</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="14" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>572200</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H121" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="I121" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>2.802</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="14" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E122" s="16" t="n">
+        <v>-0.0241</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>553200</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H122" t="n">
+        <v>77.56999999999999</v>
+      </c>
+      <c r="I122" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="n">
+        <v>2.419</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>2.016</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>533100</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H123" t="n">
+        <v>69.81999999999999</v>
+      </c>
+      <c r="I123" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="14" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>0.005500000000000001</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>527100</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H124" t="n">
+        <v>41.52</v>
+      </c>
+      <c r="I124" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="K124" s="9" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="14" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>TAKAFUL</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E125" s="16" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>525000</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H125" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>3.036</v>
+      </c>
+      <c r="K125" s="9" t="n">
+        <v>3.136</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="14" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E126" s="16" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>516200</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H126" t="n">
+        <v>45.79</v>
+      </c>
+      <c r="I126" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K126" s="9" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M96"/>
+  <autoFilter ref="A1:M126"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-01/bursa-report-2026-10-01.xlsx
+++ b/docs/downloads/2026-10-01/bursa-report-2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-01" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-01'!$A$1:$M$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-01'!$A$1:$M$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M126"/>
+  <dimension ref="A1:M152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多，现价0.505高于50日均线0.468，RSI 61.7偏强但未超买，信号可靠性中等偏上。</t>
+          <t>SAR转多，现价0.505高于50日均线0.468，RSI 61.7偏强但未超买，信号可靠性中等偏正面。</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>0.0313</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>84627800</v>
+        <v>95340400</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="H3" t="n">
         <v>21.74</v>
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.285</v>
+        <v>0.29</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.0179</v>
+        <v>0.0357</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>77209300</v>
+        <v>86551100</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>2.66</v>
+        <v>2.98</v>
       </c>
       <c r="H4" t="n">
-        <v>72.5</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="I4" s="15" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.241</v>
+        <v>0.242</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>0.234</v>
@@ -715,10 +715,10 @@
         <v>-0.0244</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>72214600</v>
+        <v>72706200</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="H5" t="n">
         <v>78</v>
@@ -754,13 +754,13 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.23</v>
+        <v>0.225</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>53847700</v>
+        <v>55583400</v>
       </c>
       <c r="G6" s="12" t="n"/>
       <c r="I6" s="13" t="inlineStr">
@@ -796,10 +796,10 @@
         <v>0.0412</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>31634400</v>
+        <v>34663900</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="H7" t="n">
         <v>62.49</v>
@@ -826,39 +826,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0145</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TFP</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.2727</v>
+        <v>5.22</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0.0077</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>19736600</v>
+        <v>20515700</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>5.08</v>
+        <v>0.9</v>
       </c>
       <c r="H8" t="n">
-        <v>28.04</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.06</v>
+        <v>4.846</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.07099999999999999</v>
+        <v>4.566</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -871,39 +871,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>0145</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ASTRO</t>
+          <t>TFP</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>-0.2727</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>19755100</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n">
         <v>0.06</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>0.09089999999999999</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>18047800</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>14.96</v>
-      </c>
-      <c r="H9" t="n">
-        <v>51.74</v>
-      </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>0.058</v>
-      </c>
       <c r="K9" s="9" t="n">
-        <v>0.06</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -916,39 +916,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>ASTRO</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0.0097</v>
+        <v>0.055</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>18038900</v>
+        <v>18081400</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.79</v>
+        <v>14.99</v>
       </c>
       <c r="H10" t="n">
-        <v>77.26000000000001</v>
-      </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.56</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>4.847</v>
+        <v>0.058</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>4.567</v>
+        <v>0.06</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -961,33 +961,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.0435</v>
+        <v>0.2222</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>16074700</v>
+        <v>16789800</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="9" t="n"/>
+        <v>21.18</v>
+      </c>
+      <c r="H11" t="n">
+        <v>69.81</v>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0.08699999999999999</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
     </row>
@@ -999,40 +1006,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.46</v>
+        <v>0.12</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.0337</v>
+        <v>0.0435</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>15945800</v>
+        <v>16290100</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="H12" t="n">
-        <v>54.57</v>
+        <v>0.52</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J12" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="K12" s="9" t="n">
-        <v>0.415</v>
-      </c>
+      <c r="J12" s="9" t="n"/>
+      <c r="K12" s="9" t="n"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
     </row>
@@ -1044,39 +1044,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.11</v>
+        <v>0.455</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.2222</v>
+        <v>0.0225</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>14389100</v>
+        <v>16066500</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>18.15</v>
+        <v>1.73</v>
       </c>
       <c r="H13" t="n">
-        <v>69.81</v>
-      </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.4</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.091</v>
+        <v>0.45</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.415</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1089,28 +1089,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>-0.0265</v>
+        <v>0.37</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0.0423</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>11832000</v>
+        <v>13323200</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.78</v>
+        <v>1.79</v>
       </c>
       <c r="H14" t="n">
-        <v>56.14</v>
+        <v>71.03</v>
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.534</v>
+        <v>0.335</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.489</v>
+        <v>0.313</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1134,28 +1134,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0.0282</v>
+        <v>0.555</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>-0.0177</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>11395100</v>
+        <v>12347000</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1.53</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>69.59</v>
+        <v>57.43</v>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.334</v>
+        <v>0.535</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.313</v>
+        <v>0.489</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1179,39 +1179,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0</v>
+        <v>0.285</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>10608500</v>
+        <v>11317500</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.41</v>
+        <v>1.6</v>
       </c>
       <c r="H16" t="n">
-        <v>73.06999999999999</v>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.15</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.295</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.495</v>
+        <v>0.31</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1224,39 +1224,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>-0.0172</v>
+        <v>0.605</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>8323200</v>
+        <v>10739000</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>1.18</v>
+        <v>0.42</v>
       </c>
       <c r="H17" t="n">
-        <v>35.15</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.09999999999999</v>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.295</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.31</v>
+        <v>0.496</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1269,39 +1269,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>-0.0128</v>
+        <v>0.205</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0.0149</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>7136500</v>
+        <v>7890700</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.16</v>
+        <v>0.36</v>
       </c>
       <c r="H18" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.58</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.337</v>
+        <v>0.196</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.203</v>
+        <v>0.18</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1.75</v>
+        <v>0.385</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0128</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>6388700</v>
+        <v>7673400</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.28</v>
+        <v>0.17</v>
       </c>
       <c r="H19" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.7</v>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1.742</v>
+        <v>0.337</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>1.562</v>
+        <v>0.203</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1359,28 +1359,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>-0.0625</v>
+        <v>0.77</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>6077600</v>
+        <v>7628900</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.16</v>
+        <v>0.57</v>
       </c>
       <c r="H20" t="n">
-        <v>47.73</v>
+        <v>48.12</v>
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.157</v>
+        <v>0.773</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.147</v>
+        <v>0.774</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1404,28 +1404,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HUBLINE</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>0</v>
+        <v>1.78</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0.0114</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>5712800</v>
+        <v>7343100</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>4.24</v>
+        <v>0.32</v>
       </c>
       <c r="H21" t="n">
-        <v>45.42</v>
+        <v>56.77</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.032</v>
+        <v>1.745</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.032</v>
+        <v>1.562</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1449,28 +1449,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>0</v>
+        <v>0.155</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5295200</v>
+        <v>6317800</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.4</v>
+        <v>0.16</v>
       </c>
       <c r="H22" t="n">
-        <v>48.12</v>
+        <v>49.88</v>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.773</v>
+        <v>0.157</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.774</v>
+        <v>0.148</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1494,39 +1494,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.165</v>
+        <v>0.805</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>-0.0294</v>
+        <v>-0.0062</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>5135700</v>
+        <v>6131000</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>1.6</v>
+        <v>0.42</v>
       </c>
       <c r="H23" t="n">
-        <v>62.21</v>
-      </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.32</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.152</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.141</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1539,28 +1539,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>HUBLINE</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.295</v>
+        <v>0.03</v>
       </c>
       <c r="E24" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>5079000</v>
+        <v>5825900</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>2.48</v>
+        <v>4.33</v>
       </c>
       <c r="H24" t="n">
-        <v>49.25</v>
+        <v>45.42</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.295</v>
+        <v>0.032</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.296</v>
+        <v>0.032</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         <v>0.0179</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>4774500</v>
+        <v>5407400</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>2.59</v>
+        <v>2.93</v>
       </c>
       <c r="H25" t="n">
         <v>64.17</v>
@@ -1629,28 +1629,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>1.2</v>
+        <v>0.61</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0167</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>4752600</v>
+        <v>5280400</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1.25</v>
+        <v>0.51</v>
       </c>
       <c r="H26" t="n">
-        <v>66.34</v>
+        <v>51.26</v>
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1.126</v>
+        <v>0.607</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1.029</v>
+        <v>0.607</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1674,28 +1674,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0.025</v>
+        <v>0.16</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>-0.0588</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>4284600</v>
+        <v>5235700</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.41</v>
+        <v>1.63</v>
       </c>
       <c r="H27" t="n">
-        <v>53.53</v>
+        <v>58.05</v>
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.608</v>
+        <v>0.152</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.607</v>
+        <v>0.141</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1719,39 +1719,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>-0.0095</v>
+        <v>1.2</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0.008399999999999999</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>4135200</v>
+        <v>5085400</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.11</v>
+        <v>1.34</v>
       </c>
       <c r="H28" t="n">
-        <v>28.26</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.34</v>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.604</v>
+        <v>1.126</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>1.029</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1764,28 +1764,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>-0.0048</v>
+        <v>0.295</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>4124300</v>
+        <v>5079000</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.24</v>
+        <v>2.48</v>
       </c>
       <c r="H29" t="n">
-        <v>44.66</v>
+        <v>49.25</v>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>2.113</v>
+        <v>0.295</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>2.069</v>
+        <v>0.296</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1809,28 +1809,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0.0337</v>
+        <v>0.52</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>-0.0095</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4074800</v>
+        <v>4909500</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.33</v>
+        <v>0.13</v>
       </c>
       <c r="H30" t="n">
-        <v>56.39</v>
+        <v>28.26</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>3.606</v>
+        <v>0.604</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>2.501</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1854,28 +1854,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="E31" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3929200</v>
+        <v>4766800</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.27</v>
+        <v>0.64</v>
       </c>
       <c r="H31" t="n">
-        <v>50.2</v>
+        <v>31.89</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.348</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.349</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1899,39 +1899,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0.0857</v>
+        <v>0.305</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3924200</v>
+        <v>4422700</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.77</v>
+        <v>0.22</v>
       </c>
       <c r="H32" t="n">
-        <v>67.62</v>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.62</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.165</v>
+        <v>0.303</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.165</v>
+        <v>0.292</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1944,28 +1944,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>0</v>
+        <v>2.07</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>3868200</v>
+        <v>4337700</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.62</v>
+        <v>0.25</v>
       </c>
       <c r="H33" t="n">
-        <v>48.24</v>
+        <v>44.66</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.367</v>
+        <v>2.113</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.367</v>
+        <v>2.069</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1989,28 +1989,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>0.0225</v>
+        <v>0.865</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>3829200</v>
+        <v>4295700</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1.64</v>
+        <v>0.23</v>
       </c>
       <c r="H34" t="n">
-        <v>77.72</v>
+        <v>46.8</v>
       </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.389</v>
+        <v>0.868</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.35</v>
+        <v>0.87</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2034,28 +2034,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>-0.062</v>
+        <v>3.66</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0.0281</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>3794800</v>
+        <v>4255900</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>2.55</v>
+        <v>0.34</v>
       </c>
       <c r="H35" t="n">
-        <v>38.75</v>
+        <v>56.05</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>1.275</v>
+        <v>3.604</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1.332</v>
+        <v>2.5</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2094,10 +2094,10 @@
         <v>-0.002</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>3742100</v>
+        <v>4231500</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="H36" t="n">
         <v>35.89</v>
@@ -2124,39 +2124,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>0</v>
+        <v>1.21</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>-0.062</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>3301600</v>
+        <v>4136000</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.43</v>
+        <v>2.78</v>
       </c>
       <c r="H37" t="n">
-        <v>62.52</v>
-      </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.75</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.335</v>
+        <v>1.275</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.315</v>
+        <v>1.332</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2169,28 +2169,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>-0.0135</v>
+        <v>0.365</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3243000</v>
+        <v>4058200</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
       <c r="H38" t="n">
-        <v>30.31</v>
+        <v>48.24</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.782</v>
+        <v>0.367</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.838</v>
+        <v>0.367</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2214,39 +2214,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>0</v>
+        <v>0.19</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0.0857</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>3159200</v>
+        <v>3968300</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.49</v>
+        <v>0.78</v>
       </c>
       <c r="H39" t="n">
-        <v>43.51</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.62</v>
+      </c>
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.77</v>
+        <v>0.165</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.771</v>
+        <v>0.165</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2259,28 +2259,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.79</v>
+        <v>0.445</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2919400</v>
+        <v>3951000</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.26</v>
+        <v>1.7</v>
       </c>
       <c r="H40" t="n">
-        <v>61.75</v>
+        <v>76.12</v>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.733</v>
+        <v>0.388</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.694</v>
+        <v>0.35</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2304,39 +2304,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>-0.027</v>
+        <v>-0.0806</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>2902700</v>
+        <v>3892300</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.42</v>
+        <v>0.61</v>
       </c>
       <c r="H41" t="n">
-        <v>38.71</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.2</v>
+      </c>
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>1.161</v>
+        <v>0.967</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>1.15</v>
+        <v>0.766</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2349,28 +2349,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>-0.0106</v>
+        <v>0.76</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>2695900</v>
+        <v>3763200</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="H42" t="n">
-        <v>28.01</v>
+        <v>43.51</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>4.804</v>
+        <v>0.77</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>4.937</v>
+        <v>0.771</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2394,28 +2394,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>0</v>
+        <v>0.36</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2652400</v>
+        <v>3560900</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.16</v>
+        <v>0.47</v>
       </c>
       <c r="H43" t="n">
-        <v>50.77</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>2.281</v>
+        <v>0.335</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>2.201</v>
+        <v>0.315</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2439,39 +2439,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>1.16</v>
+        <v>0.73</v>
       </c>
       <c r="E44" s="16" t="n">
-        <v>-0.0645</v>
+        <v>-0.0135</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>2587600</v>
+        <v>3540400</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.41</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>73.75</v>
-      </c>
-      <c r="I44" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.31</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.969</v>
+        <v>0.782</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.766</v>
+        <v>0.838</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2484,28 +2484,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>0</v>
+        <v>0.375</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>2518700</v>
+        <v>3511300</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="H45" t="n">
-        <v>46.8</v>
+        <v>50.49</v>
       </c>
       <c r="I45" s="15" t="inlineStr">
         <is>
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.868</v>
+        <v>0.376</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.87</v>
+        <v>0.372</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2529,39 +2529,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>0</v>
+        <v>3.07</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>2441500</v>
+        <v>3123500</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.29</v>
+        <v>0.87</v>
       </c>
       <c r="H46" t="n">
-        <v>50.12</v>
-      </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.23</v>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.264</v>
+        <v>2.906</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.224</v>
+        <v>2.719</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2574,28 +2574,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.79</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2432500</v>
+        <v>3060700</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.67</v>
+        <v>0.28</v>
       </c>
       <c r="H47" t="n">
-        <v>60.23</v>
+        <v>61.75</v>
       </c>
       <c r="I47" s="15" t="inlineStr">
         <is>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>2.906</v>
+        <v>0.733</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>2.719</v>
+        <v>0.694</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2619,39 +2619,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>1.08</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>-0.027</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2428800</v>
+        <v>2988400</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.24</v>
+        <v>0.43</v>
       </c>
       <c r="H48" t="n">
-        <v>55.14</v>
-      </c>
-      <c r="I48" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.71</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.636</v>
+        <v>1.161</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.582</v>
+        <v>1.15</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2388100</v>
+        <v>2988100</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="H49" t="n">
         <v>57.09</v>
@@ -2709,28 +2709,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E50" s="17" t="n">
-        <v>0</v>
+        <v>4.67</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>2348700</v>
+        <v>2973900</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1.77</v>
+        <v>0.17</v>
       </c>
       <c r="H50" t="n">
-        <v>31.63</v>
+        <v>29.36</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.357</v>
+        <v>4.806</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.391</v>
+        <v>4.937</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2754,39 +2754,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.515</v>
+        <v>0.79</v>
       </c>
       <c r="E51" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>2188500</v>
+        <v>2931500</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.34</v>
+        <v>0.47</v>
       </c>
       <c r="H51" t="n">
-        <v>30.06</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.37</v>
+      </c>
+      <c r="I51" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.55</v>
+        <v>0.77</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.584</v>
+        <v>0.756</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2799,39 +2799,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>0.009399999999999999</v>
+        <v>2.27</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>-0.0044</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>2158000</v>
+        <v>2675800</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.55</v>
+        <v>0.16</v>
       </c>
       <c r="H52" t="n">
-        <v>58.93</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.98</v>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.516</v>
+        <v>2.28</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.472</v>
+        <v>2.2</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2844,28 +2844,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.3</v>
+        <v>0.65</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>0.0169</v>
+        <v>0.0156</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2152600</v>
+        <v>2462300</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="H53" t="n">
-        <v>68.88</v>
+        <v>56.16</v>
       </c>
       <c r="I53" s="15" t="inlineStr">
         <is>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.28</v>
+        <v>0.636</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.272</v>
+        <v>0.583</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2889,39 +2889,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>0.0233</v>
+        <v>0.25</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2087200</v>
+        <v>2442900</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.38</v>
+        <v>0.29</v>
       </c>
       <c r="H54" t="n">
-        <v>54.54</v>
-      </c>
-      <c r="I54" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.34</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.215</v>
+        <v>0.263</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.213</v>
+        <v>0.224</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2934,39 +2934,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>-0.0077</v>
+        <v>0.22</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2028800</v>
+        <v>2384200</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.16</v>
+        <v>0.43</v>
       </c>
       <c r="H55" t="n">
-        <v>43.19</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.54</v>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>1.355</v>
+        <v>0.215</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>1.298</v>
+        <v>0.213</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2979,39 +2979,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.515</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1948600</v>
+        <v>2381900</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.71</v>
+        <v>0.37</v>
       </c>
       <c r="H56" t="n">
-        <v>76.33</v>
-      </c>
-      <c r="I56" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.06</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.425</v>
+        <v>0.55</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.415</v>
+        <v>0.584</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3024,39 +3024,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="E57" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1919300</v>
+        <v>2354800</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.12</v>
+        <v>1.77</v>
       </c>
       <c r="H57" t="n">
-        <v>52.59</v>
-      </c>
-      <c r="I57" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.63</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.286</v>
+        <v>0.357</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.277</v>
+        <v>0.391</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3069,33 +3069,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.475</v>
+        <v>0.295</v>
       </c>
       <c r="E58" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1861900</v>
+        <v>2317500</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.11</v>
+        <v>0.36</v>
+      </c>
+      <c r="H58" t="n">
+        <v>66.25</v>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J58" s="9" t="n"/>
-      <c r="K58" s="9" t="n"/>
+      <c r="J58" s="9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>0.272</v>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
     </row>
@@ -3107,28 +3114,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E59" s="17" t="n">
-        <v>0</v>
+        <v>0.535</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1857800</v>
+        <v>2285700</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>8.73</v>
+        <v>0.58</v>
       </c>
       <c r="H59" t="n">
-        <v>57.18</v>
+        <v>58.93</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3136,10 +3143,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.44</v>
+        <v>0.516</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.434</v>
+        <v>0.472</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3152,39 +3159,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.92</v>
+        <v>0.44</v>
       </c>
       <c r="E60" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1819000</v>
+        <v>2207800</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.36</v>
+        <v>10.38</v>
       </c>
       <c r="H60" t="n">
-        <v>63.45</v>
-      </c>
-      <c r="I60" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.18</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.895</v>
+        <v>0.44</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.854</v>
+        <v>0.434</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3197,39 +3204,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
         <v>0.51</v>
       </c>
-      <c r="E61" s="17" t="n">
-        <v>0</v>
+      <c r="E61" s="10" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1804100</v>
+        <v>2166300</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.27</v>
+        <v>0.79</v>
       </c>
       <c r="H61" t="n">
-        <v>45.42</v>
-      </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.33</v>
+      </c>
+      <c r="I61" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.522</v>
+        <v>0.425</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.532</v>
+        <v>0.415</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3242,39 +3249,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>0.009000000000000001</v>
+        <v>1.3</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1795500</v>
+        <v>2159000</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="H62" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="I62" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.18</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.497</v>
+        <v>1.356</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.415</v>
+        <v>1.298</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3287,28 +3294,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>6.9</v>
+        <v>2.74</v>
       </c>
       <c r="E63" s="16" t="n">
-        <v>-0.024</v>
+        <v>-0.0036</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1775500</v>
+        <v>2112700</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="H63" t="n">
-        <v>56.73</v>
+        <v>80.03</v>
       </c>
       <c r="I63" s="15" t="inlineStr">
         <is>
@@ -3316,10 +3323,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>6.668</v>
+        <v>2.535</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>6.552</v>
+        <v>2.18</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3332,36 +3339,40 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.265</v>
+        <v>7.43</v>
       </c>
       <c r="E64" s="16" t="n">
-        <v>-0.0185</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1722300</v>
+        <v>2089800</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H64" t="n">
-        <v>15.91</v>
+        <v>24.11</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J64" s="9" t="n"/>
-      <c r="K64" s="9" t="n"/>
+      <c r="J64" s="9" t="n">
+        <v>7.849</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>8.212999999999999</v>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
     </row>
@@ -3373,40 +3384,33 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.475</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1713300</v>
+        <v>2081400</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H65" t="n">
-        <v>61.18</v>
+        <v>0.13</v>
       </c>
       <c r="I65" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J65" s="9" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="K65" s="9" t="n">
-        <v>0.61</v>
-      </c>
+      <c r="J65" s="9" t="n"/>
+      <c r="K65" s="9" t="n"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
     </row>
@@ -3418,39 +3422,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E66" s="17" t="n">
-        <v>0</v>
+        <v>2.51</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0.004</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1699100</v>
+        <v>2061200</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="H66" t="n">
-        <v>33.55</v>
-      </c>
-      <c r="I66" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.76</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.268</v>
+        <v>2.566</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.32</v>
+        <v>2.456</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3463,28 +3467,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0.0036</v>
+        <v>5.81</v>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>-0.0102</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1662400</v>
+        <v>2010600</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.39</v>
+        <v>0.14</v>
       </c>
       <c r="H67" t="n">
-        <v>81.98999999999999</v>
+        <v>59.29</v>
       </c>
       <c r="I67" s="15" t="inlineStr">
         <is>
@@ -3492,10 +3496,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>2.537</v>
+        <v>5.69</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>2.18</v>
+        <v>5.191</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3508,39 +3512,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>7.46</v>
+        <v>6.98</v>
       </c>
       <c r="E68" s="16" t="n">
-        <v>-0.0053</v>
+        <v>-0.0127</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1612400</v>
+        <v>1996000</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="H68" t="n">
-        <v>24.83</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.93</v>
+      </c>
+      <c r="I68" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>7.852</v>
+        <v>6.675</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>8.214</v>
+        <v>6.554</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3553,28 +3557,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.305</v>
+        <v>0.51</v>
       </c>
       <c r="E69" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1612100</v>
+        <v>1981500</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.08</v>
+        <v>0.3</v>
       </c>
       <c r="H69" t="n">
-        <v>53.62</v>
+        <v>45.42</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3582,10 +3586,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.303</v>
+        <v>0.522</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.292</v>
+        <v>0.532</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3598,28 +3602,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="E70" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1605600</v>
+        <v>1954800</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="H70" t="n">
-        <v>64.37</v>
+        <v>52.59</v>
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
@@ -3627,10 +3631,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.77</v>
+        <v>0.286</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.756</v>
+        <v>0.277</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3643,28 +3647,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>-0.0263</v>
+        <v>0.245</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1587700</v>
+        <v>1922500</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>46.98</v>
+        <v>33.55</v>
       </c>
       <c r="I71" s="15" t="inlineStr">
         <is>
@@ -3672,10 +3676,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.375</v>
+        <v>0.268</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.371</v>
+        <v>0.32</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3688,28 +3692,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>5.83</v>
+        <v>2.94</v>
       </c>
       <c r="E72" s="16" t="n">
-        <v>-0.0068</v>
+        <v>-0.0265</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1574900</v>
+        <v>1903600</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.11</v>
+        <v>0.6</v>
       </c>
       <c r="H72" t="n">
-        <v>60.28</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
@@ -3717,10 +3721,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>5.692</v>
+        <v>2.409</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>5.191</v>
+        <v>1.862</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3733,39 +3737,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.74</v>
+        <v>0.92</v>
       </c>
       <c r="E73" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1559400</v>
+        <v>1830100</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.03</v>
+        <v>0.37</v>
       </c>
       <c r="H73" t="n">
-        <v>53.24</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.45</v>
+      </c>
+      <c r="I73" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.737</v>
+        <v>0.895</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.854</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3778,28 +3782,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0396</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ADNEX</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>0.0118</v>
+        <v>1.7</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>-0.0173</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1477200</v>
+        <v>1825100</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>3.41</v>
+        <v>0.34</v>
       </c>
       <c r="H74" t="n">
-        <v>56.98</v>
+        <v>41.1</v>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
@@ -3807,10 +3811,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.418</v>
+        <v>1.758</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.415</v>
+        <v>1.793</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3823,28 +3827,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E75" s="16" t="n">
-        <v>-0.0331</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1428400</v>
+        <v>1815200</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.45</v>
+        <v>0.12</v>
       </c>
       <c r="H75" t="n">
-        <v>75.3</v>
+        <v>68.7</v>
       </c>
       <c r="I75" s="15" t="inlineStr">
         <is>
@@ -3852,10 +3856,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.407</v>
+        <v>0.497</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>1.862</v>
+        <v>0.415</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3868,40 +3872,33 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E76" s="16" t="n">
-        <v>-0.0377</v>
+        <v>0.3</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0.07139999999999999</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1417900</v>
+        <v>1807200</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H76" t="n">
-        <v>64.37</v>
+        <v>0.14</v>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J76" s="9" t="n">
-        <v>0.234</v>
-      </c>
-      <c r="K76" s="9" t="n">
-        <v>0.211</v>
-      </c>
+      <c r="J76" s="9" t="n"/>
+      <c r="K76" s="9" t="n"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
     </row>
@@ -3913,39 +3910,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E77" s="17" t="n">
-        <v>0</v>
+        <v>7.77</v>
+      </c>
+      <c r="E77" s="16" t="n">
+        <v>-0.0026</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1394200</v>
+        <v>1789000</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H77" t="n">
-        <v>42.45</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.28</v>
+      </c>
+      <c r="I77" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.407</v>
+        <v>7.799</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.411</v>
+        <v>7.747</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3958,28 +3955,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E78" s="17" t="n">
-        <v>0</v>
+        <v>6.75</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1382000</v>
+        <v>1784200</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.22</v>
+        <v>0.41</v>
       </c>
       <c r="H78" t="n">
-        <v>62.32</v>
+        <v>49.04</v>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
@@ -3987,10 +3984,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.696</v>
+        <v>6.758</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.624</v>
+        <v>6.83</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4003,40 +4000,36 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.265</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1373600</v>
+        <v>1782500</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.46</v>
+        <v>0.1</v>
       </c>
       <c r="H79" t="n">
-        <v>85.89</v>
-      </c>
-      <c r="I79" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J79" s="9" t="n">
-        <v>1.124</v>
-      </c>
-      <c r="K79" s="9" t="n">
-        <v>0.929</v>
-      </c>
+        <v>15.91</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="n"/>
+      <c r="K79" s="9" t="n"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
     </row>
@@ -4048,39 +4041,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E80" s="16" t="n">
-        <v>-0.009899999999999999</v>
+        <v>2.47</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0.004099999999999999</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1361900</v>
+        <v>1777100</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="H80" t="n">
-        <v>56.72</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.42</v>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.196</v>
+        <v>2.449</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.18</v>
+        <v>2.304</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4093,28 +4086,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.675</v>
+        <v>0.65</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>0.015</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1347000</v>
+        <v>1769600</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.18</v>
+        <v>0.54</v>
       </c>
       <c r="H81" t="n">
-        <v>49.33</v>
+        <v>61.18</v>
       </c>
       <c r="I81" s="15" t="inlineStr">
         <is>
@@ -4122,10 +4115,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.68</v>
+        <v>0.608</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.666</v>
+        <v>0.61</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4138,28 +4131,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>0.028</v>
+        <v>4.28</v>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>-0.0183</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1341600</v>
+        <v>1696000</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="H82" t="n">
-        <v>74.3</v>
+        <v>73.02</v>
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
@@ -4167,10 +4160,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>1.003</v>
+        <v>3.759</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.831</v>
+        <v>3.304</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4183,28 +4176,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>7.77</v>
+        <v>2.92</v>
       </c>
       <c r="E83" s="16" t="n">
-        <v>-0.0026</v>
+        <v>-0.0034</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1317300</v>
+        <v>1660200</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="H83" t="n">
-        <v>49.28</v>
+        <v>63.71</v>
       </c>
       <c r="I83" s="15" t="inlineStr">
         <is>
@@ -4212,10 +4205,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>7.799</v>
+        <v>2.705</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>7.747</v>
+        <v>2.534</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4228,39 +4221,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>4.29</v>
+        <v>0.735</v>
       </c>
       <c r="E84" s="16" t="n">
-        <v>-0.0161</v>
+        <v>-0.0068</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1306100</v>
+        <v>1633400</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="H84" t="n">
-        <v>73.51000000000001</v>
-      </c>
-      <c r="I84" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.99</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>3.76</v>
+        <v>0.736</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>3.304</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4273,28 +4266,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E85" s="16" t="n">
-        <v>-0.0068</v>
+        <v>0.675</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0.015</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1291200</v>
+        <v>1562300</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="H85" t="n">
-        <v>63.09</v>
+        <v>49.33</v>
       </c>
       <c r="I85" s="15" t="inlineStr">
         <is>
@@ -4302,10 +4295,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>2.704</v>
+        <v>0.68</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>2.534</v>
+        <v>0.666</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4318,28 +4311,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0398</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GDGROUP</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>0</v>
+        <v>0.255</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>-0.0377</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1238300</v>
+        <v>1528900</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>1.52</v>
+        <v>0.51</v>
       </c>
       <c r="H86" t="n">
-        <v>53.25</v>
+        <v>64.37</v>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
@@ -4347,10 +4340,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.378</v>
+        <v>0.234</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.38</v>
+        <v>0.211</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4363,39 +4356,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>0.0265</v>
+        <v>0.22</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1222500</v>
+        <v>1520900</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="H87" t="n">
-        <v>53.14</v>
-      </c>
-      <c r="I87" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.44</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.57</v>
+        <v>0.239</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.575</v>
+        <v>0.242</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4408,28 +4401,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MAGMA</t>
+          <t>IWCITY</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E88" s="16" t="n">
-        <v>-0.0175</v>
+        <v>0.22</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0.0732</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1210300</v>
+        <v>1513600</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>2.16</v>
+        <v>1.73</v>
       </c>
       <c r="H88" t="n">
-        <v>28.6</v>
+        <v>53.96</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -4437,10 +4430,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.288</v>
+        <v>0.214</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.287</v>
+        <v>0.224</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4453,39 +4446,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>0396</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>ADNEX</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>0</v>
+        <v>0.43</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>0.0118</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1185800</v>
+        <v>1498100</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.47</v>
+        <v>3.46</v>
       </c>
       <c r="H89" t="n">
-        <v>27.67</v>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.98</v>
+      </c>
+      <c r="I89" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.239</v>
+        <v>0.418</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.242</v>
+        <v>0.415</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4498,39 +4491,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E90" s="16" t="n">
-        <v>-0.0192</v>
+        <v>1.1</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0.028</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1180900</v>
+        <v>1497100</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>1.39</v>
+        <v>0.3</v>
       </c>
       <c r="H90" t="n">
-        <v>37.88</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.3</v>
+      </c>
+      <c r="I90" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.26</v>
+        <v>1.003</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.265</v>
+        <v>0.831</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4543,39 +4536,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E91" s="17" t="n">
-        <v>0</v>
+        <v>0.745</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0.0136</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1164900</v>
+        <v>1489400</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.84</v>
+        <v>0.24</v>
       </c>
       <c r="H91" t="n">
-        <v>38.74</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.77</v>
+      </c>
+      <c r="I91" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.383</v>
+        <v>0.697</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.391</v>
+        <v>0.624</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4588,28 +4581,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E92" s="17" t="n">
-        <v>0</v>
+        <v>0.59</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>0.0442</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1139200</v>
+        <v>1456000</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.09</v>
+        <v>0.5</v>
       </c>
       <c r="H92" t="n">
-        <v>74.20999999999999</v>
+        <v>55.57</v>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
@@ -4617,10 +4610,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>1.026</v>
+        <v>0.571</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.868</v>
+        <v>0.575</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4633,39 +4626,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>2.88</v>
+        <v>4.08</v>
       </c>
       <c r="E93" s="16" t="n">
-        <v>-0.0103</v>
+        <v>-0.0239</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1129600</v>
+        <v>1449300</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="H93" t="n">
-        <v>63.41</v>
-      </c>
-      <c r="I93" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.15</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>2.8</v>
+        <v>4.477</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>2.659</v>
+        <v>4.51</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4678,33 +4671,40 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>0.0536</v>
+        <v>0.4</v>
+      </c>
+      <c r="E94" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1111200</v>
+        <v>1440300</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I94" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J94" s="9" t="n"/>
-      <c r="K94" s="9" t="n"/>
+        <v>0.13</v>
+      </c>
+      <c r="H94" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>0.411</v>
+      </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
     </row>
@@ -4716,39 +4716,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>0.0192</v>
+        <v>0.0072</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1072900</v>
+        <v>1414300</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.33</v>
+        <v>0.48</v>
       </c>
       <c r="H95" t="n">
-        <v>39.68</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>85.89</v>
+      </c>
+      <c r="I95" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>5.664</v>
+        <v>1.124</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>5.745</v>
+        <v>0.929</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4761,39 +4761,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>0.0109</v>
+        <v>1.64</v>
+      </c>
+      <c r="E96" s="16" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1059700</v>
+        <v>1399000</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
       <c r="H96" t="n">
-        <v>57.92</v>
-      </c>
-      <c r="I96" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.94</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.443</v>
+        <v>1.709</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.438</v>
+        <v>1.825</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4806,28 +4806,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.02</v>
+        <v>0.255</v>
       </c>
       <c r="E97" s="16" t="n">
-        <v>-0.0097</v>
+        <v>-0.0192</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1058000</v>
+        <v>1329300</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.09</v>
+        <v>0.85</v>
       </c>
       <c r="H97" t="n">
-        <v>42.99</v>
+        <v>38.92</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.068</v>
+        <v>0.267</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>1.025</v>
+        <v>0.278</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4851,39 +4851,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E98" s="17" t="n">
-        <v>0</v>
+        <v>2.88</v>
+      </c>
+      <c r="E98" s="16" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1031500</v>
+        <v>1318800</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.26</v>
+        <v>0.09</v>
       </c>
       <c r="H98" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="I98" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.41</v>
+      </c>
+      <c r="I98" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.582</v>
+        <v>2.8</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.586</v>
+        <v>2.659</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4896,28 +4896,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E99" s="17" t="n">
-        <v>0</v>
+        <v>5.3</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1028600</v>
+        <v>1253900</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.06</v>
+        <v>0.38</v>
       </c>
       <c r="H99" t="n">
-        <v>45.9</v>
+        <v>39.68</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>2.565</v>
+        <v>5.664</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>2.456</v>
+        <v>5.745</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4941,39 +4941,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E100" s="16" t="n">
-        <v>-0.0408</v>
+        <v>0.38</v>
+      </c>
+      <c r="E100" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1010200</v>
+        <v>1248300</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.32</v>
+        <v>1.53</v>
       </c>
       <c r="H100" t="n">
-        <v>41.86</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.25</v>
+      </c>
+      <c r="I100" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.254</v>
+        <v>0.378</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.253</v>
+        <v>0.38</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4986,28 +4986,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E101" s="16" t="n">
-        <v>-0.0173</v>
+        <v>1.1</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>0.0092</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>994100</v>
+        <v>1235400</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="H101" t="n">
-        <v>41.1</v>
+        <v>75.37</v>
       </c>
       <c r="I101" s="15" t="inlineStr">
         <is>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>1.758</v>
+        <v>1.027</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>1.793</v>
+        <v>0.868</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5031,28 +5031,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E102" s="17" t="n">
-        <v>0</v>
+        <v>1.02</v>
+      </c>
+      <c r="E102" s="16" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>971400</v>
+        <v>1225600</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.33</v>
+        <v>0.11</v>
       </c>
       <c r="H102" t="n">
-        <v>39.66</v>
+        <v>42.99</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>2.978</v>
+        <v>1.068</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>3.036</v>
+        <v>1.025</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5076,39 +5076,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>MAGMA</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>1.02</v>
+        <v>0.28</v>
       </c>
       <c r="E103" s="16" t="n">
-        <v>-0.0192</v>
+        <v>-0.0175</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>916300</v>
+        <v>1210300</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.58</v>
+        <v>2.16</v>
       </c>
       <c r="H103" t="n">
-        <v>49.14</v>
-      </c>
-      <c r="I103" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.6</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>1.029</v>
+        <v>0.288</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>1.018</v>
+        <v>0.287</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5121,39 +5121,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.575</v>
+        <v>0.255</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>909000</v>
+        <v>1202600</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="H104" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.14</v>
+      </c>
+      <c r="I104" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.622</v>
+        <v>0.267</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.655</v>
+        <v>0.31</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5166,39 +5166,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>12.96</v>
-      </c>
-      <c r="E105" s="17" t="n">
-        <v>0</v>
+        <v>0.255</v>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>844200</v>
+        <v>1180900</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.1</v>
+        <v>1.39</v>
       </c>
       <c r="H105" t="n">
-        <v>38.67</v>
-      </c>
-      <c r="I105" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.88</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>13.127</v>
+        <v>0.26</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>13.718</v>
+        <v>0.265</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5211,28 +5211,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="E106" s="16" t="n">
-        <v>-0.0144</v>
+        <v>0.365</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>841300</v>
+        <v>1164900</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.11</v>
+        <v>0.84</v>
       </c>
       <c r="H106" t="n">
-        <v>37.08</v>
+        <v>38.74</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>4.481</v>
+        <v>0.383</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>4.511</v>
+        <v>0.391</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5256,28 +5256,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="E107" s="17" t="n">
-        <v>0</v>
+        <v>12.94</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>-0.0015</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>785800</v>
+        <v>1160800</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="H107" t="n">
-        <v>55.28</v>
+        <v>38.11</v>
       </c>
       <c r="I107" s="15" t="inlineStr">
         <is>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>2.448</v>
+        <v>13.125</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>2.304</v>
+        <v>13.717</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5301,28 +5301,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>2.56</v>
+        <v>0.465</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>0.0039</v>
+        <v>0.0109</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>770300</v>
+        <v>1129900</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.13</v>
+        <v>0.34</v>
       </c>
       <c r="H108" t="n">
-        <v>49.62</v>
+        <v>57.92</v>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>2.565</v>
+        <v>0.443</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>2.546</v>
+        <v>0.438</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5346,39 +5346,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1.13</v>
+        <v>2.57</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>0.0089</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>733300</v>
+        <v>1115400</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="H109" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.77</v>
+      </c>
+      <c r="I109" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>1.153</v>
+        <v>2.566</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>1.105</v>
+        <v>2.546</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5391,39 +5391,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>7.38</v>
+        <v>0.475</v>
       </c>
       <c r="E110" s="16" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.0206</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>707800</v>
+        <v>1113900</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.1</v>
+        <v>0.37</v>
       </c>
       <c r="H110" t="n">
-        <v>35.26</v>
-      </c>
-      <c r="I110" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.71</v>
+      </c>
+      <c r="I110" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>7.621</v>
+        <v>0.456</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>7.814</v>
+        <v>0.411</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5436,28 +5436,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E111" s="17" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E111" s="10" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>700000</v>
+        <v>1099200</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="H111" t="n">
-        <v>41.61</v>
+        <v>55.77</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -5465,10 +5465,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.63</v>
+        <v>0.861</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.636</v>
+        <v>0.856</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5481,28 +5481,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>6.11</v>
+        <v>1.89</v>
       </c>
       <c r="E112" s="16" t="n">
-        <v>-0.0145</v>
+        <v>-0.0258</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>667500</v>
+        <v>1090700</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="H112" t="n">
-        <v>36.68</v>
+        <v>37.79</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>6.263</v>
+        <v>1.968</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>6.462</v>
+        <v>1.97</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5526,28 +5526,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.61</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E113" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>644200</v>
+        <v>1090400</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H113" t="n">
-        <v>39.13</v>
+        <v>33.33</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -5555,10 +5555,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.63</v>
+        <v>0.582</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.636</v>
+        <v>0.586</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5571,28 +5571,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E114" s="16" t="n">
-        <v>-0.0185</v>
+        <v>0.315</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>640900</v>
+        <v>1073600</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="H114" t="n">
-        <v>74.22</v>
+        <v>46.36</v>
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.318</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.783</v>
+        <v>0.337</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5616,28 +5616,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E115" s="16" t="n">
-        <v>-0.007800000000000001</v>
+        <v>2.89</v>
+      </c>
+      <c r="E115" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>640500</v>
+        <v>1043100</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="H115" t="n">
-        <v>56.5</v>
+        <v>39.66</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.635</v>
+        <v>2.978</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.598</v>
+        <v>3.036</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5661,28 +5661,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="E116" s="17" t="n">
-        <v>0</v>
+        <v>1.02</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0.0515</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>640300</v>
+        <v>1038700</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.21</v>
+        <v>1.77</v>
       </c>
       <c r="H116" t="n">
-        <v>62.24</v>
+        <v>62.33</v>
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
@@ -5690,10 +5690,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>3.802</v>
+        <v>0.985</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>3.46</v>
+        <v>0.976</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5706,40 +5706,33 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E117" s="16" t="n">
-        <v>-0.012</v>
+        <v>0.255</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>632100</v>
+        <v>1035000</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H117" t="n">
-        <v>36.94</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J117" s="9" t="n">
-        <v>1.709</v>
-      </c>
-      <c r="K117" s="9" t="n">
-        <v>1.825</v>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I117" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n"/>
+      <c r="K117" s="9" t="n"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
     </row>
@@ -5751,28 +5744,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>3.07</v>
+        <v>0.235</v>
       </c>
       <c r="E118" s="16" t="n">
-        <v>-0.0254</v>
+        <v>-0.0408</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>622400</v>
+        <v>1010200</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.18</v>
+        <v>0.32</v>
       </c>
       <c r="H118" t="n">
-        <v>26.4</v>
+        <v>41.86</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5780,10 +5773,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>3.253</v>
+        <v>0.254</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>3.452</v>
+        <v>0.253</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5796,28 +5789,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="E119" s="16" t="n">
-        <v>-0.0064</v>
+        <v>0.575</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>0.008800000000000001</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>613100</v>
+        <v>990400</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.06</v>
+        <v>0.2</v>
       </c>
       <c r="H119" t="n">
-        <v>47.08</v>
+        <v>31.6</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5825,10 +5818,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>4.73</v>
+        <v>0.622</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>4.602</v>
+        <v>0.655</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5841,28 +5834,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1.79</v>
+        <v>7.36</v>
       </c>
       <c r="E120" s="16" t="n">
-        <v>-0.0272</v>
+        <v>-0.0121</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>600400</v>
+        <v>971600</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="H120" t="n">
-        <v>37.92</v>
+        <v>34.61</v>
       </c>
       <c r="I120" s="13" t="inlineStr">
         <is>
@@ -5870,10 +5863,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>1.878</v>
+        <v>7.619</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>1.955</v>
+        <v>7.813</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5886,28 +5879,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>0.0106</v>
+        <v>1.03</v>
+      </c>
+      <c r="E121" s="16" t="n">
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>572200</v>
+        <v>970500</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.19</v>
+        <v>0.61</v>
       </c>
       <c r="H121" t="n">
-        <v>55.37</v>
+        <v>50.78</v>
       </c>
       <c r="I121" s="15" t="inlineStr">
         <is>
@@ -5915,10 +5908,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>2.802</v>
+        <v>1.029</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>2.715</v>
+        <v>1.018</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5931,39 +5924,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>2.83</v>
+        <v>6.12</v>
       </c>
       <c r="E122" s="16" t="n">
-        <v>-0.0241</v>
+        <v>-0.0129</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>553200</v>
+        <v>921100</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.21</v>
+        <v>0.06</v>
       </c>
       <c r="H122" t="n">
-        <v>77.56999999999999</v>
-      </c>
-      <c r="I122" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.18</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>2.419</v>
+        <v>6.264</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>2.016</v>
+        <v>6.462</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5976,39 +5969,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>0.09279999999999999</v>
+        <v>3.05</v>
+      </c>
+      <c r="E123" s="16" t="n">
+        <v>-0.0317</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>533100</v>
+        <v>916300</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.91</v>
+        <v>0.26</v>
       </c>
       <c r="H123" t="n">
-        <v>69.81999999999999</v>
-      </c>
-      <c r="I123" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.41</v>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.989</v>
+        <v>3.251</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.977</v>
+        <v>3.452</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6021,39 +6014,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E124" s="10" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.61</v>
+      </c>
+      <c r="E124" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>527100</v>
+        <v>881300</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="H124" t="n">
-        <v>41.52</v>
-      </c>
-      <c r="I124" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.13</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.923</v>
+        <v>0.63</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.969</v>
+        <v>0.636</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6066,39 +6059,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>2.91</v>
+        <v>1.07</v>
       </c>
       <c r="E125" s="16" t="n">
-        <v>-0.0102</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>525000</v>
+        <v>865800</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.43</v>
+        <v>0.1</v>
       </c>
       <c r="H125" t="n">
-        <v>27.51</v>
-      </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.36</v>
+      </c>
+      <c r="I125" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>3.036</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>3.136</v>
+        <v>0.783</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6111,45 +6104,1215 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>TAKAFUL</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.63</v>
+        <v>2.89</v>
       </c>
       <c r="E126" s="16" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.017</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>516200</v>
+        <v>852200</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.37</v>
+        <v>0.7</v>
       </c>
       <c r="H126" t="n">
-        <v>45.79</v>
-      </c>
-      <c r="I126" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.06</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.634</v>
+        <v>3.034</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.629</v>
+        <v>3.136</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>IHH</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E127" s="16" t="n">
+        <v>-0.0166</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>844500</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H127" t="n">
+        <v>39.45</v>
+      </c>
+      <c r="I127" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>7.869</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>8.057</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="14" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>811400</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H128" t="n">
+        <v>45.44</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="n">
+        <v>1.262</v>
+      </c>
+      <c r="K128" s="9" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="14" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E129" s="16" t="n">
+        <v>-0.004500000000000001</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>803400</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H129" t="n">
+        <v>30.07</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="n">
+        <v>4.639</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>4.942</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="14" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>IOICORP</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="E130" s="16" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>767700</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H130" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>4.602</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>762600</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H131" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>1.153</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="14" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>-0.0207</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>742100</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H132" t="n">
+        <v>78.34999999999999</v>
+      </c>
+      <c r="I132" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>2.016</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>739800</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H133" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="14" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E134" s="16" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>719200</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H134" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="K134" s="9" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>713700</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H135" t="n">
+        <v>57.35</v>
+      </c>
+      <c r="I135" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>2.805</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>2.716</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="14" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>0.005500000000000001</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>707200</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H136" t="n">
+        <v>41.52</v>
+      </c>
+      <c r="I136" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E137" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H137" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K137" s="9" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="14" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="E138" s="16" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>680700</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H138" t="n">
+        <v>61.58</v>
+      </c>
+      <c r="I138" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="n">
+        <v>3.802</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>3.459</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E139" s="16" t="n">
+        <v>-0.0217</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>650000</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H139" t="n">
+        <v>38.77</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="n">
+        <v>1.879</v>
+      </c>
+      <c r="K139" s="9" t="n">
+        <v>1.955</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="14" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E140" s="16" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>649600</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H140" t="n">
+        <v>37.36</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E141" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>649300</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H141" t="n">
+        <v>35.68</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="K141" s="9" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="14" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E142" s="16" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>606300</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H142" t="n">
+        <v>45.79</v>
+      </c>
+      <c r="I142" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E143" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>578500</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H143" t="n">
+        <v>37.69</v>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="K143" s="9" t="n">
+        <v>2.061</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="14" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E144" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>575100</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H144" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="I144" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>3565</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>WCEHB</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="E145" s="16" t="n">
+        <v>-0.006999999999999999</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>565500</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H145" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="14" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>556100</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H146" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="I146" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E147" s="16" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>544500</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H147" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="I147" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K147" s="9" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="14" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E148" s="16" t="n">
+        <v>-0.0117</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>539600</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H148" t="n">
+        <v>30.61</v>
+      </c>
+      <c r="I148" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>2.769</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>532500</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H149" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n">
+        <v>1.354</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E150" s="16" t="n">
+        <v>-0.0223</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>531700</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H150" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="I150" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n">
+        <v>2.671</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>2.844</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>4863</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>TM</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="E151" s="16" t="n">
+        <v>-0.0125</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>513300</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H151" t="n">
+        <v>52.34</v>
+      </c>
+      <c r="I151" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="n">
+        <v>7.888</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>7.818</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="14" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>0351</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>LSH</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>513000</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H152" t="n">
+        <v>55.34</v>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>1.601</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M126"/>
+  <autoFilter ref="A1:M152"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-01/bursa-report-2026-10-01.xlsx
+++ b/docs/downloads/2026-10-01/bursa-report-2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-01" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-01'!$A$1:$M$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-01'!$A$1:$M$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M152"/>
+  <dimension ref="A1:M192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -557,95 +557,103 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>3995000</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>62.29</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多，现价0.55高于50日均线0.473，RSI 62.29偏强但未超买，信号可靠性中等偏正面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>1287</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>EXSIMHB</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>1356100</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="n">
+      <c r="D3" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>1391500</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>64.61</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
         <v>0.497</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K3" s="3" t="n">
         <v>0.468</v>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>🎯 SAR 转多</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr">
-        <is>
-          <t>SAR转多，现价0.505高于50日均线0.468，RSI 61.7偏强但未超买，信号可靠性中等偏正面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>0.0313</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>95340400</v>
-      </c>
-      <c r="G3" s="12" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="H3" t="n">
-        <v>21.74</v>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>0.246</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="14" t="inlineStr"/>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多，现价0.51高于50日均线0.468，RSI 64.61接近超买区，信号偏积极但需留意短线过热。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -655,39 +663,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.29</v>
+        <v>0.165</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.0357</v>
+        <v>0.0313</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>86551100</v>
+        <v>109068200</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>2.98</v>
+        <v>0.22</v>
       </c>
       <c r="H4" t="n">
-        <v>73.68000000000001</v>
-      </c>
-      <c r="I4" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.74</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.242</v>
+        <v>0.246</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.234</v>
+        <v>0.46</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -700,28 +708,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>-0.0244</v>
+        <v>0.29</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>72706200</v>
+        <v>101232900</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>1.37</v>
+        <v>3.49</v>
       </c>
       <c r="H5" t="n">
-        <v>78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
@@ -729,10 +737,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.16</v>
+        <v>0.242</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.123</v>
+        <v>0.234</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -745,31 +753,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0475.KL</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E6" s="17" t="n">
-        <v>0</v>
+        <v>0.2</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>55583400</v>
-      </c>
-      <c r="G6" s="12" t="n"/>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="n"/>
-      <c r="K6" s="9" t="n"/>
+        <v>74251800</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>78</v>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.123</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
     </row>
@@ -781,40 +798,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>0475.KL</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>0.0412</v>
+        <v>0.22</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>34663900</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="H7" t="n">
-        <v>62.49</v>
-      </c>
-      <c r="I7" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>0.473</v>
-      </c>
-      <c r="K7" s="9" t="n">
-        <v>0.472</v>
-      </c>
+        <v>58044300</v>
+      </c>
+      <c r="G7" s="12" t="n"/>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="n"/>
+      <c r="K7" s="9" t="n"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
     </row>
@@ -826,28 +834,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>5.22</v>
+        <v>0.505</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.0077</v>
+        <v>0.0412</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>20515700</v>
+        <v>38825500</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.9</v>
+        <v>1.67</v>
       </c>
       <c r="H8" t="n">
-        <v>77</v>
+        <v>62.49</v>
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
@@ -855,10 +863,10 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>4.846</v>
+        <v>0.473</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>4.566</v>
+        <v>0.472</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -871,39 +879,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0145</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TFP</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>-0.2727</v>
+        <v>0.125</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.3889</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>19755100</v>
+        <v>26088900</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>5.09</v>
+        <v>32.91</v>
       </c>
       <c r="H9" t="n">
-        <v>28.04</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.25</v>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.06</v>
+        <v>0.092</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -916,39 +924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ASTRO</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>0</v>
+        <v>5.2</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>18081400</v>
+        <v>23502200</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>14.99</v>
+        <v>1.03</v>
       </c>
       <c r="H10" t="n">
-        <v>44.56</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.45999999999999</v>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.058</v>
+        <v>4.844</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.06</v>
+        <v>4.566</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -961,39 +969,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>0145</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>TFP</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0.2222</v>
+        <v>0.045</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>-0.1818</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>16789800</v>
+        <v>19999100</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>21.18</v>
+        <v>5.15</v>
       </c>
       <c r="H11" t="n">
-        <v>69.81</v>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.84</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.091</v>
+        <v>0.061</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1006,33 +1014,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>ASTRO</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0.0435</v>
+        <v>0.055</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>16290100</v>
+        <v>18424400</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.52</v>
+        <v>15.28</v>
+      </c>
+      <c r="H12" t="n">
+        <v>44.56</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n"/>
+      <c r="J12" s="9" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.06</v>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
     </row>
@@ -1044,40 +1059,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0.0225</v>
+        <v>0.115</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>16066500</v>
+        <v>17608900</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H13" t="n">
-        <v>53.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J13" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="K13" s="9" t="n">
-        <v>0.415</v>
-      </c>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="9" t="n"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
     </row>
@@ -1089,39 +1097,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.0423</v>
+        <v>0.0337</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>13323200</v>
+        <v>17033700</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="H14" t="n">
-        <v>71.03</v>
-      </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.57</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.335</v>
+        <v>0.45</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.313</v>
+        <v>0.415</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1134,28 +1142,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>-0.0177</v>
+        <v>0.375</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0.0563</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>12347000</v>
+        <v>14105400</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="H15" t="n">
-        <v>57.43</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
@@ -1163,10 +1171,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.535</v>
+        <v>0.335</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.489</v>
+        <v>0.313</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1179,39 +1187,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.285</v>
+        <v>0.555</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>-0.0172</v>
+        <v>-0.0177</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>11317500</v>
+        <v>13297100</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1.6</v>
+        <v>0.87</v>
       </c>
       <c r="H16" t="n">
-        <v>35.15</v>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.43</v>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.295</v>
+        <v>0.535</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.31</v>
+        <v>0.489</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1224,28 +1232,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.155</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>10739000</v>
+        <v>12290900</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="H17" t="n">
-        <v>74.09999999999999</v>
+        <v>49.88</v>
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
@@ -1253,10 +1261,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.157</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.496</v>
+        <v>0.148</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1269,39 +1277,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.205</v>
+        <v>0.61</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>0.0149</v>
+        <v>0.0167</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>7890700</v>
+        <v>11520500</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="H18" t="n">
-        <v>60.58</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.05</v>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.196</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.18</v>
+        <v>0.496</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1314,39 +1322,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.385</v>
+        <v>0.285</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>-0.0128</v>
+        <v>-0.0172</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>7673400</v>
+        <v>11437900</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.17</v>
+        <v>1.62</v>
       </c>
       <c r="H19" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.15</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.337</v>
+        <v>0.295</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.203</v>
+        <v>0.31</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1374,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>7628900</v>
+        <v>10785900</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.57</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H20" t="n">
         <v>48.12</v>
@@ -1404,39 +1412,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.385</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>-0.0128</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>7343100</v>
+        <v>10306700</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.32</v>
+        <v>0.23</v>
       </c>
       <c r="H21" t="n">
-        <v>56.77</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.7</v>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1.745</v>
+        <v>0.337</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1.562</v>
+        <v>0.203</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1449,28 +1457,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
         <v>0.155</v>
       </c>
-      <c r="E22" s="16" t="n">
-        <v>-0.0313</v>
+      <c r="E22" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>6317800</v>
+        <v>9758000</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.16</v>
+        <v>0.39</v>
       </c>
       <c r="H22" t="n">
-        <v>49.88</v>
+        <v>44.71</v>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
@@ -1478,10 +1486,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.157</v>
+        <v>0.155</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.148</v>
+        <v>0.158</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1494,28 +1502,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>-0.0062</v>
+        <v>1.78</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0.0114</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>6131000</v>
+        <v>8927600</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="H23" t="n">
-        <v>47.32</v>
+        <v>56.77</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
@@ -1523,10 +1531,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.8090000000000001</v>
+        <v>1.745</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>1.562</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1539,28 +1547,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HUBLINE</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0</v>
+        <v>0.2</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>5825900</v>
+        <v>8735700</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>4.33</v>
+        <v>0.4</v>
       </c>
       <c r="H24" t="n">
-        <v>45.42</v>
+        <v>56.72</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -1568,10 +1576,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.032</v>
+        <v>0.196</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.032</v>
+        <v>0.18</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1584,39 +1592,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SENDAI</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>0.0179</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>5407400</v>
+        <v>8569900</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>2.93</v>
+        <v>0.59</v>
       </c>
       <c r="H25" t="n">
-        <v>64.17</v>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.2</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.263</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.268</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1629,28 +1637,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0.0167</v>
+        <v>0.865</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>5280400</v>
+        <v>8354500</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="H26" t="n">
-        <v>51.26</v>
+        <v>46.8</v>
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
@@ -1658,10 +1666,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.607</v>
+        <v>0.868</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.607</v>
+        <v>0.87</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1674,39 +1682,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>-0.0588</v>
+        <v>0.305</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>5235700</v>
+        <v>8268700</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>1.63</v>
+        <v>0.42</v>
       </c>
       <c r="H27" t="n">
-        <v>58.05</v>
-      </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.62</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.152</v>
+        <v>0.303</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.141</v>
+        <v>0.292</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1719,28 +1727,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>1.2</v>
+        <v>0.61</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0167</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>5085400</v>
+        <v>7469400</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1.34</v>
+        <v>0.72</v>
       </c>
       <c r="H28" t="n">
-        <v>66.34</v>
+        <v>51.26</v>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
@@ -1748,10 +1756,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1.126</v>
+        <v>0.607</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>1.029</v>
+        <v>0.607</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1764,28 +1772,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>0</v>
+        <v>9.91</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>5079000</v>
+        <v>7372800</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>2.48</v>
+        <v>0.6</v>
       </c>
       <c r="H29" t="n">
-        <v>49.25</v>
+        <v>33.15</v>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
@@ -1793,10 +1801,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.295</v>
+        <v>10.12</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.296</v>
+        <v>10.278</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1809,39 +1817,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.52</v>
+        <v>0.375</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>-0.0095</v>
+        <v>-0.0132</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4909500</v>
+        <v>6419400</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.13</v>
+        <v>0.59</v>
       </c>
       <c r="H30" t="n">
-        <v>28.26</v>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.49</v>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.604</v>
+        <v>0.376</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.372</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1854,39 +1862,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>SENDAI</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="E31" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>4766800</v>
+        <v>6377400</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.64</v>
+        <v>3.46</v>
       </c>
       <c r="H31" t="n">
-        <v>31.89</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.92</v>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.348</v>
+        <v>0.263</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.349</v>
+        <v>0.268</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1899,28 +1907,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>HUBLINE</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.305</v>
+        <v>0.03</v>
       </c>
       <c r="E32" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>4422700</v>
+        <v>5825900</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.22</v>
+        <v>4.33</v>
       </c>
       <c r="H32" t="n">
-        <v>53.62</v>
+        <v>45.42</v>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
@@ -1928,10 +1936,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.303</v>
+        <v>0.032</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.292</v>
+        <v>0.032</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1944,39 +1952,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>-0.0048</v>
+        <v>1.19</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>4337700</v>
+        <v>5563700</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.25</v>
+        <v>1.46</v>
       </c>
       <c r="H33" t="n">
-        <v>44.66</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.23999999999999</v>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>2.113</v>
+        <v>1.125</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>2.069</v>
+        <v>1.028</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1989,39 +1997,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E34" s="17" t="n">
-        <v>0</v>
+        <v>0.52</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>-0.0095</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>4295700</v>
+        <v>5470600</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="H34" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="I34" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.26</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.868</v>
+        <v>0.604</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.87</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2034,39 +2042,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0.0281</v>
+        <v>0.165</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>-0.0294</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>4255900</v>
+        <v>5335800</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.34</v>
+        <v>1.67</v>
       </c>
       <c r="H35" t="n">
-        <v>56.05</v>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.21</v>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>3.604</v>
+        <v>0.152</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>2.5</v>
+        <v>0.141</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2079,28 +2087,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>-0.002</v>
+        <v>0.365</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>4231500</v>
+        <v>5308200</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.35</v>
+        <v>0.85</v>
       </c>
       <c r="H36" t="n">
-        <v>35.89</v>
+        <v>48.24</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
@@ -2108,10 +2116,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>10.125</v>
+        <v>0.367</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>10.28</v>
+        <v>0.367</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2124,39 +2132,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>-0.062</v>
+        <v>0.3</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4136000</v>
+        <v>5080100</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>2.78</v>
+        <v>2.48</v>
       </c>
       <c r="H37" t="n">
-        <v>38.75</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.73</v>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>1.275</v>
+        <v>0.295</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>1.332</v>
+        <v>0.296</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2169,39 +2177,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>0</v>
+        <v>0.785</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>-0.0063</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>4058200</v>
+        <v>5040100</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.65</v>
+        <v>0.46</v>
       </c>
       <c r="H38" t="n">
-        <v>48.24</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.78</v>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.367</v>
+        <v>0.732</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.367</v>
+        <v>0.694</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2214,39 +2222,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0.0857</v>
+        <v>0.33</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>3968300</v>
+        <v>5008900</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="H39" t="n">
-        <v>67.62</v>
-      </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.89</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.165</v>
+        <v>0.348</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.165</v>
+        <v>0.349</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2259,39 +2267,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.445</v>
+        <v>2.08</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>3951000</v>
+        <v>4909600</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>1.7</v>
+        <v>0.28</v>
       </c>
       <c r="H40" t="n">
-        <v>76.12</v>
-      </c>
-      <c r="I40" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.91</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.388</v>
+        <v>2.114</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.35</v>
+        <v>2.069</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2304,39 +2312,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>1.14</v>
+        <v>0.73</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>-0.0806</v>
+        <v>-0.0135</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3892300</v>
+        <v>4907400</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.61</v>
+        <v>1.12</v>
       </c>
       <c r="H41" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="I41" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.31</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.967</v>
+        <v>0.782</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.766</v>
+        <v>0.838</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2364,10 +2372,10 @@
         <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>3763200</v>
+        <v>4721400</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.58</v>
+        <v>0.73</v>
       </c>
       <c r="H42" t="n">
         <v>43.51</v>
@@ -2394,39 +2402,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>0.0141</v>
+        <v>0.215</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3560900</v>
+        <v>4721300</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="H43" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="I43" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.71</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.335</v>
+        <v>0.232</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.315</v>
+        <v>0.246</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2439,39 +2447,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.73</v>
+        <v>1.18</v>
       </c>
       <c r="E44" s="16" t="n">
-        <v>-0.0135</v>
+        <v>-0.0484</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>3540400</v>
+        <v>4714200</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="H44" t="n">
-        <v>30.31</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.5</v>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.782</v>
+        <v>0.97</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.838</v>
+        <v>0.767</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2484,28 +2492,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.375</v>
+        <v>0.435</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>-0.0132</v>
+        <v>-0.0225</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3511300</v>
+        <v>4591600</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.32</v>
+        <v>1.97</v>
       </c>
       <c r="H45" t="n">
-        <v>50.49</v>
+        <v>71</v>
       </c>
       <c r="I45" s="15" t="inlineStr">
         <is>
@@ -2513,10 +2521,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.376</v>
+        <v>0.387</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.372</v>
+        <v>0.349</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2529,28 +2537,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>3.07</v>
+        <v>0.19</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3123500</v>
+        <v>4588300</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="H46" t="n">
-        <v>60.23</v>
+        <v>67.62</v>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
@@ -2558,10 +2566,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>2.906</v>
+        <v>0.165</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.719</v>
+        <v>0.165</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2574,39 +2582,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E47" s="17" t="n">
-        <v>0</v>
+        <v>3.63</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0.0197</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3060700</v>
+        <v>4587100</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.28</v>
+        <v>0.37</v>
       </c>
       <c r="H47" t="n">
-        <v>61.75</v>
-      </c>
-      <c r="I47" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.54</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.733</v>
+        <v>3.601</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.694</v>
+        <v>2.5</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2619,28 +2627,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>1.08</v>
+        <v>4.67</v>
       </c>
       <c r="E48" s="16" t="n">
-        <v>-0.027</v>
+        <v>-0.0064</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2988400</v>
+        <v>4473700</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.43</v>
+        <v>0.26</v>
       </c>
       <c r="H48" t="n">
-        <v>38.71</v>
+        <v>29.36</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2648,10 +2656,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>1.161</v>
+        <v>4.806</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>1.15</v>
+        <v>4.937</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2664,39 +2672,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>0</v>
+        <v>1.22</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>-0.05429999999999999</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2988100</v>
+        <v>4322500</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.53</v>
+        <v>2.9</v>
       </c>
       <c r="H49" t="n">
-        <v>57.09</v>
-      </c>
-      <c r="I49" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.82</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.406</v>
+        <v>1.276</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.404</v>
+        <v>1.332</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2709,39 +2717,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>4.67</v>
+        <v>4.3</v>
       </c>
       <c r="E50" s="16" t="n">
-        <v>-0.0064</v>
+        <v>-0.0138</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>2973900</v>
+        <v>4180500</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.17</v>
+        <v>0.63</v>
       </c>
       <c r="H50" t="n">
-        <v>29.36</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.01000000000001</v>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>4.806</v>
+        <v>3.76</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>4.937</v>
+        <v>3.304</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2754,28 +2762,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.79</v>
+        <v>0.245</v>
       </c>
       <c r="E51" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>2931500</v>
+        <v>4089000</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.47</v>
+        <v>0.14</v>
       </c>
       <c r="H51" t="n">
-        <v>64.37</v>
+        <v>33.55</v>
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
@@ -2783,10 +2791,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.77</v>
+        <v>0.268</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.756</v>
+        <v>0.32</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2814,10 +2822,10 @@
         <v>-0.0044</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>2675800</v>
+        <v>4073800</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="H52" t="n">
         <v>49.98</v>
@@ -2844,39 +2852,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0.0156</v>
+        <v>1.09</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>-0.018</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2462300</v>
+        <v>3801600</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.25</v>
+        <v>0.55</v>
       </c>
       <c r="H53" t="n">
-        <v>56.16</v>
-      </c>
-      <c r="I53" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.73</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.636</v>
+        <v>1.162</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.583</v>
+        <v>1.15</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2889,40 +2897,33 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E54" s="16" t="n">
-        <v>-0.0196</v>
+        <v>0.295</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0.0536</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2442900</v>
+        <v>3752600</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H54" t="n">
-        <v>48.34</v>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J54" s="9" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="K54" s="9" t="n">
-        <v>0.224</v>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="I54" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="n"/>
+      <c r="K54" s="9" t="n"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
     </row>
@@ -2934,39 +2935,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0.0233</v>
+        <v>0.19</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2384200</v>
+        <v>3739300</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="H55" t="n">
-        <v>54.54</v>
-      </c>
-      <c r="I55" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.53</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.215</v>
+        <v>0.194</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.213</v>
+        <v>0.197</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2979,39 +2980,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E56" s="17" t="n">
-        <v>0</v>
+        <v>0.36</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2381900</v>
+        <v>3691800</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.37</v>
+        <v>0.48</v>
       </c>
       <c r="H56" t="n">
-        <v>30.06</v>
-      </c>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.09999999999999</v>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.55</v>
+        <v>0.335</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.584</v>
+        <v>0.315</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3024,28 +3025,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.34</v>
+        <v>0.165</v>
       </c>
       <c r="E57" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2354800</v>
+        <v>3571600</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>1.77</v>
+        <v>0.16</v>
       </c>
       <c r="H57" t="n">
-        <v>31.63</v>
+        <v>36.1</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -3053,10 +3054,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.357</v>
+        <v>0.177</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.391</v>
+        <v>0.212</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3069,28 +3070,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.295</v>
+        <v>0.79</v>
       </c>
       <c r="E58" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2317500</v>
+        <v>3358600</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.36</v>
+        <v>0.54</v>
       </c>
       <c r="H58" t="n">
-        <v>66.25</v>
+        <v>64.37</v>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
@@ -3098,10 +3099,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.28</v>
+        <v>0.77</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.272</v>
+        <v>0.756</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3114,28 +3115,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.51</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2285700</v>
+        <v>3338500</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.58</v>
+        <v>0.51</v>
       </c>
       <c r="H59" t="n">
-        <v>58.93</v>
+        <v>28.82</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3143,10 +3144,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.516</v>
+        <v>0.55</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.472</v>
+        <v>0.584</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3159,39 +3160,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E60" s="17" t="n">
-        <v>0</v>
+        <v>0.325</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0.0317</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2207800</v>
+        <v>3301700</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>10.38</v>
+        <v>0.59</v>
       </c>
       <c r="H60" t="n">
-        <v>57.18</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.5</v>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.44</v>
+        <v>0.319</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.434</v>
+        <v>0.337</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3204,28 +3205,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.425</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2166300</v>
+        <v>3258400</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.79</v>
+        <v>0.58</v>
       </c>
       <c r="H61" t="n">
-        <v>76.33</v>
+        <v>57.09</v>
       </c>
       <c r="I61" s="15" t="inlineStr">
         <is>
@@ -3233,10 +3234,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.425</v>
+        <v>0.406</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.415</v>
+        <v>0.404</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3249,39 +3250,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E62" s="17" t="n">
-        <v>0</v>
+        <v>5.83</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2159000</v>
+        <v>3231900</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="H62" t="n">
-        <v>44.18</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.28</v>
+      </c>
+      <c r="I62" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>1.356</v>
+        <v>5.692</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>1.298</v>
+        <v>5.191</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3294,28 +3295,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E63" s="16" t="n">
-        <v>-0.0036</v>
+        <v>0.295</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2112700</v>
+        <v>3219400</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.5</v>
+        <v>0.19</v>
       </c>
       <c r="H63" t="n">
-        <v>80.03</v>
+        <v>54.28</v>
       </c>
       <c r="I63" s="15" t="inlineStr">
         <is>
@@ -3323,10 +3324,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>2.535</v>
+        <v>0.287</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>2.18</v>
+        <v>0.277</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3339,39 +3340,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="E64" s="16" t="n">
-        <v>-0.009300000000000001</v>
+        <v>3.09</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0.0164</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2089800</v>
+        <v>3212200</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.2</v>
+        <v>0.89</v>
       </c>
       <c r="H64" t="n">
-        <v>24.11</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.03</v>
+      </c>
+      <c r="I64" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>7.849</v>
+        <v>2.908</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>8.212999999999999</v>
+        <v>2.72</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3384,33 +3385,40 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.475</v>
+        <v>0.44</v>
       </c>
       <c r="E65" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2081400</v>
+        <v>3207900</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I65" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J65" s="9" t="n"/>
-      <c r="K65" s="9" t="n"/>
+        <v>15.08</v>
+      </c>
+      <c r="H65" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K65" s="9" t="n">
+        <v>0.434</v>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
     </row>
@@ -3422,28 +3430,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0.004</v>
+        <v>7.44</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2061200</v>
+        <v>3138100</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="H66" t="n">
-        <v>46.76</v>
+        <v>24.35</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3451,10 +3459,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>2.566</v>
+        <v>7.85</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>2.456</v>
+        <v>8.212999999999999</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3467,39 +3475,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="E67" s="16" t="n">
-        <v>-0.0102</v>
+        <v>2.52</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>0.008</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2010600</v>
+        <v>3036900</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="H67" t="n">
-        <v>59.29</v>
-      </c>
-      <c r="I67" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.59</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>5.69</v>
+        <v>2.567</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>5.191</v>
+        <v>2.456</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3512,28 +3520,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>6.98</v>
+        <v>2.88</v>
       </c>
       <c r="E68" s="16" t="n">
-        <v>-0.0127</v>
+        <v>-0.0103</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1996000</v>
+        <v>2955800</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.58</v>
+        <v>0.2</v>
       </c>
       <c r="H68" t="n">
-        <v>58.93</v>
+        <v>63.41</v>
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
@@ -3541,10 +3549,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>6.675</v>
+        <v>2.8</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>6.554</v>
+        <v>2.659</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3557,39 +3565,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="E69" s="16" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1981500</v>
+        <v>2904000</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.3</v>
+        <v>0.85</v>
       </c>
       <c r="H69" t="n">
-        <v>45.42</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.51</v>
+      </c>
+      <c r="I69" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.522</v>
+        <v>6.677</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.532</v>
+        <v>6.554</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3602,28 +3610,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1954800</v>
+        <v>2889300</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="H70" t="n">
-        <v>52.59</v>
+        <v>68.7</v>
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
@@ -3631,10 +3639,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.286</v>
+        <v>0.497</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.277</v>
+        <v>0.415</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3647,39 +3655,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.245</v>
+        <v>1.3</v>
       </c>
       <c r="E71" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1922500</v>
+        <v>2839300</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="H71" t="n">
-        <v>33.55</v>
-      </c>
-      <c r="I71" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.18</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.268</v>
+        <v>1.356</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.32</v>
+        <v>1.298</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3692,28 +3700,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="E72" s="16" t="n">
-        <v>-0.0265</v>
+        <v>0.65</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1903600</v>
+        <v>2807700</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.6</v>
+        <v>0.28</v>
       </c>
       <c r="H72" t="n">
-        <v>76.40000000000001</v>
+        <v>56.16</v>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
@@ -3721,10 +3729,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>2.409</v>
+        <v>0.636</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>1.862</v>
+        <v>0.583</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3746,19 +3754,19 @@
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>0</v>
+        <v>0.905</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>-0.0163</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1830100</v>
+        <v>2708200</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.37</v>
+        <v>0.54</v>
       </c>
       <c r="H73" t="n">
-        <v>63.45</v>
+        <v>57.18</v>
       </c>
       <c r="I73" s="15" t="inlineStr">
         <is>
@@ -3766,7 +3774,7 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.895</v>
+        <v>0.893</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>0.854</v>
@@ -3782,28 +3790,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E74" s="16" t="n">
-        <v>-0.0173</v>
+        <v>0.22</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1825100</v>
+        <v>2626300</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.34</v>
+        <v>0.48</v>
       </c>
       <c r="H74" t="n">
-        <v>41.1</v>
+        <v>54.54</v>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
@@ -3811,10 +3819,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.758</v>
+        <v>0.215</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1.793</v>
+        <v>0.213</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3827,28 +3835,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>0.009000000000000001</v>
+        <v>2.92</v>
+      </c>
+      <c r="E75" s="16" t="n">
+        <v>-0.0034</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1815200</v>
+        <v>2604200</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.12</v>
+        <v>0.29</v>
       </c>
       <c r="H75" t="n">
-        <v>68.7</v>
+        <v>63.71</v>
       </c>
       <c r="I75" s="15" t="inlineStr">
         <is>
@@ -3856,10 +3864,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.497</v>
+        <v>2.705</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.415</v>
+        <v>2.534</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3872,33 +3880,40 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>0.07139999999999999</v>
+        <v>0.25</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1807200</v>
+        <v>2602200</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I76" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J76" s="9" t="n"/>
-      <c r="K76" s="9" t="n"/>
+        <v>0.31</v>
+      </c>
+      <c r="H76" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>0.224</v>
+      </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
     </row>
@@ -3910,28 +3925,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>7.77</v>
+        <v>2.73</v>
       </c>
       <c r="E77" s="16" t="n">
-        <v>-0.0026</v>
+        <v>-0.0073</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1789000</v>
+        <v>2537100</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.14</v>
+        <v>0.6</v>
       </c>
       <c r="H77" t="n">
-        <v>49.28</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
@@ -3939,10 +3954,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>7.799</v>
+        <v>2.534</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>7.747</v>
+        <v>2.179</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3955,28 +3970,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>6.75</v>
+        <v>0.3</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.0169</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1784200</v>
+        <v>2508500</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="H78" t="n">
-        <v>49.04</v>
+        <v>68.88</v>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
@@ -3984,10 +3999,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>6.758</v>
+        <v>0.28</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>6.83</v>
+        <v>0.272</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4000,36 +4015,40 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.265</v>
+        <v>0.23</v>
       </c>
       <c r="E79" s="16" t="n">
-        <v>-0.0185</v>
+        <v>-0.0612</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1782500</v>
+        <v>2416200</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.1</v>
+        <v>0.77</v>
       </c>
       <c r="H79" t="n">
-        <v>15.91</v>
+        <v>40.24</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J79" s="9" t="n"/>
-      <c r="K79" s="9" t="n"/>
+      <c r="J79" s="9" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="K79" s="9" t="n">
+        <v>0.253</v>
+      </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
     </row>
@@ -4041,39 +4060,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>0.004099999999999999</v>
+        <v>4.07</v>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1777100</v>
+        <v>2398200</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="H80" t="n">
-        <v>56.42</v>
-      </c>
-      <c r="I80" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.93</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>2.449</v>
+        <v>4.476</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>2.304</v>
+        <v>4.51</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4086,28 +4105,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.65</v>
+        <v>0.515</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0198</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1769600</v>
+        <v>2383700</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.54</v>
+        <v>0.86</v>
       </c>
       <c r="H81" t="n">
-        <v>61.18</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="I81" s="15" t="inlineStr">
         <is>
@@ -4115,10 +4134,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.608</v>
+        <v>0.426</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.61</v>
+        <v>0.415</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4131,39 +4150,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="E82" s="16" t="n">
-        <v>-0.0183</v>
+        <v>0.34</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1696000</v>
+        <v>2380400</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.26</v>
+        <v>1.79</v>
       </c>
       <c r="H82" t="n">
-        <v>73.02</v>
-      </c>
-      <c r="I82" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.63</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>3.759</v>
+        <v>0.357</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>3.304</v>
+        <v>0.391</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4176,40 +4195,33 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E83" s="16" t="n">
-        <v>-0.0034</v>
+        <v>0.475</v>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1660200</v>
+        <v>2362400</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H83" t="n">
-        <v>63.71</v>
+        <v>0.14</v>
       </c>
       <c r="I83" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J83" s="9" t="n">
-        <v>2.705</v>
-      </c>
-      <c r="K83" s="9" t="n">
-        <v>2.534</v>
-      </c>
+      <c r="J83" s="9" t="n"/>
+      <c r="K83" s="9" t="n"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
     </row>
@@ -4221,39 +4233,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.735</v>
+        <v>0.255</v>
       </c>
       <c r="E84" s="16" t="n">
-        <v>-0.0068</v>
+        <v>-0.0377</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1633400</v>
+        <v>2318900</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.04</v>
+        <v>0.78</v>
       </c>
       <c r="H84" t="n">
-        <v>51.99</v>
-      </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.37</v>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.736</v>
+        <v>0.234</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.211</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4266,39 +4278,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>0.015</v>
+        <v>1.61</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>-0.0301</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1562300</v>
+        <v>2316100</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="H85" t="n">
-        <v>49.33</v>
-      </c>
-      <c r="I85" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.31</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.68</v>
+        <v>1.706</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.666</v>
+        <v>1.824</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4311,28 +4323,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.255</v>
+        <v>1.46</v>
       </c>
       <c r="E86" s="16" t="n">
-        <v>-0.0377</v>
+        <v>-0.0068</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1528900</v>
+        <v>2277800</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="H86" t="n">
-        <v>64.37</v>
+        <v>46.54</v>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
@@ -4340,10 +4352,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.234</v>
+        <v>1.47</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.211</v>
+        <v>1.471</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4356,39 +4368,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.22</v>
+        <v>1.7</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>-0.0222</v>
+        <v>-0.0173</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1520900</v>
+        <v>2262800</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.6</v>
+        <v>0.42</v>
       </c>
       <c r="H87" t="n">
-        <v>24.44</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.1</v>
+      </c>
+      <c r="I87" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.239</v>
+        <v>1.758</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.242</v>
+        <v>1.793</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4401,39 +4413,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IWCITY</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>0.0732</v>
+        <v>2.45</v>
+      </c>
+      <c r="E88" s="16" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1513600</v>
+        <v>2234200</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>1.73</v>
+        <v>0.14</v>
       </c>
       <c r="H88" t="n">
-        <v>53.96</v>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.86</v>
+      </c>
+      <c r="I88" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.214</v>
+        <v>2.447</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.224</v>
+        <v>2.304</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4446,28 +4458,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0396</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ADNEX</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>0.0118</v>
+        <v>2.91</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>-0.0364</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1498100</v>
+        <v>2197000</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>3.46</v>
+        <v>0.7</v>
       </c>
       <c r="H89" t="n">
-        <v>56.98</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="I89" s="15" t="inlineStr">
         <is>
@@ -4475,10 +4487,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.418</v>
+        <v>2.406</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.415</v>
+        <v>1.862</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4491,28 +4503,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>1.1</v>
+        <v>6.75</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>0.028</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1497100</v>
+        <v>2169500</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H90" t="n">
-        <v>74.3</v>
+        <v>49.04</v>
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
@@ -4520,10 +4532,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>1.003</v>
+        <v>6.758</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.831</v>
+        <v>6.83</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4536,28 +4548,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>0.0136</v>
+        <v>7.76</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>-0.0039</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1489400</v>
+        <v>2164400</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="H91" t="n">
-        <v>63.77</v>
+        <v>48.77</v>
       </c>
       <c r="I91" s="15" t="inlineStr">
         <is>
@@ -4565,10 +4577,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.697</v>
+        <v>7.798</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.624</v>
+        <v>7.747</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4581,39 +4593,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>0.0442</v>
+        <v>0.51</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1456000</v>
+        <v>2125200</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.5</v>
+        <v>0.32</v>
       </c>
       <c r="H92" t="n">
-        <v>55.57</v>
-      </c>
-      <c r="I92" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.42</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.571</v>
+        <v>0.522</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.575</v>
+        <v>0.532</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4626,28 +4638,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>4.08</v>
+        <v>3.05</v>
       </c>
       <c r="E93" s="16" t="n">
-        <v>-0.0239</v>
+        <v>-0.0317</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1449300</v>
+        <v>2083700</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.18</v>
+        <v>0.59</v>
       </c>
       <c r="H93" t="n">
-        <v>36.15</v>
+        <v>25.41</v>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
@@ -4655,10 +4667,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>4.477</v>
+        <v>3.251</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>4.51</v>
+        <v>3.452</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4671,28 +4683,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E94" s="17" t="n">
-        <v>0</v>
+        <v>0.735</v>
+      </c>
+      <c r="E94" s="16" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1440300</v>
+        <v>2047800</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="H94" t="n">
-        <v>42.45</v>
+        <v>51.99</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -4700,10 +4712,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.407</v>
+        <v>0.736</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.411</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4716,39 +4728,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>0.0072</v>
+        <v>1.24</v>
+      </c>
+      <c r="E95" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1414300</v>
+        <v>2010200</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.48</v>
+        <v>0.35</v>
       </c>
       <c r="H95" t="n">
-        <v>85.89</v>
-      </c>
-      <c r="I95" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.13</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>1.124</v>
+        <v>1.261</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.929</v>
+        <v>1.298</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4761,39 +4773,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E96" s="16" t="n">
-        <v>-0.012</v>
+        <v>0.675</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0.015</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1399000</v>
+        <v>1997500</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="H96" t="n">
-        <v>36.94</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.33</v>
+      </c>
+      <c r="I96" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>1.709</v>
+        <v>0.68</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>1.825</v>
+        <v>0.666</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4806,28 +4818,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.255</v>
+        <v>0.755</v>
       </c>
       <c r="E97" s="16" t="n">
-        <v>-0.0192</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1329300</v>
+        <v>1988400</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.85</v>
+        <v>1.33</v>
       </c>
       <c r="H97" t="n">
-        <v>38.92</v>
+        <v>19.62</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -4835,10 +4847,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.267</v>
+        <v>0.863</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.278</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4851,28 +4863,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>2.88</v>
+        <v>12.9</v>
       </c>
       <c r="E98" s="16" t="n">
-        <v>-0.0103</v>
+        <v>-0.0046</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1318800</v>
+        <v>1906700</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.09</v>
+        <v>0.23</v>
       </c>
       <c r="H98" t="n">
-        <v>63.41</v>
+        <v>37.04</v>
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
@@ -4880,10 +4892,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>2.8</v>
+        <v>13.121</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>2.659</v>
+        <v>13.717</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4896,28 +4908,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>0.0192</v>
+        <v>7.33</v>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1253900</v>
+        <v>1902000</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.38</v>
+        <v>0.27</v>
       </c>
       <c r="H99" t="n">
-        <v>39.68</v>
+        <v>33.67</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -4925,10 +4937,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>5.664</v>
+        <v>7.616</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>5.745</v>
+        <v>7.813</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4941,39 +4953,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0398</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GDGROUP</t>
+          <t>IWCITY</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E100" s="17" t="n">
-        <v>0</v>
+        <v>0.215</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>0.0488</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1248300</v>
+        <v>1896500</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="H100" t="n">
-        <v>53.25</v>
-      </c>
-      <c r="I100" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.91</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.378</v>
+        <v>0.213</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.38</v>
+        <v>0.223</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4986,39 +4998,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>0.0092</v>
+        <v>6.12</v>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>-0.0129</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1235400</v>
+        <v>1848100</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H101" t="n">
-        <v>75.37</v>
-      </c>
-      <c r="I101" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.18</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>1.027</v>
+        <v>6.264</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.868</v>
+        <v>6.462</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5031,40 +5043,36 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E102" s="16" t="n">
-        <v>-0.0097</v>
+        <v>0.27</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1225600</v>
+        <v>1810400</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H102" t="n">
-        <v>42.99</v>
+        <v>16.24</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J102" s="9" t="n">
-        <v>1.068</v>
-      </c>
-      <c r="K102" s="9" t="n">
-        <v>1.025</v>
-      </c>
+      <c r="J102" s="9" t="n"/>
+      <c r="K102" s="9" t="n"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
     </row>
@@ -5076,39 +5084,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MAGMA</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E103" s="16" t="n">
-        <v>-0.0175</v>
+        <v>0.65</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1210300</v>
+        <v>1792800</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>2.16</v>
+        <v>0.54</v>
       </c>
       <c r="H103" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.18</v>
+      </c>
+      <c r="I103" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.288</v>
+        <v>0.608</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.287</v>
+        <v>0.61</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5136,10 +5144,10 @@
         <v>0.02</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1202600</v>
+        <v>1785300</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="H104" t="n">
         <v>40.14</v>
@@ -5166,28 +5174,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.255</v>
+        <v>1.89</v>
       </c>
       <c r="E105" s="16" t="n">
-        <v>-0.0192</v>
+        <v>-0.0258</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1180900</v>
+        <v>1778300</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>1.39</v>
+        <v>0.24</v>
       </c>
       <c r="H105" t="n">
-        <v>37.88</v>
+        <v>37.79</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -5195,10 +5203,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.26</v>
+        <v>1.968</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.265</v>
+        <v>1.97</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5211,39 +5219,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>0</v>
+        <v>1.08</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>-0.0092</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1164900</v>
+        <v>1771800</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.84</v>
+        <v>0.14</v>
       </c>
       <c r="H106" t="n">
-        <v>38.74</v>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.89</v>
+      </c>
+      <c r="I106" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.383</v>
+        <v>1.025</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.391</v>
+        <v>0.868</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5256,28 +5264,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>12.94</v>
-      </c>
-      <c r="E107" s="16" t="n">
-        <v>-0.0015</v>
+        <v>0.735</v>
+      </c>
+      <c r="E107" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1160800</v>
+        <v>1728200</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="H107" t="n">
-        <v>38.11</v>
+        <v>62.32</v>
       </c>
       <c r="I107" s="15" t="inlineStr">
         <is>
@@ -5285,10 +5293,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>13.125</v>
+        <v>0.696</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>13.717</v>
+        <v>0.624</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5301,39 +5309,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.465</v>
+        <v>0.865</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>0.0109</v>
+        <v>0.0058</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1129900</v>
+        <v>1706000</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.34</v>
+        <v>0.57</v>
       </c>
       <c r="H108" t="n">
-        <v>57.92</v>
-      </c>
-      <c r="I108" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.77</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.443</v>
+        <v>0.861</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.438</v>
+        <v>0.856</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5346,28 +5354,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>2.57</v>
+        <v>0.47</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0217</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1115400</v>
+        <v>1694200</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.19</v>
+        <v>0.51</v>
       </c>
       <c r="H109" t="n">
-        <v>50.77</v>
+        <v>59.19</v>
       </c>
       <c r="I109" s="15" t="inlineStr">
         <is>
@@ -5375,10 +5383,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>2.566</v>
+        <v>0.443</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>2.546</v>
+        <v>0.438</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5391,28 +5399,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E110" s="16" t="n">
-        <v>-0.0206</v>
+        <v>1.09</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>0.0187</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1113900</v>
+        <v>1639900</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="H110" t="n">
-        <v>62.71</v>
+        <v>73.41</v>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
@@ -5420,10 +5428,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.456</v>
+        <v>1.002</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.411</v>
+        <v>0.831</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5436,28 +5444,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.865</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E111" s="10" t="n">
-        <v>0.0058</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1099200</v>
+        <v>1634800</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.37</v>
+        <v>0.73</v>
       </c>
       <c r="H111" t="n">
-        <v>55.77</v>
+        <v>48.69</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -5465,10 +5473,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.861</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.856</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5481,39 +5489,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="E112" s="16" t="n">
-        <v>-0.0258</v>
+        <v>0.585</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>0.0354</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1090700</v>
+        <v>1622500</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.15</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H112" t="n">
-        <v>37.79</v>
-      </c>
-      <c r="I112" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.39</v>
+      </c>
+      <c r="I112" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>1.968</v>
+        <v>0.57</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>1.97</v>
+        <v>0.575</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5526,28 +5534,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E113" s="17" t="n">
-        <v>0</v>
+        <v>0.395</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>-0.0125</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1090400</v>
+        <v>1595500</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.28</v>
+        <v>0.14</v>
       </c>
       <c r="H113" t="n">
-        <v>33.33</v>
+        <v>38.9</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -5555,10 +5563,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.582</v>
+        <v>0.407</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.586</v>
+        <v>0.411</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5571,28 +5579,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E114" s="17" t="n">
-        <v>0</v>
+        <v>1.38</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>-0.0072</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1073600</v>
+        <v>1595000</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.19</v>
+        <v>0.54</v>
       </c>
       <c r="H114" t="n">
-        <v>46.36</v>
+        <v>83.83</v>
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
@@ -5600,10 +5608,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.318</v>
+        <v>1.122</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.337</v>
+        <v>0.929</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5616,28 +5624,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E115" s="17" t="n">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+      <c r="E115" s="16" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1043100</v>
+        <v>1566300</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="H115" t="n">
-        <v>39.66</v>
+        <v>24.44</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5645,10 +5653,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>2.978</v>
+        <v>0.239</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>3.036</v>
+        <v>0.242</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5661,39 +5669,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>1.02</v>
+        <v>5.3</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>0.0515</v>
+        <v>0.0192</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1038700</v>
+        <v>1535900</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>1.77</v>
+        <v>0.47</v>
       </c>
       <c r="H116" t="n">
-        <v>62.33</v>
-      </c>
-      <c r="I116" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.68</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.985</v>
+        <v>5.664</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.976</v>
+        <v>5.745</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5706,33 +5714,40 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0396</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>ADNEX</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E117" s="17" t="n">
-        <v>0</v>
+        <v>0.435</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0.0235</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1035000</v>
+        <v>1525400</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.52</v>
+      </c>
+      <c r="H117" t="n">
+        <v>59.08</v>
       </c>
       <c r="I117" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J117" s="9" t="n"/>
-      <c r="K117" s="9" t="n"/>
+      <c r="J117" s="9" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>0.415</v>
+      </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
     </row>
@@ -5744,28 +5759,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E118" s="16" t="n">
-        <v>-0.0408</v>
+        <v>0.395</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1010200</v>
+        <v>1459400</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.32</v>
+        <v>0.06</v>
       </c>
       <c r="H118" t="n">
-        <v>41.86</v>
+        <v>56.49</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5773,10 +5788,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.254</v>
+        <v>0.384</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.253</v>
+        <v>0.327</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5789,28 +5804,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E119" s="10" t="n">
-        <v>0.008800000000000001</v>
+        <v>1.79</v>
+      </c>
+      <c r="E119" s="16" t="n">
+        <v>-0.0272</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>990400</v>
+        <v>1443800</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="H119" t="n">
-        <v>31.6</v>
+        <v>37.92</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5818,10 +5833,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.622</v>
+        <v>1.878</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.655</v>
+        <v>1.955</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5834,39 +5849,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="E120" s="16" t="n">
-        <v>-0.0121</v>
+        <v>0.53</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>0.0095</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>971600</v>
+        <v>1435600</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.14</v>
+        <v>0.77</v>
       </c>
       <c r="H120" t="n">
-        <v>34.61</v>
-      </c>
-      <c r="I120" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.46</v>
+      </c>
+      <c r="I120" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>7.619</v>
+        <v>0.507</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>7.813</v>
+        <v>0.418</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5879,39 +5894,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>1422400</v>
+      </c>
+      <c r="G121" s="12" t="n">
         <v>1.03</v>
       </c>
-      <c r="E121" s="16" t="n">
-        <v>-0.009599999999999999</v>
-      </c>
-      <c r="F121" s="11" t="n">
-        <v>970500</v>
-      </c>
-      <c r="G121" s="12" t="n">
-        <v>0.61</v>
-      </c>
       <c r="H121" t="n">
-        <v>50.78</v>
-      </c>
-      <c r="I121" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.74</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>1.029</v>
+        <v>0.383</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>1.018</v>
+        <v>0.391</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5924,28 +5939,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>6.12</v>
+        <v>1.02</v>
       </c>
       <c r="E122" s="16" t="n">
-        <v>-0.0129</v>
+        <v>-0.0097</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>921100</v>
+        <v>1383400</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="H122" t="n">
-        <v>37.18</v>
+        <v>42.99</v>
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
@@ -5953,10 +5968,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>6.264</v>
+        <v>1.068</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>6.462</v>
+        <v>1.025</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5969,28 +5984,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="E123" s="16" t="n">
-        <v>-0.0317</v>
+        <v>0.575</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>0.008800000000000001</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>916300</v>
+        <v>1378000</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H123" t="n">
-        <v>25.41</v>
+        <v>31.6</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -5998,10 +6013,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>3.251</v>
+        <v>0.622</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>3.452</v>
+        <v>0.655</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6014,28 +6029,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E124" s="17" t="n">
-        <v>0</v>
+        <v>1.29</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>881300</v>
+        <v>1352900</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.36</v>
+        <v>0.12</v>
       </c>
       <c r="H124" t="n">
-        <v>39.13</v>
+        <v>38.46</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -6043,10 +6058,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.63</v>
+        <v>1.319</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.636</v>
+        <v>1.423</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6059,39 +6074,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1.07</v>
+        <v>0.255</v>
       </c>
       <c r="E125" s="16" t="n">
-        <v>-0.009300000000000001</v>
+        <v>-0.0192</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>865800</v>
+        <v>1347100</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.1</v>
+        <v>0.86</v>
       </c>
       <c r="H125" t="n">
-        <v>76.36</v>
-      </c>
-      <c r="I125" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.92</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.267</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.783</v>
+        <v>0.278</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6104,39 +6119,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E126" s="16" t="n">
-        <v>-0.017</v>
+        <v>2.58</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>0.0118</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>852200</v>
+        <v>1325700</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.7</v>
+        <v>0.23</v>
       </c>
       <c r="H126" t="n">
-        <v>26.06</v>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.87</v>
+      </c>
+      <c r="I126" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>3.034</v>
+        <v>2.566</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>3.136</v>
+        <v>2.546</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6149,28 +6164,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="E127" s="16" t="n">
-        <v>-0.0166</v>
+        <v>0.385</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>844500</v>
+        <v>1286000</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.21</v>
+        <v>1.57</v>
       </c>
       <c r="H127" t="n">
-        <v>39.45</v>
+        <v>59.67</v>
       </c>
       <c r="I127" s="15" t="inlineStr">
         <is>
@@ -6178,10 +6193,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>7.869</v>
+        <v>0.378</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>8.057</v>
+        <v>0.38</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6194,28 +6209,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E128" s="10" t="n">
-        <v>0.008100000000000001</v>
+        <v>4.68</v>
+      </c>
+      <c r="E128" s="16" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>811400</v>
+        <v>1234700</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="H128" t="n">
-        <v>45.44</v>
+        <v>47.08</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6223,10 +6238,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>1.262</v>
+        <v>4.73</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.299</v>
+        <v>4.602</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6239,28 +6254,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E129" s="16" t="n">
-        <v>-0.004500000000000001</v>
+        <v>1.26</v>
+      </c>
+      <c r="E129" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>803400</v>
+        <v>1228300</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.16</v>
+        <v>0.3</v>
       </c>
       <c r="H129" t="n">
-        <v>30.07</v>
+        <v>53.68</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
@@ -6268,10 +6283,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>4.639</v>
+        <v>1.248</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>4.942</v>
+        <v>1.155</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6284,28 +6299,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>MAGMA</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>4.68</v>
+        <v>0.28</v>
       </c>
       <c r="E130" s="16" t="n">
-        <v>-0.0064</v>
+        <v>-0.0175</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>767700</v>
+        <v>1210300</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.08</v>
+        <v>2.16</v>
       </c>
       <c r="H130" t="n">
-        <v>47.08</v>
+        <v>28.6</v>
       </c>
       <c r="I130" s="13" t="inlineStr">
         <is>
@@ -6313,10 +6328,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>4.73</v>
+        <v>0.288</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>4.602</v>
+        <v>0.287</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6329,28 +6344,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>0.0089</v>
+        <v>0.255</v>
+      </c>
+      <c r="E131" s="16" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>762600</v>
+        <v>1180900</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.08</v>
+        <v>1.39</v>
       </c>
       <c r="H131" t="n">
-        <v>47.6</v>
+        <v>37.88</v>
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
@@ -6358,10 +6373,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>1.153</v>
+        <v>0.26</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>1.105</v>
+        <v>0.265</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6374,28 +6389,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>2.84</v>
+        <v>0.48</v>
       </c>
       <c r="E132" s="16" t="n">
-        <v>-0.0207</v>
+        <v>-0.0103</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>742100</v>
+        <v>1159700</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.28</v>
+        <v>0.38</v>
       </c>
       <c r="H132" t="n">
-        <v>78.34999999999999</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
@@ -6403,10 +6418,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>2.42</v>
+        <v>0.456</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>2.016</v>
+        <v>0.411</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6419,28 +6434,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="E133" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0089</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>739800</v>
+        <v>1154600</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="H133" t="n">
-        <v>54.63</v>
+        <v>47.6</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -6448,10 +6463,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>1.249</v>
+        <v>1.153</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>1.156</v>
+        <v>1.105</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6464,28 +6479,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.635</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E134" s="16" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>719200</v>
+        <v>1149400</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.21</v>
+        <v>0.29</v>
       </c>
       <c r="H134" t="n">
-        <v>56.5</v>
+        <v>30.73</v>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
@@ -6493,10 +6508,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.635</v>
+        <v>0.581</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.598</v>
+        <v>0.586</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6509,39 +6524,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>0.0247</v>
+        <v>2.89</v>
+      </c>
+      <c r="E135" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>713700</v>
+        <v>1146800</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.24</v>
+        <v>0.39</v>
       </c>
       <c r="H135" t="n">
-        <v>57.35</v>
-      </c>
-      <c r="I135" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.66</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>2.805</v>
+        <v>2.978</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>2.716</v>
+        <v>3.036</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6554,28 +6569,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.91</v>
+        <v>0.46</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.011</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>707200</v>
+        <v>1145700</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.22</v>
+        <v>0.62</v>
       </c>
       <c r="H136" t="n">
-        <v>41.52</v>
+        <v>53.95</v>
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
@@ -6583,10 +6598,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.923</v>
+        <v>0.45</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.969</v>
+        <v>0.459</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6599,39 +6614,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E137" s="17" t="n">
-        <v>0</v>
+        <v>7.68</v>
+      </c>
+      <c r="E137" s="16" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>700000</v>
+        <v>1129500</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.28</v>
       </c>
       <c r="H137" t="n">
-        <v>41.61</v>
-      </c>
-      <c r="I137" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.72</v>
+      </c>
+      <c r="I137" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>0.63</v>
+        <v>7.867</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>0.636</v>
+        <v>8.057</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6644,39 +6659,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>3.93</v>
+        <v>4.37</v>
       </c>
       <c r="E138" s="16" t="n">
-        <v>-0.0025</v>
+        <v>-0.0113</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>680700</v>
+        <v>1114200</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="H138" t="n">
-        <v>61.58</v>
-      </c>
-      <c r="I138" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.02</v>
+      </c>
+      <c r="I138" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>3.802</v>
+        <v>4.636</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>3.459</v>
+        <v>4.941</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6689,39 +6704,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>1.8</v>
+        <v>1.07</v>
       </c>
       <c r="E139" s="16" t="n">
-        <v>-0.0217</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>650000</v>
+        <v>1100500</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="H139" t="n">
-        <v>38.77</v>
-      </c>
-      <c r="I139" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.36</v>
+      </c>
+      <c r="I139" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>1.879</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>1.955</v>
+        <v>0.783</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6734,40 +6749,33 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E140" s="16" t="n">
-        <v>-0.0052</v>
+        <v>0.255</v>
+      </c>
+      <c r="E140" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>649600</v>
+        <v>1098400</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H140" t="n">
-        <v>37.36</v>
-      </c>
-      <c r="I140" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J140" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="K140" s="9" t="n">
-        <v>1.04</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="I140" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n"/>
+      <c r="K140" s="9" t="n"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
     </row>
@@ -6779,39 +6787,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E141" s="17" t="n">
-        <v>0</v>
+        <v>2.89</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>0.0212</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>649300</v>
+        <v>1093500</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.06</v>
+        <v>0.36</v>
       </c>
       <c r="H141" t="n">
-        <v>35.68</v>
-      </c>
-      <c r="I141" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.87</v>
+      </c>
+      <c r="I141" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>1.318</v>
+        <v>2.805</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>1.423</v>
+        <v>2.716</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6824,28 +6832,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.63</v>
+        <v>2.81</v>
       </c>
       <c r="E142" s="16" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.031</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>606300</v>
+        <v>1090500</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="H142" t="n">
-        <v>45.79</v>
+        <v>76.05</v>
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
@@ -6853,10 +6861,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.634</v>
+        <v>2.417</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.629</v>
+        <v>2.016</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6869,39 +6877,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="E143" s="17" t="n">
-        <v>0</v>
+        <v>0.615</v>
+      </c>
+      <c r="E143" s="16" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>578500</v>
+        <v>1068600</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.13</v>
+        <v>0.35</v>
       </c>
       <c r="H143" t="n">
-        <v>37.69</v>
-      </c>
-      <c r="I143" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.47</v>
+      </c>
+      <c r="I143" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>1.939</v>
+        <v>0.611</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>2.061</v>
+        <v>0.592</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6914,39 +6922,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E144" s="17" t="n">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="E144" s="16" t="n">
+        <v>-0.0426</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>575100</v>
+        <v>1054000</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.15</v>
+        <v>0.64</v>
       </c>
       <c r="H144" t="n">
-        <v>59.19</v>
-      </c>
-      <c r="I144" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.46</v>
+      </c>
+      <c r="I144" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>0.625</v>
+        <v>0.238</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>0.588</v>
+        <v>0.243</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6959,39 +6967,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>WCEHB</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>0.705</v>
+        <v>1.03</v>
       </c>
       <c r="E145" s="16" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>565500</v>
+        <v>1040300</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>1.1</v>
+        <v>0.66</v>
       </c>
       <c r="H145" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="I145" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.78</v>
+      </c>
+      <c r="I145" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>0.705</v>
+        <v>1.029</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>1.018</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7004,28 +7012,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E146" s="10" t="n">
-        <v>0.0138</v>
+        <v>3.41</v>
+      </c>
+      <c r="E146" s="16" t="n">
+        <v>-0.0145</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>556100</v>
+        <v>1039700</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.33</v>
+        <v>0.18</v>
       </c>
       <c r="H146" t="n">
-        <v>49.47</v>
+        <v>34.83</v>
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
@@ -7033,10 +7041,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>0.732</v>
+        <v>3.566</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>0.751</v>
+        <v>3.689</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7049,28 +7057,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E147" s="16" t="n">
-        <v>-0.006</v>
+        <v>1.02</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>0.0515</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>544500</v>
+        <v>1038700</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.17</v>
+        <v>1.77</v>
       </c>
       <c r="H147" t="n">
-        <v>59.82</v>
+        <v>62.33</v>
       </c>
       <c r="I147" s="15" t="inlineStr">
         <is>
@@ -7078,10 +7086,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.985</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>0.733</v>
+        <v>0.976</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7094,28 +7102,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>TAKAFUL</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>2.54</v>
+        <v>2.89</v>
       </c>
       <c r="E148" s="16" t="n">
-        <v>-0.0117</v>
+        <v>-0.017</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>539600</v>
+        <v>1034100</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.16</v>
+        <v>0.84</v>
       </c>
       <c r="H148" t="n">
-        <v>30.61</v>
+        <v>26.06</v>
       </c>
       <c r="I148" s="13" t="inlineStr">
         <is>
@@ -7123,10 +7131,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>2.645</v>
+        <v>3.034</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>2.769</v>
+        <v>3.136</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7139,28 +7147,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E149" s="10" t="n">
-        <v>0.0146</v>
+        <v>0.365</v>
+      </c>
+      <c r="E149" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>532500</v>
+        <v>1003900</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="H149" t="n">
-        <v>57.54</v>
+        <v>40.94</v>
       </c>
       <c r="I149" s="13" t="inlineStr">
         <is>
@@ -7168,10 +7176,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>1.354</v>
+        <v>0.374</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>1.18</v>
+        <v>0.389</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7184,39 +7192,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="E150" s="16" t="n">
-        <v>-0.0223</v>
+        <v>1.4</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>0.0219</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>531700</v>
+        <v>984700</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
       <c r="H150" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="I150" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.41</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>2.671</v>
+        <v>1.355</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>2.844</v>
+        <v>1.18</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7229,28 +7237,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="E151" s="16" t="n">
-        <v>-0.0125</v>
+        <v>0.65</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>0.04</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>513300</v>
+        <v>922800</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.14</v>
+        <v>0.8</v>
       </c>
       <c r="H151" t="n">
-        <v>52.34</v>
+        <v>58.77</v>
       </c>
       <c r="I151" s="15" t="inlineStr">
         <is>
@@ -7258,10 +7266,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>7.888</v>
+        <v>0.629</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>7.818</v>
+        <v>0.605</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7274,28 +7282,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0351</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>LSH</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E152" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.61</v>
+      </c>
+      <c r="E152" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>513000</v>
+        <v>906000</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1.4</v>
+        <v>0.37</v>
       </c>
       <c r="H152" t="n">
-        <v>55.34</v>
+        <v>39.13</v>
       </c>
       <c r="I152" s="13" t="inlineStr">
         <is>
@@ -7303,16 +7311,1816 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>1.601</v>
+        <v>0.63</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>1.6</v>
+        <v>0.636</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E153" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>905700</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H153" t="n">
+        <v>39.41</v>
+      </c>
+      <c r="I153" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>904700</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H154" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>2.061</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>896100</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H155" t="n">
+        <v>65.12</v>
+      </c>
+      <c r="I155" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="n">
+        <v>9.647</v>
+      </c>
+      <c r="K155" s="9" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="14" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E156" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>885400</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H156" t="n">
+        <v>38.48</v>
+      </c>
+      <c r="I156" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="14" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="E157" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>872300</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H157" t="n">
+        <v>62.24</v>
+      </c>
+      <c r="I157" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="n">
+        <v>3.802</v>
+      </c>
+      <c r="K157" s="9" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="14" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>MCEMENT</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>832500</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H158" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="I158" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="n">
+        <v>5.629</v>
+      </c>
+      <c r="K158" s="9" t="n">
+        <v>6.035</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="14" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>5053</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>OSK</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E159" s="16" t="n">
+        <v>-0.0222</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>796300</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H159" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="n">
+        <v>1.877</v>
+      </c>
+      <c r="K159" s="9" t="n">
+        <v>1.953</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="14" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E160" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>791300</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H160" t="n">
+        <v>52.65</v>
+      </c>
+      <c r="I160" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K160" s="9" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>790800</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H161" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="K161" s="9" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="14" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E162" s="16" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>750500</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H162" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="I162" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="K162" s="9" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E163" s="16" t="n">
+        <v>-0.0117</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>733700</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H163" t="n">
+        <v>30.61</v>
+      </c>
+      <c r="I163" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="K163" s="9" t="n">
+        <v>2.769</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="14" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>FFB</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="E164" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>703200</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H164" t="n">
+        <v>36.18</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="n">
+        <v>1.955</v>
+      </c>
+      <c r="K164" s="9" t="n">
+        <v>2.064</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E165" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H165" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K165" s="9" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="14" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E166" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>689900</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H166" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="I166" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="K166" s="9" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="14" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E167" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>683600</v>
+      </c>
+      <c r="G167" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H167" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="K167" s="9" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="14" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>4243</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>WTK</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E168" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>681800</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H168" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="K168" s="9" t="n">
+        <v>1.019</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>0351</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>LSH</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E169" s="10" t="n">
+        <v>0.0312</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>675800</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H169" t="n">
+        <v>61.61</v>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="n">
+        <v>1.604</v>
+      </c>
+      <c r="K169" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="14" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>0366</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ICENTS</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E170" s="16" t="n">
+        <v>-0.0298</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>661300</v>
+      </c>
+      <c r="G170" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H170" t="n">
+        <v>51.07</v>
+      </c>
+      <c r="I170" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="K170" s="9" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="14" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>6012</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>MAXIS</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="E171" s="16" t="n">
+        <v>-0.0197</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>656600</v>
+      </c>
+      <c r="G171" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H171" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J171" s="9" t="n">
+        <v>3.562</v>
+      </c>
+      <c r="K171" s="9" t="n">
+        <v>3.604</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="14" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>655200</v>
+      </c>
+      <c r="G172" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H172" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="I172" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="K172" s="9" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="14" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>4863</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>TM</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="E173" s="16" t="n">
+        <v>-0.0112</v>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>651800</v>
+      </c>
+      <c r="G173" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H173" t="n">
+        <v>52.91</v>
+      </c>
+      <c r="I173" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J173" s="9" t="n">
+        <v>7.889</v>
+      </c>
+      <c r="K173" s="9" t="n">
+        <v>7.818</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="14" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E174" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>635400</v>
+      </c>
+      <c r="G174" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H174" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="I174" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J174" s="9" t="n">
+        <v>2.071</v>
+      </c>
+      <c r="K174" s="9" t="n">
+        <v>2.012</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="14" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E175" s="16" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>627500</v>
+      </c>
+      <c r="G175" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H175" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="I175" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J175" s="9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K175" s="9" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="14" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>3565</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>WCEHB</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="E176" s="16" t="n">
+        <v>-0.006999999999999999</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>625300</v>
+      </c>
+      <c r="G176" s="12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H176" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="I176" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J176" s="9" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="K176" s="9" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E177" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>610100</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H177" t="n">
+        <v>42.24</v>
+      </c>
+      <c r="I177" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="K177" s="9" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="14" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>7197</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>GESHEN</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>609900</v>
+      </c>
+      <c r="G178" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H178" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="I178" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J178" s="9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K178" s="9" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E179" s="16" t="n">
+        <v>-0.0223</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>609300</v>
+      </c>
+      <c r="G179" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H179" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="I179" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="n">
+        <v>2.671</v>
+      </c>
+      <c r="K179" s="9" t="n">
+        <v>2.844</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="14" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>PADINI</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>599800</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H180" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="I180" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J180" s="9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K180" s="9" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="14" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>7231</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>WELLCAL</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E181" s="16" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>590200</v>
+      </c>
+      <c r="G181" s="12" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="H181" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="I181" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="K181" s="9" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="14" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E182" s="16" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="F182" s="11" t="n">
+        <v>586800</v>
+      </c>
+      <c r="G182" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H182" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="I182" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="n">
+        <v>2.059</v>
+      </c>
+      <c r="K182" s="9" t="n">
+        <v>2.098</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="14" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E183" s="10" t="n">
+        <v>0.004699999999999999</v>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>585300</v>
+      </c>
+      <c r="G183" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H183" t="n">
+        <v>45.42</v>
+      </c>
+      <c r="I183" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J183" s="9" t="n">
+        <v>2.205</v>
+      </c>
+      <c r="K183" s="9" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="14" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>0308</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>KTI</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E184" s="16" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="F184" s="11" t="n">
+        <v>584800</v>
+      </c>
+      <c r="G184" s="12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H184" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="I184" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J184" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K184" s="9" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="14" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>UNISEM</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E185" s="10" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>582300</v>
+      </c>
+      <c r="G185" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H185" t="n">
+        <v>44</v>
+      </c>
+      <c r="I185" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="n">
+        <v>4.356</v>
+      </c>
+      <c r="K185" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="14" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>TMK</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E186" s="10" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="F186" s="11" t="n">
+        <v>576600</v>
+      </c>
+      <c r="G186" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H186" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="I186" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J186" s="9" t="n">
+        <v>2.944</v>
+      </c>
+      <c r="K186" s="9" t="n">
+        <v>2.828</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="14" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E187" s="16" t="n">
+        <v>-0.0073</v>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>576000</v>
+      </c>
+      <c r="G187" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H187" t="n">
+        <v>78.39</v>
+      </c>
+      <c r="I187" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J187" s="9" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="K187" s="9" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="14" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="E188" s="16" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="F188" s="11" t="n">
+        <v>536000</v>
+      </c>
+      <c r="G188" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H188" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="I188" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J188" s="9" t="n">
+        <v>6.641</v>
+      </c>
+      <c r="K188" s="9" t="n">
+        <v>6.869</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="14" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>3417</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>E&amp;O</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E189" s="16" t="n">
+        <v>-0.006500000000000001</v>
+      </c>
+      <c r="F189" s="11" t="n">
+        <v>528400</v>
+      </c>
+      <c r="G189" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H189" t="n">
+        <v>47.36</v>
+      </c>
+      <c r="I189" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J189" s="9" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="K189" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="14" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>6599</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>AEON</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E190" s="16" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="F190" s="11" t="n">
+        <v>523200</v>
+      </c>
+      <c r="G190" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H190" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="I190" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J190" s="9" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="K190" s="9" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="14" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="E191" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>522500</v>
+      </c>
+      <c r="G191" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H191" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="I191" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J191" s="9" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="K191" s="9" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="14" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E192" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F192" s="11" t="n">
+        <v>519000</v>
+      </c>
+      <c r="G192" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H192" t="n">
+        <v>55.47</v>
+      </c>
+      <c r="I192" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J192" s="9" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="K192" s="9" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M152"/>
+  <autoFilter ref="A1:M192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-01/bursa-report-2026-10-01.xlsx
+++ b/docs/downloads/2026-10-01/bursa-report-2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-01" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-01'!$A$1:$M$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-01'!$A$1:$M$206</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M204"/>
+  <dimension ref="A1:M206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.555</v>
+        <v>0.55</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0472</v>
+        <v>0.0377</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>4339400</v>
+        <v>4404700</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>63.29</v>
+        <v>62.29</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.518</v>
+        <v>0.517</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.473</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.555高于50日均线0.473，SAR转多信号获均线支撑；RSI 63.29偏强但未超买，信号可靠性中等偏上。</t>
+          <t>现价0.55高于50日均线0.473，SAR转多信号获均线支撑；RSI 62.29偏强但未超买，信号可靠性中等偏上。</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>SAR转多，现价0.51高于50日均线0.468，RSI 64.61接近超买区，信号偏积极但需留意上行空间有限。</t>
+          <t>现价0.51高于50日均线0.468，SAR转多信号获均线支撑；RSI 64.61接近超买区，动能偏强但上行空间受限。</t>
         </is>
       </c>
     </row>
@@ -672,19 +672,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.165</v>
+        <v>0.17</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.0313</v>
+        <v>0.0625</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>138255600</v>
+        <v>140398300</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H4" t="n">
-        <v>21.74</v>
+        <v>23.37</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.246</v>
+        <v>0.247</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>0.46</v>
@@ -723,10 +723,10 @@
         <v>0.0179</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>104182800</v>
+        <v>105957100</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>3.59</v>
+        <v>3.65</v>
       </c>
       <c r="H5" t="n">
         <v>72.5</v>
@@ -768,7 +768,7 @@
         <v>-0.0244</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>75114200</v>
+        <v>75261600</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>1.42</v>
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>58620600</v>
+        <v>58691700</v>
       </c>
       <c r="G7" s="12" t="n"/>
       <c r="I7" s="13" t="inlineStr">
@@ -843,19 +843,19 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.5</v>
+        <v>0.505</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.0309</v>
+        <v>0.0412</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>41920500</v>
+        <v>43372000</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="H8" t="n">
-        <v>61.13</v>
+        <v>62.49</v>
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.472</v>
+        <v>0.473</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>0.472</v>
@@ -894,10 +894,10 @@
         <v>0.3889</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>27904400</v>
+        <v>28019500</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>35.2</v>
+        <v>35.35</v>
       </c>
       <c r="H9" t="n">
         <v>76.25</v>
@@ -939,10 +939,10 @@
         <v>0.0077</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>25012800</v>
+        <v>25404800</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="H10" t="n">
         <v>77</v>
@@ -1029,10 +1029,10 @@
         <v>-0.1818</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>20892000</v>
+        <v>20982000</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>5.38</v>
+        <v>5.4</v>
       </c>
       <c r="H12" t="n">
         <v>30.84</v>
@@ -1074,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>18427400</v>
+        <v>18436400</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>15.28</v>
+        <v>15.29</v>
       </c>
       <c r="H13" t="n">
         <v>44.56</v>
@@ -1113,13 +1113,13 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0.0435</v>
+        <v>0.115</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>17828900</v>
+        <v>17883700</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>0.57</v>
@@ -1157,10 +1157,10 @@
         <v>0.0337</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>17546100</v>
+        <v>17647500</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H15" t="n">
         <v>54.57</v>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.37</v>
+        <v>0.375</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.0423</v>
+        <v>0.0563</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>15582700</v>
+        <v>15582800</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>2.09</v>
       </c>
       <c r="H16" t="n">
-        <v>71.03</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>14015400</v>
+        <v>14041700</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0.92</v>
       </c>
       <c r="H17" t="n">
-        <v>58.78</v>
+        <v>60.2</v>
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.535</v>
+        <v>0.536</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0.489</v>
@@ -1292,10 +1292,10 @@
         <v>0.0083</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>12559400</v>
+        <v>13059500</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H18" t="n">
         <v>74.09999999999999</v>
@@ -1337,7 +1337,7 @@
         <v>-0.0625</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>12302200</v>
+        <v>12338500</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>0.32</v>
@@ -1376,19 +1376,19 @@
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>0</v>
+        <v>0.285</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>11438000</v>
+        <v>11453000</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>1.62</v>
       </c>
       <c r="H20" t="n">
-        <v>39.08</v>
+        <v>35.15</v>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.296</v>
+        <v>0.295</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.311</v>
+        <v>0.31</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1427,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>10885900</v>
+        <v>11085900</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="H21" t="n">
         <v>48.12</v>
@@ -1472,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>10557600</v>
+        <v>10558700</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>0.23</v>
@@ -1646,19 +1646,19 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>0.0227</v>
+        <v>0.017</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>9517000</v>
+        <v>9741300</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="H26" t="n">
-        <v>58.2</v>
+        <v>57.5</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1.747</v>
+        <v>1.746</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1.563</v>
+        <v>1.562</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1682,28 +1682,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.2</v>
+        <v>9.94</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>-0.009899999999999999</v>
+        <v>-0.005</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>8787800</v>
+        <v>8913200</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.4</v>
+        <v>0.73</v>
       </c>
       <c r="H27" t="n">
-        <v>56.72</v>
+        <v>34.46</v>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.196</v>
+        <v>10.123</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.18</v>
+        <v>10.279</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1727,28 +1727,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>9.93</v>
+        <v>0.2</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>-0.006</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>8259800</v>
+        <v>8879200</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.67</v>
+        <v>0.4</v>
       </c>
       <c r="H28" t="n">
-        <v>34.01</v>
+        <v>56.72</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>10.122</v>
+        <v>0.196</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>10.279</v>
+        <v>0.18</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1787,7 +1787,7 @@
         <v>-0.0132</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>7778400</v>
+        <v>7779100</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0.72</v>
@@ -1877,10 +1877,10 @@
         <v>-0.0203</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>7371300</v>
+        <v>7411200</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H31" t="n">
         <v>29.47</v>
@@ -1916,19 +1916,19 @@
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.275</v>
+        <v>0.27</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>-0.0179</v>
+        <v>-0.0357</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>7227800</v>
+        <v>7330800</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>3.92</v>
+        <v>3.97</v>
       </c>
       <c r="H32" t="n">
-        <v>58.27</v>
+        <v>55.02</v>
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
@@ -1952,28 +1952,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.365</v>
+        <v>0.525</v>
       </c>
       <c r="E33" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>5997200</v>
+        <v>6090300</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.96</v>
+        <v>0.16</v>
       </c>
       <c r="H33" t="n">
-        <v>48.24</v>
+        <v>28.71</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.367</v>
+        <v>0.604</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.367</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1997,39 +1997,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>-0.0063</v>
+        <v>0.365</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>5995100</v>
+        <v>5997200</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.54</v>
+        <v>0.96</v>
       </c>
       <c r="H34" t="n">
-        <v>60.78</v>
-      </c>
-      <c r="I34" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.24</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.732</v>
+        <v>0.367</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.694</v>
+        <v>0.367</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2042,39 +2042,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.52</v>
+        <v>0.785</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>-0.0095</v>
+        <v>-0.0063</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5990200</v>
+        <v>5995200</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.16</v>
+        <v>0.54</v>
       </c>
       <c r="H35" t="n">
-        <v>28.26</v>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.78</v>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.604</v>
+        <v>0.732</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2102,10 +2102,10 @@
         <v>-0.008399999999999999</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5898700</v>
+        <v>5918400</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H36" t="n">
         <v>63.17</v>
@@ -2237,10 +2237,10 @@
         <v>-0.008500000000000001</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>5299800</v>
+        <v>5508400</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="H39" t="n">
         <v>28.67</v>
@@ -2267,28 +2267,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>0.0066</v>
+        <v>2.08</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>5264900</v>
+        <v>5385900</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="H40" t="n">
-        <v>46.78</v>
+        <v>45.91</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.771</v>
+        <v>2.114</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.771</v>
+        <v>2.069</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2312,28 +2312,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.76</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>5254300</v>
+        <v>5283300</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.42</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>54.66</v>
+        <v>43.51</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>3.596</v>
+        <v>0.77</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>2.499</v>
+        <v>0.771</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2357,28 +2357,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>0</v>
+        <v>3.59</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0.008399999999999999</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>5180900</v>
+        <v>5258400</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="H42" t="n">
-        <v>45.91</v>
+        <v>54.84</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>2.114</v>
+        <v>3.597</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>2.069</v>
+        <v>2.499</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2402,39 +2402,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>0.0169</v>
+        <v>0.33</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>5080100</v>
+        <v>5249700</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>2.48</v>
+        <v>0.71</v>
       </c>
       <c r="H43" t="n">
-        <v>61.73</v>
-      </c>
-      <c r="I43" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.89</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.295</v>
+        <v>0.348</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.296</v>
+        <v>0.349</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2447,28 +2447,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.33</v>
+        <v>2.5</v>
       </c>
       <c r="E44" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>5039200</v>
+        <v>5171200</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.68</v>
+        <v>0.28</v>
       </c>
       <c r="H44" t="n">
-        <v>31.89</v>
+        <v>45.9</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.348</v>
+        <v>2.565</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.349</v>
+        <v>2.456</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2492,28 +2492,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1.17</v>
+        <v>0.29</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>-0.0565</v>
+        <v>-0.0169</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>4838400</v>
+        <v>5104100</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.76</v>
+        <v>2.5</v>
       </c>
       <c r="H45" t="n">
-        <v>75.09999999999999</v>
+        <v>37.14</v>
       </c>
       <c r="I45" s="15" t="inlineStr">
         <is>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.97</v>
+        <v>0.294</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.766</v>
+        <v>0.296</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2537,28 +2537,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>2.49</v>
+        <v>0.215</v>
       </c>
       <c r="E46" s="16" t="n">
-        <v>-0.004</v>
+        <v>-0.0227</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>4810900</v>
+        <v>5072700</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="H46" t="n">
-        <v>45.17</v>
+        <v>36.71</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>2.564</v>
+        <v>0.232</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.455</v>
+        <v>0.246</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2582,39 +2582,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E47" s="17" t="n">
-        <v>0</v>
+        <v>0.435</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0.0235</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>4809900</v>
+        <v>4980900</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.2</v>
+        <v>0.88</v>
       </c>
       <c r="H47" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.54</v>
+      </c>
+      <c r="I47" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.232</v>
+        <v>0.407</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.246</v>
+        <v>0.405</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2627,39 +2627,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0363</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PMCK</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E48" s="17" t="n">
-        <v>0</v>
+        <v>1.16</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>-0.0645</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>4641800</v>
+        <v>4874400</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>4.67</v>
+        <v>0.76</v>
       </c>
       <c r="H48" t="n">
-        <v>41.65</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.75</v>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.195</v>
+        <v>0.969</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.2</v>
+        <v>0.766</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2672,28 +2672,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>-0.0225</v>
+        <v>0.185</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4634900</v>
+        <v>4742700</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>1.99</v>
+        <v>0.93</v>
       </c>
       <c r="H49" t="n">
-        <v>71</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="I49" s="15" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.387</v>
+        <v>0.165</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.349</v>
+        <v>0.165</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2717,39 +2717,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0363</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>PMCK</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
         <v>0.19</v>
       </c>
-      <c r="E50" s="10" t="n">
-        <v>0.0857</v>
+      <c r="E50" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>4612700</v>
+        <v>4645000</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.91</v>
+        <v>4.67</v>
       </c>
       <c r="H50" t="n">
-        <v>67.62</v>
-      </c>
-      <c r="I50" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.65</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.165</v>
+        <v>0.195</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.165</v>
+        <v>0.2</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2762,39 +2762,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1.23</v>
+        <v>0.435</v>
       </c>
       <c r="E51" s="16" t="n">
-        <v>-0.04650000000000001</v>
+        <v>-0.0225</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4607800</v>
+        <v>4640200</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>3.1</v>
+        <v>1.99</v>
       </c>
       <c r="H51" t="n">
-        <v>40.94</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71</v>
+      </c>
+      <c r="I51" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>1.277</v>
+        <v>0.387</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>1.332</v>
+        <v>0.349</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         <v>-0.0097</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4580100</v>
+        <v>4609800</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="H52" t="n">
         <v>28.82</v>
@@ -2852,39 +2852,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>4.28</v>
+        <v>1.23</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>-0.0183</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>4511700</v>
+        <v>4608600</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.68</v>
+        <v>3.1</v>
       </c>
       <c r="H53" t="n">
-        <v>73.02</v>
-      </c>
-      <c r="I53" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.94</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>3.759</v>
+        <v>1.277</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>3.304</v>
+        <v>1.332</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2897,28 +2897,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>0</v>
+        <v>4.28</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>-0.0183</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>4293800</v>
+        <v>4551300</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.15</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>33.55</v>
+        <v>73.02</v>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.268</v>
+        <v>3.759</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.32</v>
+        <v>3.304</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2942,28 +2942,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.245</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>4239400</v>
+        <v>4294900</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="H55" t="n">
-        <v>49.21</v>
+        <v>33.55</v>
       </c>
       <c r="I55" s="15" t="inlineStr">
         <is>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>2.279</v>
+        <v>0.268</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>2.2</v>
+        <v>0.32</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2987,28 +2987,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>2.87</v>
+        <v>2.26</v>
       </c>
       <c r="E56" s="16" t="n">
-        <v>-0.0137</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>4059800</v>
+        <v>4245100</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="H56" t="n">
-        <v>62.04</v>
+        <v>49.21</v>
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>2.799</v>
+        <v>2.279</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>2.659</v>
+        <v>2.2</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3032,28 +3032,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0.0118</v>
+        <v>2.87</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3862200</v>
+        <v>4068300</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="H57" t="n">
-        <v>58.35</v>
+        <v>62.04</v>
       </c>
       <c r="I57" s="15" t="inlineStr">
         <is>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.407</v>
+        <v>2.799</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.404</v>
+        <v>2.659</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3086,16 +3086,16 @@
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.3</v>
+        <v>0.295</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>0.07139999999999999</v>
+        <v>0.0536</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3856400</v>
+        <v>3884300</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
@@ -3115,28 +3115,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E59" s="17" t="n">
-        <v>0</v>
+        <v>1.08</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>-0.027</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3840000</v>
+        <v>3882000</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>45.53</v>
+        <v>38.71</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.194</v>
+        <v>1.161</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.197</v>
+        <v>1.15</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3160,39 +3160,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E60" s="16" t="n">
-        <v>-0.018</v>
+        <v>0.355</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3823500</v>
+        <v>3852300</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H60" t="n">
-        <v>39.73</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.52</v>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>1.162</v>
+        <v>0.335</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>1.15</v>
+        <v>0.315</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3205,28 +3205,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>4.08</v>
+        <v>7.45</v>
       </c>
       <c r="E61" s="16" t="n">
-        <v>-0.0239</v>
+        <v>-0.0067</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3820500</v>
+        <v>3851600</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.48</v>
+        <v>0.37</v>
       </c>
       <c r="H61" t="n">
-        <v>36.15</v>
+        <v>24.59</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>4.477</v>
+        <v>7.851</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>4.51</v>
+        <v>8.214</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3250,39 +3250,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E62" s="17" t="n">
-        <v>0</v>
+        <v>4.09</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>-0.0215</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3816900</v>
+        <v>3844600</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="H62" t="n">
-        <v>62.52</v>
-      </c>
-      <c r="I62" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.38</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.335</v>
+        <v>4.478</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.315</v>
+        <v>4.51</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3295,28 +3295,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="E63" s="16" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.19</v>
+      </c>
+      <c r="E63" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3650500</v>
+        <v>3840000</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.35</v>
+        <v>0.49</v>
       </c>
       <c r="H63" t="n">
-        <v>24.11</v>
+        <v>45.53</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>7.849</v>
+        <v>0.194</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>8.212999999999999</v>
+        <v>0.197</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3340,39 +3340,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.16</v>
+        <v>5.82</v>
       </c>
       <c r="E64" s="16" t="n">
-        <v>-0.0303</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3628500</v>
+        <v>3721300</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="H64" t="n">
-        <v>34.07</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.78</v>
+      </c>
+      <c r="I64" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.176</v>
+        <v>5.691</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.212</v>
+        <v>5.191</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3385,39 +3385,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="E65" s="16" t="n">
-        <v>-0.0068</v>
+        <v>0.165</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3616900</v>
+        <v>3658500</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="H65" t="n">
-        <v>60.28</v>
-      </c>
-      <c r="I65" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.1</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>5.692</v>
+        <v>0.177</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>5.191</v>
+        <v>0.212</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3445,10 +3445,10 @@
         <v>0.0326</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3599200</v>
+        <v>3649800</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H66" t="n">
         <v>60.38</v>
@@ -3475,28 +3475,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0.009899999999999999</v>
+        <v>2.74</v>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>-0.0036</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3505000</v>
+        <v>3616500</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.97</v>
+        <v>0.85</v>
       </c>
       <c r="H67" t="n">
-        <v>60.23</v>
+        <v>80.03</v>
       </c>
       <c r="I67" s="15" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>2.906</v>
+        <v>2.535</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>2.719</v>
+        <v>2.18</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3520,28 +3520,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E68" s="17" t="n">
-        <v>0</v>
+        <v>3.08</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3421300</v>
+        <v>3506300</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.55</v>
+        <v>0.97</v>
       </c>
       <c r="H68" t="n">
-        <v>64.37</v>
+        <v>60.63</v>
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.77</v>
+        <v>2.907</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.756</v>
+        <v>2.719</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         <v>-0.0231</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3386800</v>
+        <v>3480700</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H69" t="n">
         <v>40.09</v>
@@ -3610,39 +3610,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0.0345</v>
+        <v>0.73</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3323600</v>
+        <v>3443900</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="H70" t="n">
-        <v>55.84</v>
-      </c>
-      <c r="I70" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.8</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.287</v>
+        <v>0.736</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.277</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3655,28 +3655,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>0.0317</v>
+        <v>0.79</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>3321700</v>
+        <v>3421300</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="H71" t="n">
-        <v>51.5</v>
+        <v>64.37</v>
       </c>
       <c r="I71" s="15" t="inlineStr">
         <is>
@@ -3684,10 +3684,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.319</v>
+        <v>0.77</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.337</v>
+        <v>0.756</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3700,28 +3700,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.325</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.0317</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>3313800</v>
+        <v>3407300</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.22</v>
+        <v>0.61</v>
       </c>
       <c r="H72" t="n">
-        <v>68.7</v>
+        <v>51.5</v>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.497</v>
+        <v>0.319</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.415</v>
+        <v>0.337</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3745,39 +3745,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E73" s="16" t="n">
-        <v>-0.0241</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>3232600</v>
+        <v>3363200</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.5</v>
+        <v>0.23</v>
       </c>
       <c r="H73" t="n">
-        <v>35.14</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.7</v>
+      </c>
+      <c r="I73" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>1.707</v>
+        <v>0.497</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>1.824</v>
+        <v>0.415</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3790,28 +3790,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E74" s="16" t="n">
-        <v>-0.0145</v>
+        <v>0.3</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>3212300</v>
+        <v>3324600</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.76</v>
+        <v>0.2</v>
       </c>
       <c r="H74" t="n">
-        <v>75.58</v>
+        <v>55.84</v>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>2.532</v>
+        <v>0.287</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>2.179</v>
+        <v>0.277</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3835,28 +3835,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E75" s="17" t="n">
-        <v>0</v>
+        <v>1.61</v>
+      </c>
+      <c r="E75" s="16" t="n">
+        <v>-0.0301</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>3207900</v>
+        <v>3311700</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>15.08</v>
+        <v>0.51</v>
       </c>
       <c r="H75" t="n">
-        <v>57.18</v>
+        <v>34.31</v>
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
@@ -3864,10 +3864,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.44</v>
+        <v>1.706</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.434</v>
+        <v>1.824</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3880,39 +3880,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="E76" s="16" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.44</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>3073700</v>
+        <v>3207900</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.9</v>
+        <v>15.08</v>
       </c>
       <c r="H76" t="n">
-        <v>59.81</v>
-      </c>
-      <c r="I76" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.18</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>6.678</v>
+        <v>0.44</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>6.555</v>
+        <v>0.434</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3934,19 +3934,19 @@
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.89</v>
+        <v>0.905</v>
       </c>
       <c r="E77" s="16" t="n">
-        <v>-0.0326</v>
+        <v>-0.0163</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3068700</v>
+        <v>3140300</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H77" t="n">
-        <v>52.03</v>
+        <v>57.18</v>
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.892</v>
+        <v>0.893</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.853</v>
+        <v>0.854</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3970,39 +3970,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>7.74</v>
+        <v>7.02</v>
       </c>
       <c r="E78" s="16" t="n">
-        <v>-0.0064</v>
+        <v>-0.0071</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>3064200</v>
+        <v>3122400</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.25</v>
+        <v>0.91</v>
       </c>
       <c r="H78" t="n">
-        <v>47.79</v>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.1</v>
+      </c>
+      <c r="I78" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>7.796</v>
+        <v>6.679</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>7.747</v>
+        <v>6.555</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4015,39 +4015,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>2.91</v>
+        <v>7.74</v>
       </c>
       <c r="E79" s="16" t="n">
-        <v>-0.0068</v>
+        <v>-0.0064</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2965000</v>
+        <v>3079900</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="H79" t="n">
-        <v>63.09</v>
-      </c>
-      <c r="I79" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.79</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>2.704</v>
+        <v>7.796</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>2.534</v>
+        <v>7.747</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4075,7 +4075,7 @@
         <v>0.0156</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2964900</v>
+        <v>3024200</v>
       </c>
       <c r="G80" s="12" t="n">
         <v>0.3</v>
@@ -4105,39 +4105,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>1.29</v>
+        <v>2.92</v>
       </c>
       <c r="E81" s="16" t="n">
-        <v>-0.0077</v>
+        <v>-0.0034</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2941100</v>
+        <v>3023100</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="H81" t="n">
-        <v>43.19</v>
-      </c>
-      <c r="I81" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.71</v>
+      </c>
+      <c r="I81" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>1.355</v>
+        <v>2.705</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1.298</v>
+        <v>2.534</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4150,28 +4150,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.77</v>
+        <v>1.29</v>
       </c>
       <c r="E82" s="16" t="n">
-        <v>-0.0723</v>
+        <v>-0.0077</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2844200</v>
+        <v>2998100</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1.9</v>
+        <v>0.24</v>
       </c>
       <c r="H82" t="n">
-        <v>21.05</v>
+        <v>43.19</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.865</v>
+        <v>1.355</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.9389999999999999</v>
+        <v>1.298</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4195,39 +4195,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>0.0233</v>
+        <v>0.78</v>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>-0.0602</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2765300</v>
+        <v>2990400</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.5</v>
+        <v>1.99</v>
       </c>
       <c r="H83" t="n">
-        <v>54.54</v>
-      </c>
-      <c r="I83" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.13</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.215</v>
+        <v>0.866</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.213</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4240,28 +4240,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E84" s="16" t="n">
-        <v>-0.0196</v>
+        <v>0.51</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2637000</v>
+        <v>2842100</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.31</v>
+        <v>0.42</v>
       </c>
       <c r="H84" t="n">
-        <v>48.34</v>
+        <v>45.42</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.263</v>
+        <v>0.522</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.224</v>
+        <v>0.532</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4285,28 +4285,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E85" s="17" t="n">
-        <v>0</v>
+        <v>0.52</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0.0297</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2606500</v>
+        <v>2785100</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.4</v>
+        <v>1.01</v>
       </c>
       <c r="H85" t="n">
-        <v>66.25</v>
+        <v>77.55</v>
       </c>
       <c r="I85" s="15" t="inlineStr">
         <is>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.28</v>
+        <v>0.426</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.272</v>
+        <v>0.415</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4330,28 +4330,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E86" s="16" t="n">
-        <v>-0.008100000000000001</v>
+        <v>0.22</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2572300</v>
+        <v>2765300</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="H86" t="n">
-        <v>60.47</v>
+        <v>54.54</v>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
@@ -4359,10 +4359,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.611</v>
+        <v>0.215</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.592</v>
+        <v>0.213</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>-0.0317</v>
+        <v>-0.0349</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2569800</v>
+        <v>2667200</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="H87" t="n">
-        <v>25.41</v>
+        <v>24.94</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -4435,10 +4435,10 @@
         <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2530500</v>
+        <v>2650400</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="H88" t="n">
         <v>50.06</v>
@@ -4465,33 +4465,40 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>0</v>
+        <v>2.43</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>-0.0122</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2492800</v>
+        <v>2649700</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
+      </c>
+      <c r="H89" t="n">
+        <v>51.23</v>
       </c>
       <c r="I89" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J89" s="9" t="n"/>
-      <c r="K89" s="9" t="n"/>
+      <c r="J89" s="9" t="n">
+        <v>2.446</v>
+      </c>
+      <c r="K89" s="9" t="n">
+        <v>2.303</v>
+      </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
     </row>
@@ -4503,39 +4510,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
         <v>0.25</v>
       </c>
       <c r="E90" s="16" t="n">
-        <v>-0.0566</v>
+        <v>-0.0196</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2466700</v>
+        <v>2637000</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.83</v>
+        <v>0.31</v>
       </c>
       <c r="H90" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="I90" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.34</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.234</v>
+        <v>0.263</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.211</v>
+        <v>0.224</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4548,28 +4555,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>0.0297</v>
+        <v>0.295</v>
+      </c>
+      <c r="E91" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2464400</v>
+        <v>2606500</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.89</v>
+        <v>0.4</v>
       </c>
       <c r="H91" t="n">
-        <v>77.55</v>
+        <v>66.25</v>
       </c>
       <c r="I91" s="15" t="inlineStr">
         <is>
@@ -4577,10 +4584,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.426</v>
+        <v>0.28</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.415</v>
+        <v>0.272</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4593,39 +4600,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E92" s="17" t="n">
-        <v>0</v>
+        <v>0.615</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2419800</v>
+        <v>2572300</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>1.82</v>
+        <v>0.85</v>
       </c>
       <c r="H92" t="n">
-        <v>31.63</v>
-      </c>
-      <c r="I92" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.47</v>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.357</v>
+        <v>0.611</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.391</v>
+        <v>0.592</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4638,40 +4645,33 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E93" s="16" t="n">
-        <v>-0.0612</v>
+        <v>0.48</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>0.0105</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2416700</v>
+        <v>2512800</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="H93" t="n">
-        <v>40.24</v>
-      </c>
-      <c r="I93" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J93" s="9" t="n">
-        <v>0.254</v>
-      </c>
-      <c r="K93" s="9" t="n">
-        <v>0.253</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="I93" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="n"/>
+      <c r="K93" s="9" t="n"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
     </row>
@@ -4683,39 +4683,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0219</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>0.0167</v>
+        <v>0.255</v>
+      </c>
+      <c r="E94" s="16" t="n">
+        <v>-0.0377</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>2416200</v>
+        <v>2476700</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.32</v>
+        <v>0.83</v>
       </c>
       <c r="H94" t="n">
-        <v>51.15</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.37</v>
+      </c>
+      <c r="I94" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.306</v>
+        <v>0.234</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.296</v>
+        <v>0.211</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4728,28 +4728,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.255</v>
+        <v>6.75</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>0.02</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>2405900</v>
+        <v>2467300</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.22</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H95" t="n">
-        <v>40.14</v>
+        <v>49.04</v>
       </c>
       <c r="I95" s="15" t="inlineStr">
         <is>
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.267</v>
+        <v>6.758</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.31</v>
+        <v>6.83</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4773,28 +4773,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="E96" s="16" t="n">
-        <v>-0.008100000000000001</v>
+        <v>0.68</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0.0226</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>2391300</v>
+        <v>2458200</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.15</v>
+        <v>0.34</v>
       </c>
       <c r="H96" t="n">
-        <v>52.51</v>
+        <v>50.26</v>
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>2.446</v>
+        <v>0.68</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>2.304</v>
+        <v>0.666</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4818,28 +4818,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>6.75</v>
+        <v>0.255</v>
       </c>
       <c r="E97" s="10" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>2351600</v>
+        <v>2448000</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.54</v>
+        <v>0.22</v>
       </c>
       <c r="H97" t="n">
-        <v>49.04</v>
+        <v>40.14</v>
       </c>
       <c r="I97" s="15" t="inlineStr">
         <is>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>6.758</v>
+        <v>0.267</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>6.83</v>
+        <v>0.31</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4863,28 +4863,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E98" s="16" t="n">
-        <v>-0.0068</v>
+        <v>0.34</v>
+      </c>
+      <c r="E98" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>2335300</v>
+        <v>2419800</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.05</v>
+        <v>1.82</v>
       </c>
       <c r="H98" t="n">
-        <v>51.99</v>
+        <v>31.63</v>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
@@ -4892,10 +4892,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.736</v>
+        <v>0.357</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.391</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4908,28 +4908,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E99" s="17" t="n">
-        <v>0</v>
+        <v>0.235</v>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>-0.0408</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>2313300</v>
+        <v>2416900</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.34</v>
+        <v>0.77</v>
       </c>
       <c r="H99" t="n">
-        <v>45.42</v>
+        <v>41.86</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -4937,10 +4937,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.522</v>
+        <v>0.254</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.532</v>
+        <v>0.253</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4953,39 +4953,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E100" s="16" t="n">
-        <v>-0.0298</v>
+        <v>0.305</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>2303000</v>
+        <v>2416200</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.73</v>
+        <v>0.32</v>
       </c>
       <c r="H100" t="n">
-        <v>75.84999999999999</v>
-      </c>
-      <c r="I100" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.15</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>2.408</v>
+        <v>0.306</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>1.862</v>
+        <v>0.296</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4998,28 +4998,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>1.23</v>
+        <v>0.23</v>
       </c>
       <c r="E101" s="16" t="n">
-        <v>-0.008100000000000001</v>
+        <v>-0.0213</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>2302500</v>
+        <v>2394100</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.4</v>
+        <v>1.44</v>
       </c>
       <c r="H101" t="n">
-        <v>41.37</v>
+        <v>42.62</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>1.26</v>
+        <v>0.238</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>1.298</v>
+        <v>0.244</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5043,39 +5043,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>0.018</v>
+        <v>0.039</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>2259400</v>
+        <v>2366200</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>1.01</v>
+        <v>0.39</v>
       </c>
       <c r="H102" t="n">
-        <v>51.15</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.78</v>
+      </c>
+      <c r="I102" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.631</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5088,28 +5088,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E103" s="10" t="n">
-        <v>0.015</v>
+        <v>2.92</v>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>-0.0331</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>2211500</v>
+        <v>2350200</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
       <c r="H103" t="n">
-        <v>49.33</v>
+        <v>75.3</v>
       </c>
       <c r="I103" s="15" t="inlineStr">
         <is>
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.68</v>
+        <v>2.407</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.666</v>
+        <v>1.862</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5133,28 +5133,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>6.11</v>
+        <v>1.23</v>
       </c>
       <c r="E104" s="16" t="n">
-        <v>-0.0145</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>2174800</v>
+        <v>2329400</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.14</v>
+        <v>0.4</v>
       </c>
       <c r="H104" t="n">
-        <v>36.68</v>
+        <v>41.37</v>
       </c>
       <c r="I104" s="13" t="inlineStr">
         <is>
@@ -5162,10 +5162,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>6.263</v>
+        <v>1.26</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>6.462</v>
+        <v>1.298</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5178,39 +5178,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>7.31</v>
+        <v>12.88</v>
       </c>
       <c r="E105" s="16" t="n">
-        <v>-0.0188</v>
+        <v>-0.0062</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>2152600</v>
+        <v>2284100</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="H105" t="n">
-        <v>33.08</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.53</v>
+      </c>
+      <c r="I105" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>7.615</v>
+        <v>13.119</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>7.812</v>
+        <v>13.716</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5223,39 +5223,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="E106" s="16" t="n">
-        <v>-0.0046</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>0.018</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>2110600</v>
+        <v>2259400</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.25</v>
+        <v>1.01</v>
       </c>
       <c r="H106" t="n">
-        <v>37.04</v>
-      </c>
-      <c r="I106" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.15</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>13.121</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>13.717</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>IWCITY</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.595</v>
+        <v>0.21</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>0.05309999999999999</v>
+        <v>0.0244</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>2061300</v>
+        <v>2235500</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.71</v>
+        <v>2.55</v>
       </c>
       <c r="H107" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="I107" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.09</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.571</v>
+        <v>0.213</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.575</v>
+        <v>0.223</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5313,28 +5313,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>IWCITY</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>0.0488</v>
+        <v>6.09</v>
+      </c>
+      <c r="E108" s="16" t="n">
+        <v>-0.0177</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1950500</v>
+        <v>2231600</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>2.23</v>
+        <v>0.14</v>
       </c>
       <c r="H108" t="n">
-        <v>49.91</v>
+        <v>35.73</v>
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.213</v>
+        <v>6.261</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.223</v>
+        <v>6.461</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5358,39 +5358,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E109" s="17" t="n">
-        <v>0</v>
+        <v>7.31</v>
+      </c>
+      <c r="E109" s="16" t="n">
+        <v>-0.0188</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1947300</v>
+        <v>2176700</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.59</v>
+        <v>0.31</v>
       </c>
       <c r="H109" t="n">
-        <v>60.19</v>
-      </c>
-      <c r="I109" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.08</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.608</v>
+        <v>7.615</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.61</v>
+        <v>7.812</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5403,39 +5403,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E110" s="16" t="n">
-        <v>-0.0426</v>
+        <v>0.595</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>0.05309999999999999</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1929100</v>
+        <v>2061300</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1.16</v>
+        <v>0.71</v>
       </c>
       <c r="H110" t="n">
-        <v>39.46</v>
-      </c>
-      <c r="I110" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.7</v>
+      </c>
+      <c r="I110" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.238</v>
+        <v>0.571</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.243</v>
+        <v>0.575</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5448,28 +5448,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>1.09</v>
+        <v>0.645</v>
       </c>
       <c r="E111" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1894100</v>
+        <v>1948300</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.15</v>
+        <v>0.59</v>
       </c>
       <c r="H111" t="n">
-        <v>74.20999999999999</v>
+        <v>60.19</v>
       </c>
       <c r="I111" s="15" t="inlineStr">
         <is>
@@ -5477,10 +5477,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>1.026</v>
+        <v>0.608</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.868</v>
+        <v>0.61</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5493,39 +5493,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E112" s="16" t="n">
-        <v>-0.0206</v>
+        <v>1.09</v>
+      </c>
+      <c r="E112" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1888900</v>
+        <v>1933900</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="H112" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="I112" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.20999999999999</v>
+      </c>
+      <c r="I112" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>1.969</v>
+        <v>1.026</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>1.97</v>
+        <v>0.868</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5538,28 +5538,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>0.025</v>
+        <v>1.89</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>-0.0258</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1852100</v>
+        <v>1923800</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="H113" t="n">
-        <v>40.58</v>
+        <v>37.79</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>5.667</v>
+        <v>1.968</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>5.746</v>
+        <v>1.97</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5583,36 +5583,40 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E114" s="17" t="n">
-        <v>0</v>
+        <v>5.34</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>0.0269</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1821500</v>
+        <v>1922200</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.1</v>
+        <v>0.58</v>
       </c>
       <c r="H114" t="n">
-        <v>16.24</v>
+        <v>40.88</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J114" s="9" t="n"/>
-      <c r="K114" s="9" t="n"/>
+      <c r="J114" s="9" t="n">
+        <v>5.668</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>5.746</v>
+      </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
     </row>
@@ -5639,10 +5643,10 @@
         <v>-0.0144</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1814800</v>
+        <v>1875500</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H115" t="n">
         <v>82.15000000000001</v>
@@ -5684,10 +5688,10 @@
         <v>0</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1756300</v>
+        <v>1823300</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="H116" t="n">
         <v>62.32</v>
@@ -5714,40 +5718,36 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>0.0058</v>
+        <v>0.27</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1706000</v>
+        <v>1823100</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.57</v>
+        <v>0.1</v>
       </c>
       <c r="H117" t="n">
-        <v>55.77</v>
+        <v>16.24</v>
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J117" s="9" t="n">
-        <v>0.861</v>
-      </c>
-      <c r="K117" s="9" t="n">
-        <v>0.856</v>
-      </c>
+      <c r="J117" s="9" t="n"/>
+      <c r="K117" s="9" t="n"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
     </row>
@@ -5759,28 +5759,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E118" s="16" t="n">
-        <v>-0.0444</v>
+        <v>0.575</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>0.008800000000000001</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1691400</v>
+        <v>1707400</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.67</v>
+        <v>0.34</v>
       </c>
       <c r="H118" t="n">
-        <v>21.89</v>
+        <v>31.6</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.238</v>
+        <v>0.622</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.242</v>
+        <v>0.655</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5804,39 +5804,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1.08</v>
+        <v>0.865</v>
       </c>
       <c r="E119" s="10" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.0058</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1666800</v>
+        <v>1706000</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.34</v>
+        <v>0.57</v>
       </c>
       <c r="H119" t="n">
-        <v>72.45999999999999</v>
-      </c>
-      <c r="I119" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.77</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.001</v>
+        <v>0.861</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.831</v>
+        <v>0.856</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5849,28 +5849,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.22</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1640600</v>
+        <v>1701400</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="H120" t="n">
-        <v>31.6</v>
+        <v>24.44</v>
       </c>
       <c r="I120" s="13" t="inlineStr">
         <is>
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.622</v>
+        <v>0.239</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.655</v>
+        <v>0.242</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5894,28 +5894,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>2.59</v>
+        <v>1.08</v>
       </c>
       <c r="E121" s="10" t="n">
-        <v>0.0157</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1637900</v>
+        <v>1666800</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="H121" t="n">
-        <v>52.92</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="I121" s="15" t="inlineStr">
         <is>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>2.567</v>
+        <v>1.001</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>2.547</v>
+        <v>0.831</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5939,28 +5939,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.395</v>
+        <v>1.8</v>
       </c>
       <c r="E122" s="16" t="n">
-        <v>-0.0125</v>
+        <v>-0.0217</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1603700</v>
+        <v>1659600</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="H122" t="n">
-        <v>38.9</v>
+        <v>38.77</v>
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.407</v>
+        <v>1.879</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.411</v>
+        <v>1.955</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E123" s="16" t="n">
-        <v>-0.0097</v>
+        <v>2.6</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1594800</v>
+        <v>1638800</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="H123" t="n">
-        <v>42.99</v>
-      </c>
-      <c r="I123" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.93</v>
+      </c>
+      <c r="I123" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>1.068</v>
+        <v>2.568</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>1.025</v>
+        <v>2.547</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6029,28 +6029,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
         <v>0.395</v>
       </c>
-      <c r="E124" s="17" t="n">
-        <v>0</v>
+      <c r="E124" s="16" t="n">
+        <v>-0.0125</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1545300</v>
+        <v>1603700</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="H124" t="n">
-        <v>56.49</v>
+        <v>38.9</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -6058,10 +6058,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.384</v>
+        <v>0.407</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.327</v>
+        <v>0.411</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6074,39 +6074,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0396</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ADNEX</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>0.0235</v>
+        <v>1.02</v>
+      </c>
+      <c r="E125" s="16" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1525400</v>
+        <v>1595000</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>3.52</v>
+        <v>0.14</v>
       </c>
       <c r="H125" t="n">
-        <v>59.08</v>
-      </c>
-      <c r="I125" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.99</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.419</v>
+        <v>1.068</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.415</v>
+        <v>1.025</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6119,28 +6119,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E126" s="16" t="n">
-        <v>-0.0326</v>
+        <v>0.4</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1508800</v>
+        <v>1547500</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H126" t="n">
-        <v>37.11</v>
+        <v>57.7</v>
       </c>
       <c r="I126" s="13" t="inlineStr">
         <is>
@@ -6148,10 +6148,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>1.877</v>
+        <v>0.385</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>1.955</v>
+        <v>0.328</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6173,19 +6173,19 @@
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E127" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>1.28</v>
+      </c>
+      <c r="E127" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1452600</v>
+        <v>1543100</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H127" t="n">
-        <v>38.46</v>
+        <v>35.68</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>1.319</v>
+        <v>1.318</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>1.423</v>
@@ -6209,28 +6209,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0396</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>ADNEX</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.53</v>
+        <v>0.435</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>0.0095</v>
+        <v>0.0235</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1435600</v>
+        <v>1525400</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.77</v>
+        <v>3.52</v>
       </c>
       <c r="H128" t="n">
-        <v>58.46</v>
+        <v>59.08</v>
       </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.507</v>
+        <v>0.419</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.418</v>
+        <v>0.415</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6254,28 +6254,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.37</v>
+        <v>2.92</v>
       </c>
       <c r="E129" s="10" t="n">
-        <v>0.0137</v>
+        <v>0.0104</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1429400</v>
+        <v>1447900</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>1.03</v>
+        <v>0.49</v>
       </c>
       <c r="H129" t="n">
-        <v>41.85</v>
+        <v>43</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.383</v>
+        <v>2.981</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.391</v>
+        <v>3.037</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6299,39 +6299,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.48</v>
+        <v>4.68</v>
       </c>
       <c r="E130" s="16" t="n">
-        <v>-0.0103</v>
+        <v>-0.0064</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1408800</v>
+        <v>1440300</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.46</v>
+        <v>0.15</v>
       </c>
       <c r="H130" t="n">
-        <v>65.34999999999999</v>
-      </c>
-      <c r="I130" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.08</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.456</v>
+        <v>4.73</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.411</v>
+        <v>4.602</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6344,28 +6344,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0192</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E131" s="16" t="n">
-        <v>-0.0235</v>
+        <v>0.53</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>0.0095</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1362600</v>
+        <v>1435600</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="H131" t="n">
-        <v>60.59</v>
+        <v>58.46</v>
       </c>
       <c r="I131" s="15" t="inlineStr">
         <is>
@@ -6373,10 +6373,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.4</v>
+        <v>0.507</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.383</v>
+        <v>0.418</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6389,28 +6389,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E132" s="16" t="n">
-        <v>-0.0192</v>
+        <v>0.37</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>0.0137</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1352200</v>
+        <v>1429400</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.86</v>
+        <v>1.03</v>
       </c>
       <c r="H132" t="n">
-        <v>38.92</v>
+        <v>41.85</v>
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
@@ -6418,10 +6418,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.267</v>
+        <v>0.383</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.278</v>
+        <v>0.391</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6434,39 +6434,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>4.69</v>
+        <v>2.65</v>
       </c>
       <c r="E133" s="16" t="n">
-        <v>-0.0042</v>
+        <v>-0.0149</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1350600</v>
+        <v>1424900</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="H133" t="n">
-        <v>48.03</v>
-      </c>
-      <c r="I133" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.69</v>
+      </c>
+      <c r="I133" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>4.731</v>
+        <v>2.673</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>4.602</v>
+        <v>2.844</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6479,39 +6479,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>1.25</v>
+        <v>0.48</v>
       </c>
       <c r="E134" s="16" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1321100</v>
+        <v>1408800</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="H134" t="n">
-        <v>52.57</v>
-      </c>
-      <c r="I134" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.34999999999999</v>
+      </c>
+      <c r="I134" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>1.247</v>
+        <v>0.456</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>1.155</v>
+        <v>0.411</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6524,28 +6524,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0398</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>GDGROUP</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.385</v>
+        <v>2.92</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>0.0132</v>
+        <v>0.0318</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1286000</v>
+        <v>1408500</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>1.57</v>
+        <v>0.47</v>
       </c>
       <c r="H135" t="n">
-        <v>59.67</v>
+        <v>58.28</v>
       </c>
       <c r="I135" s="15" t="inlineStr">
         <is>
@@ -6553,10 +6553,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.378</v>
+        <v>2.807</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.38</v>
+        <v>2.716</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6569,39 +6569,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E136" s="16" t="n">
-        <v>-0.009300000000000001</v>
+        <v>1.26</v>
+      </c>
+      <c r="E136" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1258000</v>
+        <v>1373900</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.15</v>
+        <v>0.34</v>
       </c>
       <c r="H136" t="n">
-        <v>76.36</v>
-      </c>
-      <c r="I136" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.68</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.248</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.783</v>
+        <v>1.155</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6614,28 +6614,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.64</v>
+        <v>0.415</v>
       </c>
       <c r="E137" s="16" t="n">
-        <v>-0.0154</v>
+        <v>-0.0235</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1256200</v>
+        <v>1372600</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.32</v>
+        <v>0.61</v>
       </c>
       <c r="H137" t="n">
-        <v>56.18</v>
+        <v>60.59</v>
       </c>
       <c r="I137" s="15" t="inlineStr">
         <is>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>0.624</v>
+        <v>0.4</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>0.588</v>
+        <v>0.383</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6659,28 +6659,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E138" s="10" t="n">
-        <v>0.0179</v>
+        <v>0.255</v>
+      </c>
+      <c r="E138" s="16" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1246100</v>
+        <v>1352200</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.13</v>
+        <v>0.86</v>
       </c>
       <c r="H138" t="n">
-        <v>49.15</v>
+        <v>38.92</v>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>1.154</v>
+        <v>0.267</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>1.105</v>
+        <v>0.278</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6704,39 +6704,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E139" s="17" t="n">
-        <v>0</v>
+        <v>2.81</v>
+      </c>
+      <c r="E139" s="16" t="n">
+        <v>-0.031</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>1245200</v>
+        <v>1317400</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.42</v>
+        <v>0.51</v>
       </c>
       <c r="H139" t="n">
-        <v>39.66</v>
-      </c>
-      <c r="I139" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.05</v>
+      </c>
+      <c r="I139" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>2.978</v>
+        <v>2.417</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>3.036</v>
+        <v>2.016</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6749,28 +6749,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="E140" s="16" t="n">
-        <v>-0.031</v>
+        <v>0.385</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1238100</v>
+        <v>1286000</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.48</v>
+        <v>1.57</v>
       </c>
       <c r="H140" t="n">
-        <v>76.05</v>
+        <v>59.67</v>
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>2.417</v>
+        <v>0.378</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>2.016</v>
+        <v>0.38</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6794,28 +6794,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>7.64</v>
+        <v>0.635</v>
       </c>
       <c r="E141" s="16" t="n">
-        <v>-0.0243</v>
+        <v>-0.0231</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>1232600</v>
+        <v>1263700</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="H141" t="n">
-        <v>37.33</v>
+        <v>54.79</v>
       </c>
       <c r="I141" s="15" t="inlineStr">
         <is>
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>7.863</v>
+        <v>0.624</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>8.055999999999999</v>
+        <v>0.588</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6839,39 +6839,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.79</v>
+        <v>1.13</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>0.026</v>
+        <v>0.0089</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1222900</v>
+        <v>1261900</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="H142" t="n">
-        <v>74.75</v>
-      </c>
-      <c r="I142" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.6</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.7</v>
+        <v>1.153</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.631</v>
+        <v>1.105</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6884,39 +6884,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MAGMA</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.28</v>
+        <v>1.07</v>
       </c>
       <c r="E143" s="16" t="n">
-        <v>-0.0175</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1210300</v>
+        <v>1258400</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>2.16</v>
+        <v>0.15</v>
       </c>
       <c r="H143" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="I143" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.36</v>
+      </c>
+      <c r="I143" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.288</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.287</v>
+        <v>0.783</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6929,39 +6929,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>4.39</v>
+        <v>7.65</v>
       </c>
       <c r="E144" s="16" t="n">
-        <v>-0.0068</v>
+        <v>-0.023</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1194500</v>
+        <v>1235800</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="H144" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="I144" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.66</v>
+      </c>
+      <c r="I144" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>4.638</v>
+        <v>7.864</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>4.942</v>
+        <v>8.055999999999999</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6974,28 +6974,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>MAGMA</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E145" s="17" t="n">
-        <v>0</v>
+        <v>0.28</v>
+      </c>
+      <c r="E145" s="16" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1188400</v>
+        <v>1210300</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.3</v>
+        <v>2.16</v>
       </c>
       <c r="H145" t="n">
-        <v>33.33</v>
+        <v>28.6</v>
       </c>
       <c r="I145" s="13" t="inlineStr">
         <is>
@@ -7003,10 +7003,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>0.582</v>
+        <v>0.288</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>0.586</v>
+        <v>0.287</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7019,28 +7019,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E146" s="16" t="n">
-        <v>-0.0192</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E146" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1180900</v>
+        <v>1201700</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>1.39</v>
+        <v>0.3</v>
       </c>
       <c r="H146" t="n">
-        <v>37.88</v>
+        <v>33.33</v>
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>0.26</v>
+        <v>0.582</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>0.265</v>
+        <v>0.586</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7064,39 +7064,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E147" s="10" t="n">
-        <v>0.0283</v>
+        <v>4.38</v>
+      </c>
+      <c r="E147" s="16" t="n">
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>1163800</v>
+        <v>1198200</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
       <c r="H147" t="n">
-        <v>57.82</v>
-      </c>
-      <c r="I147" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.36</v>
+      </c>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>2.806</v>
+        <v>4.637</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>2.716</v>
+        <v>4.941</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7109,39 +7109,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E148" s="10" t="n">
-        <v>0.011</v>
+        <v>0.255</v>
+      </c>
+      <c r="E148" s="16" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>1156400</v>
+        <v>1180900</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.62</v>
+        <v>1.39</v>
       </c>
       <c r="H148" t="n">
-        <v>53.95</v>
-      </c>
-      <c r="I148" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.88</v>
+      </c>
+      <c r="I148" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>0.459</v>
+        <v>0.265</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7154,28 +7154,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E149" s="16" t="n">
-        <v>-0.0196</v>
+        <v>0.46</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>0.011</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>1140000</v>
+        <v>1156500</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.41</v>
+        <v>0.62</v>
       </c>
       <c r="H149" t="n">
-        <v>45.48</v>
+        <v>53.95</v>
       </c>
       <c r="I149" s="15" t="inlineStr">
         <is>
@@ -7183,10 +7183,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>0.254</v>
+        <v>0.45</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>0.267</v>
+        <v>0.459</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7199,33 +7199,40 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>0.255</v>
+        <v>0.365</v>
       </c>
       <c r="E150" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>1118400</v>
+        <v>1146400</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I150" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J150" s="9" t="n"/>
-      <c r="K150" s="9" t="n"/>
+        <v>0.27</v>
+      </c>
+      <c r="H150" t="n">
+        <v>40.94</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>0.389</v>
+      </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
     </row>
@@ -7237,28 +7244,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>1.02</v>
+        <v>0.25</v>
       </c>
       <c r="E151" s="16" t="n">
-        <v>-0.0192</v>
+        <v>-0.0196</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>1110600</v>
+        <v>1140000</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.7</v>
+        <v>0.41</v>
       </c>
       <c r="H151" t="n">
-        <v>49.14</v>
+        <v>45.48</v>
       </c>
       <c r="I151" s="15" t="inlineStr">
         <is>
@@ -7266,10 +7273,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>1.029</v>
+        <v>0.254</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>1.018</v>
+        <v>0.267</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7282,28 +7289,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>1.4</v>
+        <v>0.735</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>0.0219</v>
+        <v>0.0138</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>1108200</v>
+        <v>1136300</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.35</v>
+        <v>0.68</v>
       </c>
       <c r="H152" t="n">
-        <v>58.41</v>
+        <v>49.47</v>
       </c>
       <c r="I152" s="13" t="inlineStr">
         <is>
@@ -7311,10 +7318,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>1.355</v>
+        <v>0.732</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>1.18</v>
+        <v>0.751</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7327,28 +7334,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E153" s="16" t="n">
-        <v>-0.017</v>
+        <v>1.38</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>0.0073</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>1099200</v>
+        <v>1135400</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.9</v>
+        <v>0.35</v>
       </c>
       <c r="H153" t="n">
-        <v>26.06</v>
+        <v>56.65</v>
       </c>
       <c r="I153" s="13" t="inlineStr">
         <is>
@@ -7356,10 +7363,10 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>3.034</v>
+        <v>1.353</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>3.136</v>
+        <v>1.18</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7372,39 +7379,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E154" s="17" t="n">
-        <v>0</v>
+        <v>1.02</v>
+      </c>
+      <c r="E154" s="16" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>1096400</v>
+        <v>1130000</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.16</v>
+        <v>0.72</v>
       </c>
       <c r="H154" t="n">
-        <v>44.64</v>
-      </c>
-      <c r="I154" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.14</v>
+      </c>
+      <c r="I154" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>2.205</v>
+        <v>1.029</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>2.11</v>
+        <v>1.018</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7417,39 +7424,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E155" s="17" t="n">
-        <v>0</v>
+        <v>0.645</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>0.032</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>1091400</v>
+        <v>1124200</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.26</v>
+        <v>0.98</v>
       </c>
       <c r="H155" t="n">
-        <v>40.94</v>
-      </c>
-      <c r="I155" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.42</v>
+      </c>
+      <c r="I155" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>0.374</v>
+        <v>0.628</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>0.389</v>
+        <v>0.605</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7462,40 +7469,33 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>0.905</v>
+        <v>0.255</v>
       </c>
       <c r="E156" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>1087500</v>
+        <v>1118400</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="H156" t="n">
-        <v>39.41</v>
+        <v>0.08</v>
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J156" s="9" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="K156" s="9" t="n">
-        <v>0.969</v>
-      </c>
+      <c r="J156" s="9" t="n"/>
+      <c r="K156" s="9" t="n"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
     </row>
@@ -7507,39 +7507,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>2.64</v>
+        <v>3.42</v>
       </c>
       <c r="E157" s="16" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>1076700</v>
+        <v>1106300</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="H157" t="n">
-        <v>43.88</v>
-      </c>
-      <c r="I157" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.35</v>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>2.672</v>
+        <v>3.567</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>2.844</v>
+        <v>3.689</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7552,28 +7552,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>TAKAFUL</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>3.41</v>
+        <v>2.9</v>
       </c>
       <c r="E158" s="16" t="n">
-        <v>-0.0145</v>
+        <v>-0.0136</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>1055400</v>
+        <v>1105900</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.18</v>
+        <v>0.9</v>
       </c>
       <c r="H158" t="n">
-        <v>34.83</v>
+        <v>26.77</v>
       </c>
       <c r="I158" s="13" t="inlineStr">
         <is>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>3.566</v>
+        <v>3.035</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>3.689</v>
+        <v>3.136</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7597,28 +7597,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>1.02</v>
+        <v>0.495</v>
       </c>
       <c r="E159" s="10" t="n">
-        <v>0.0515</v>
+        <v>0.0313</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>1038700</v>
+        <v>1105500</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>1.77</v>
+        <v>0.85</v>
       </c>
       <c r="H159" t="n">
-        <v>62.33</v>
+        <v>57.63</v>
       </c>
       <c r="I159" s="15" t="inlineStr">
         <is>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>0.985</v>
+        <v>0.475</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>0.976</v>
+        <v>0.471</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7642,28 +7642,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E160" s="10" t="n">
-        <v>0.04</v>
+        <v>0.905</v>
+      </c>
+      <c r="E160" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>1035600</v>
+        <v>1101900</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.9</v>
+        <v>0.35</v>
       </c>
       <c r="H160" t="n">
-        <v>58.77</v>
+        <v>39.41</v>
       </c>
       <c r="I160" s="15" t="inlineStr">
         <is>
@@ -7671,10 +7671,10 @@
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>0.629</v>
+        <v>0.923</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>0.605</v>
+        <v>0.969</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7687,28 +7687,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E161" s="10" t="n">
-        <v>0.0069</v>
+        <v>2.12</v>
+      </c>
+      <c r="E161" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1006600</v>
+        <v>1101800</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.6</v>
+        <v>0.16</v>
       </c>
       <c r="H161" t="n">
-        <v>47.51</v>
+        <v>44.64</v>
       </c>
       <c r="I161" s="13" t="inlineStr">
         <is>
@@ -7716,10 +7716,10 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>0.732</v>
+        <v>2.205</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>0.75</v>
+        <v>2.11</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7732,39 +7732,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>5.56</v>
+        <v>0.62</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>0.0202</v>
+        <v>0.0164</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>998100</v>
+        <v>1066400</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="H162" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="I162" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.19</v>
+      </c>
+      <c r="I162" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>5.629</v>
+        <v>0.631</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>6.035</v>
+        <v>0.636</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7792,10 +7792,10 @@
         <v>-0.0025</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>974500</v>
+        <v>1042800</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="H163" t="n">
         <v>61.58</v>
@@ -7822,28 +7822,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>10</v>
+        <v>1.02</v>
       </c>
       <c r="E164" s="10" t="n">
-        <v>0.0091</v>
+        <v>0.0515</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>967000</v>
+        <v>1038700</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.28</v>
+        <v>1.77</v>
       </c>
       <c r="H164" t="n">
-        <v>65.12</v>
+        <v>62.33</v>
       </c>
       <c r="I164" s="15" t="inlineStr">
         <is>
@@ -7851,10 +7851,10 @@
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>9.647</v>
+        <v>0.985</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>9.19</v>
+        <v>0.976</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7867,39 +7867,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E165" s="16" t="n">
-        <v>-0.008</v>
+        <v>5.56</v>
+      </c>
+      <c r="E165" s="10" t="n">
+        <v>0.0202</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>956400</v>
+        <v>1002600</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.32</v>
+        <v>0.53</v>
       </c>
       <c r="H165" t="n">
-        <v>33</v>
-      </c>
-      <c r="I165" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.4</v>
+      </c>
+      <c r="I165" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>1.36</v>
+        <v>5.629</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>1.317</v>
+        <v>6.035</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7912,39 +7912,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="E166" s="16" t="n">
-        <v>-0.0052</v>
+        <v>-0.0049</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>953900</v>
+        <v>979700</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
       <c r="H166" t="n">
-        <v>37.36</v>
-      </c>
-      <c r="I166" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.98</v>
+      </c>
+      <c r="I166" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>0.99</v>
+        <v>2.059</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>1.04</v>
+        <v>2.098</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7957,39 +7957,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="E167" s="17" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="E167" s="10" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>924200</v>
+        <v>975400</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="H167" t="n">
-        <v>37.69</v>
-      </c>
-      <c r="I167" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.12</v>
+      </c>
+      <c r="I167" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>1.939</v>
+        <v>9.647</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>2.061</v>
+        <v>9.19</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8002,28 +8002,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>0.615</v>
+        <v>1.9</v>
       </c>
       <c r="E168" s="10" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.0053</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>916000</v>
+        <v>964000</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.38</v>
+        <v>0.22</v>
       </c>
       <c r="H168" t="n">
-        <v>41.77</v>
+        <v>39.51</v>
       </c>
       <c r="I168" s="13" t="inlineStr">
         <is>
@@ -8031,10 +8031,10 @@
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>0.631</v>
+        <v>1.94</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>0.636</v>
+        <v>2.061</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8047,28 +8047,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="E169" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>885800</v>
+        <v>963100</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="H169" t="n">
-        <v>36.18</v>
+        <v>33.9</v>
       </c>
       <c r="I169" s="13" t="inlineStr">
         <is>
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>1.955</v>
+        <v>1.361</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>2.064</v>
+        <v>1.318</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8092,28 +8092,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>1.74</v>
+        <v>0.96</v>
       </c>
       <c r="E170" s="16" t="n">
-        <v>-0.0333</v>
+        <v>-0.0052</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>880600</v>
+        <v>953900</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.67</v>
+        <v>0.22</v>
       </c>
       <c r="H170" t="n">
-        <v>26.45</v>
+        <v>37.36</v>
       </c>
       <c r="I170" s="13" t="inlineStr">
         <is>
@@ -8121,10 +8121,10 @@
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>1.875</v>
+        <v>0.99</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>1.952</v>
+        <v>1.04</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8137,28 +8137,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1.39</v>
+        <v>1.91</v>
       </c>
       <c r="E171" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>879000</v>
+        <v>895400</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.44</v>
+        <v>0.29</v>
       </c>
       <c r="H171" t="n">
-        <v>65.20999999999999</v>
+        <v>36.18</v>
       </c>
       <c r="I171" s="13" t="inlineStr">
         <is>
@@ -8166,10 +8166,10 @@
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>1.365</v>
+        <v>1.955</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>1.329</v>
+        <v>2.064</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8182,39 +8182,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>7.97</v>
+        <v>1.74</v>
       </c>
       <c r="E172" s="16" t="n">
-        <v>-0.005</v>
+        <v>-0.0333</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>853600</v>
+        <v>881300</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.23</v>
+        <v>0.67</v>
       </c>
       <c r="H172" t="n">
-        <v>55.94</v>
-      </c>
-      <c r="I172" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.45</v>
+      </c>
+      <c r="I172" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>7.894</v>
+        <v>1.875</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>7.819</v>
+        <v>1.952</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8227,39 +8227,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>TMK</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="E173" s="17" t="n">
-        <v>0</v>
+        <v>2.87</v>
+      </c>
+      <c r="E173" s="10" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>846700</v>
+        <v>880600</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.29</v>
+        <v>0.68</v>
       </c>
       <c r="H173" t="n">
-        <v>45.89</v>
-      </c>
-      <c r="I173" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.9</v>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>2.06</v>
+        <v>2.946</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>2.099</v>
+        <v>2.828</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8272,28 +8272,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="E174" s="16" t="n">
-        <v>-0.0117</v>
+        <v>1.39</v>
+      </c>
+      <c r="E174" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>821200</v>
+        <v>879000</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.24</v>
+        <v>0.44</v>
       </c>
       <c r="H174" t="n">
-        <v>30.61</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="I174" s="13" t="inlineStr">
         <is>
@@ -8301,10 +8301,10 @@
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>2.645</v>
+        <v>1.365</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>2.769</v>
+        <v>1.329</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8317,28 +8317,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>0.835</v>
+        <v>0.635</v>
       </c>
       <c r="E175" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>817700</v>
+        <v>871300</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.26</v>
+        <v>0.62</v>
       </c>
       <c r="H175" t="n">
-        <v>61.34</v>
+        <v>52.65</v>
       </c>
       <c r="I175" s="15" t="inlineStr">
         <is>
@@ -8346,10 +8346,10 @@
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.634</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>0.733</v>
+        <v>0.629</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8362,39 +8362,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E176" s="10" t="n">
-        <v>0.0177</v>
+        <v>7.96</v>
+      </c>
+      <c r="E176" s="16" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>800300</v>
+        <v>865100</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.62</v>
+        <v>0.24</v>
       </c>
       <c r="H176" t="n">
-        <v>46.67</v>
-      </c>
-      <c r="I176" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.31</v>
+      </c>
+      <c r="I176" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>2.947</v>
+        <v>7.893</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>2.829</v>
+        <v>7.819</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8407,28 +8407,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E177" s="17" t="n">
-        <v>0</v>
+        <v>0.83</v>
+      </c>
+      <c r="E177" s="16" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>791300</v>
+        <v>848900</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="H177" t="n">
-        <v>52.65</v>
+        <v>59.82</v>
       </c>
       <c r="I177" s="15" t="inlineStr">
         <is>
@@ -8436,10 +8436,10 @@
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>0.634</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>0.629</v>
+        <v>0.733</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8452,39 +8452,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>0.63</v>
+        <v>2.1</v>
       </c>
       <c r="E178" s="16" t="n">
-        <v>-0.0156</v>
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>760300</v>
+        <v>831000</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="H178" t="n">
-        <v>52.49</v>
-      </c>
-      <c r="I178" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.88</v>
+      </c>
+      <c r="I178" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>0.634</v>
+        <v>2.07</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>0.598</v>
+        <v>2.012</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8497,39 +8497,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>2.1</v>
+        <v>2.54</v>
       </c>
       <c r="E179" s="16" t="n">
-        <v>-0.004699999999999999</v>
+        <v>-0.0117</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>749300</v>
+        <v>822000</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="H179" t="n">
-        <v>54.88</v>
-      </c>
-      <c r="I179" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.61</v>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>2.07</v>
+        <v>2.645</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>2.012</v>
+        <v>2.769</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8551,19 +8551,19 @@
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="E180" s="10" t="n">
-        <v>0.0312</v>
+        <v>0.0375</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>746600</v>
+        <v>796600</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="H180" t="n">
-        <v>61.61</v>
+        <v>63.33</v>
       </c>
       <c r="I180" s="13" t="inlineStr">
         <is>
@@ -8571,10 +8571,10 @@
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>1.604</v>
+        <v>1.605</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>1.6</v>
+        <v>1.601</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
@@ -8587,28 +8587,28 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E181" s="16" t="n">
-        <v>-0.0146</v>
+        <v>1.07</v>
+      </c>
+      <c r="E181" s="10" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>720100</v>
+        <v>761700</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="H181" t="n">
-        <v>76.53</v>
+        <v>44.6</v>
       </c>
       <c r="I181" s="15" t="inlineStr">
         <is>
@@ -8616,10 +8616,10 @@
         </is>
       </c>
       <c r="J181" s="9" t="n">
-        <v>0.59</v>
+        <v>1.09</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>0.505</v>
+        <v>1.119</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="14" t="inlineStr"/>
@@ -8632,28 +8632,28 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D182" s="9" t="n">
-        <v>0.915</v>
+        <v>0.63</v>
       </c>
       <c r="E182" s="16" t="n">
-        <v>-0.0054</v>
+        <v>-0.0156</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>719300</v>
+        <v>760300</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="H182" t="n">
-        <v>31.12</v>
+        <v>52.49</v>
       </c>
       <c r="I182" s="13" t="inlineStr">
         <is>
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="J182" s="9" t="n">
-        <v>1.012</v>
+        <v>0.634</v>
       </c>
       <c r="K182" s="9" t="n">
-        <v>1.019</v>
+        <v>0.598</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="14" t="inlineStr"/>
@@ -8677,28 +8677,28 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0366</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ICENTS</t>
+          <t>MAXIS</t>
         </is>
       </c>
       <c r="D183" s="9" t="n">
-        <v>0.82</v>
+        <v>3.49</v>
       </c>
       <c r="E183" s="16" t="n">
-        <v>-0.0238</v>
+        <v>-0.0197</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>712700</v>
+        <v>754200</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="H183" t="n">
-        <v>52.02</v>
+        <v>41.11</v>
       </c>
       <c r="I183" s="13" t="inlineStr">
         <is>
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="J183" s="9" t="n">
-        <v>0.827</v>
+        <v>3.562</v>
       </c>
       <c r="K183" s="9" t="n">
-        <v>0.744</v>
+        <v>3.604</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="14" t="inlineStr"/>
@@ -8722,28 +8722,28 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>GESHEN</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D184" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E184" s="10" t="n">
-        <v>0.0182</v>
+        <v>0.915</v>
+      </c>
+      <c r="E184" s="16" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>709900</v>
+        <v>728800</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>1.63</v>
+        <v>0.31</v>
       </c>
       <c r="H184" t="n">
-        <v>35.18</v>
+        <v>31.12</v>
       </c>
       <c r="I184" s="13" t="inlineStr">
         <is>
@@ -8751,10 +8751,10 @@
         </is>
       </c>
       <c r="J184" s="9" t="n">
-        <v>1.16</v>
+        <v>1.012</v>
       </c>
       <c r="K184" s="9" t="n">
-        <v>1.267</v>
+        <v>1.019</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="14" t="inlineStr"/>
@@ -8767,39 +8767,39 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>MAXIS</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D185" s="9" t="n">
-        <v>3.47</v>
+        <v>0.675</v>
       </c>
       <c r="E185" s="16" t="n">
-        <v>-0.0253</v>
+        <v>-0.0146</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>701200</v>
+        <v>724100</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="H185" t="n">
-        <v>39.46</v>
-      </c>
-      <c r="I185" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.53</v>
+      </c>
+      <c r="I185" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J185" s="9" t="n">
-        <v>3.56</v>
+        <v>0.59</v>
       </c>
       <c r="K185" s="9" t="n">
-        <v>3.604</v>
+        <v>0.505</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="14" t="inlineStr"/>
@@ -8812,28 +8812,28 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>PADINI</t>
         </is>
       </c>
       <c r="D186" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E186" s="17" t="n">
-        <v>0</v>
+        <v>1.03</v>
+      </c>
+      <c r="E186" s="10" t="n">
+        <v>0.0198</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>700000</v>
+        <v>723700</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="H186" t="n">
-        <v>41.61</v>
+        <v>35.46</v>
       </c>
       <c r="I186" s="13" t="inlineStr">
         <is>
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="J186" s="9" t="n">
-        <v>0.63</v>
+        <v>1.07</v>
       </c>
       <c r="K186" s="9" t="n">
-        <v>0.636</v>
+        <v>1.241</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="14" t="inlineStr"/>
@@ -8857,39 +8857,39 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0366</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>ICENTS</t>
         </is>
       </c>
       <c r="D187" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E187" s="10" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.82</v>
+      </c>
+      <c r="E187" s="16" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>696700</v>
+        <v>713600</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="H187" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="I187" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.02</v>
+      </c>
+      <c r="I187" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J187" s="9" t="n">
-        <v>1.09</v>
+        <v>0.827</v>
       </c>
       <c r="K187" s="9" t="n">
-        <v>1.119</v>
+        <v>0.744</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="14" t="inlineStr"/>
@@ -8902,28 +8902,28 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>GESHEN</t>
         </is>
       </c>
       <c r="D188" s="9" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="E188" s="16" t="n">
-        <v>-0.0016</v>
+        <v>1.12</v>
+      </c>
+      <c r="E188" s="10" t="n">
+        <v>0.0182</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>681200</v>
+        <v>709900</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>0.15</v>
+        <v>1.63</v>
       </c>
       <c r="H188" t="n">
-        <v>24.95</v>
+        <v>35.18</v>
       </c>
       <c r="I188" s="13" t="inlineStr">
         <is>
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="J188" s="9" t="n">
-        <v>6.642</v>
+        <v>1.16</v>
       </c>
       <c r="K188" s="9" t="n">
-        <v>6.87</v>
+        <v>1.267</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" s="14" t="inlineStr"/>
@@ -8947,28 +8947,28 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D189" s="9" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="E189" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.625</v>
+      </c>
+      <c r="E189" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>670700</v>
+        <v>700000</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>0.26</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H189" t="n">
-        <v>44.39</v>
+        <v>41.61</v>
       </c>
       <c r="I189" s="13" t="inlineStr">
         <is>
@@ -8976,10 +8976,10 @@
         </is>
       </c>
       <c r="J189" s="9" t="n">
-        <v>4.357</v>
+        <v>0.63</v>
       </c>
       <c r="K189" s="9" t="n">
-        <v>4.4</v>
+        <v>0.636</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" s="14" t="inlineStr"/>
@@ -8992,28 +8992,28 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>WCEHB</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D190" s="9" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E190" s="16" t="n">
-        <v>-0.006999999999999999</v>
+        <v>4.22</v>
+      </c>
+      <c r="E190" s="10" t="n">
+        <v>0.009599999999999999</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>634300</v>
+        <v>690100</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>1.23</v>
+        <v>0.26</v>
       </c>
       <c r="H190" t="n">
-        <v>51.2</v>
+        <v>44.77</v>
       </c>
       <c r="I190" s="13" t="inlineStr">
         <is>
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="J190" s="9" t="n">
-        <v>0.705</v>
+        <v>4.358</v>
       </c>
       <c r="K190" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>4.401</v>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" s="14" t="inlineStr"/>
@@ -9037,28 +9037,28 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D191" s="9" t="n">
-        <v>0.925</v>
+        <v>6.37</v>
       </c>
       <c r="E191" s="16" t="n">
-        <v>-0.016</v>
+        <v>-0.0016</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>630500</v>
+        <v>686700</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>0.68</v>
+        <v>0.15</v>
       </c>
       <c r="H191" t="n">
-        <v>21.85</v>
+        <v>24.95</v>
       </c>
       <c r="I191" s="13" t="inlineStr">
         <is>
@@ -9066,10 +9066,10 @@
         </is>
       </c>
       <c r="J191" s="9" t="n">
-        <v>0.968</v>
+        <v>6.642</v>
       </c>
       <c r="K191" s="9" t="n">
-        <v>1.004</v>
+        <v>6.87</v>
       </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" s="14" t="inlineStr"/>
@@ -9082,39 +9082,39 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>PADINI</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D192" s="9" t="n">
-        <v>1.03</v>
+        <v>0.785</v>
       </c>
       <c r="E192" s="10" t="n">
-        <v>0.0198</v>
+        <v>0.0195</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>623400</v>
+        <v>658100</v>
       </c>
       <c r="G192" s="12" t="n">
         <v>0.25</v>
       </c>
       <c r="H192" t="n">
-        <v>35.46</v>
-      </c>
-      <c r="I192" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.81</v>
+      </c>
+      <c r="I192" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J192" s="9" t="n">
-        <v>1.07</v>
+        <v>0.761</v>
       </c>
       <c r="K192" s="9" t="n">
-        <v>1.241</v>
+        <v>0.742</v>
       </c>
       <c r="L192" t="inlineStr"/>
       <c r="M192" s="14" t="inlineStr"/>
@@ -9127,39 +9127,39 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>WELLCAL</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="D193" s="9" t="n">
-        <v>1.12</v>
+        <v>0.925</v>
       </c>
       <c r="E193" s="16" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.016</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>590200</v>
+        <v>640500</v>
       </c>
       <c r="G193" s="12" t="n">
-        <v>2.41</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H193" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="I193" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.85</v>
+      </c>
+      <c r="I193" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J193" s="9" t="n">
-        <v>1.116</v>
+        <v>0.968</v>
       </c>
       <c r="K193" s="9" t="n">
-        <v>1.113</v>
+        <v>1.004</v>
       </c>
       <c r="L193" t="inlineStr"/>
       <c r="M193" s="14" t="inlineStr"/>
@@ -9172,28 +9172,28 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>0308</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>KTI</t>
+          <t>WCEHB</t>
         </is>
       </c>
       <c r="D194" s="9" t="n">
-        <v>0.515</v>
+        <v>0.705</v>
       </c>
       <c r="E194" s="16" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>584800</v>
+        <v>634300</v>
       </c>
       <c r="G194" s="12" t="n">
-        <v>2.05</v>
+        <v>1.23</v>
       </c>
       <c r="H194" t="n">
-        <v>44.4</v>
+        <v>51.2</v>
       </c>
       <c r="I194" s="13" t="inlineStr">
         <is>
@@ -9201,10 +9201,10 @@
         </is>
       </c>
       <c r="J194" s="9" t="n">
-        <v>0.52</v>
+        <v>0.705</v>
       </c>
       <c r="K194" s="9" t="n">
-        <v>0.529</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L194" t="inlineStr"/>
       <c r="M194" s="14" t="inlineStr"/>
@@ -9217,39 +9217,39 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>SENTRAL</t>
+          <t>WELLCAL</t>
         </is>
       </c>
       <c r="D195" s="9" t="n">
-        <v>0.64</v>
+        <v>1.12</v>
       </c>
       <c r="E195" s="16" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>566800</v>
+        <v>590200</v>
       </c>
       <c r="G195" s="12" t="n">
-        <v>0.78</v>
+        <v>2.41</v>
       </c>
       <c r="H195" t="n">
-        <v>33.82</v>
-      </c>
-      <c r="I195" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.95</v>
+      </c>
+      <c r="I195" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J195" s="9" t="n">
-        <v>0.658</v>
+        <v>1.116</v>
       </c>
       <c r="K195" s="9" t="n">
-        <v>0.677</v>
+        <v>1.113</v>
       </c>
       <c r="L195" t="inlineStr"/>
       <c r="M195" s="14" t="inlineStr"/>
@@ -9262,39 +9262,39 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MKH</t>
         </is>
       </c>
       <c r="D196" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E196" s="10" t="n">
-        <v>0.005500000000000001</v>
+        <v>1.99</v>
+      </c>
+      <c r="E196" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>546800</v>
+        <v>589000</v>
       </c>
       <c r="G196" s="12" t="n">
-        <v>0.3</v>
+        <v>0.91</v>
       </c>
       <c r="H196" t="n">
-        <v>54.73</v>
-      </c>
-      <c r="I196" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.76000000000001</v>
+      </c>
+      <c r="I196" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J196" s="9" t="n">
-        <v>0.908</v>
+        <v>1.989</v>
       </c>
       <c r="K196" s="9" t="n">
-        <v>0.801</v>
+        <v>1.982</v>
       </c>
       <c r="L196" t="inlineStr"/>
       <c r="M196" s="14" t="inlineStr"/>
@@ -9307,39 +9307,39 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0308</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>KTI</t>
         </is>
       </c>
       <c r="D197" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E197" s="10" t="n">
-        <v>0.013</v>
+        <v>0.515</v>
+      </c>
+      <c r="E197" s="16" t="n">
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>544600</v>
+        <v>584800</v>
       </c>
       <c r="G197" s="12" t="n">
-        <v>0.21</v>
+        <v>2.05</v>
       </c>
       <c r="H197" t="n">
-        <v>55.79</v>
-      </c>
-      <c r="I197" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.4</v>
+      </c>
+      <c r="I197" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J197" s="9" t="n">
-        <v>0.761</v>
+        <v>0.52</v>
       </c>
       <c r="K197" s="9" t="n">
-        <v>0.742</v>
+        <v>0.529</v>
       </c>
       <c r="L197" t="inlineStr"/>
       <c r="M197" s="14" t="inlineStr"/>
@@ -9352,39 +9352,39 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>E&amp;O</t>
+          <t>SENTRAL</t>
         </is>
       </c>
       <c r="D198" s="9" t="n">
-        <v>0.77</v>
+        <v>0.645</v>
       </c>
       <c r="E198" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>540400</v>
+        <v>570100</v>
       </c>
       <c r="G198" s="12" t="n">
-        <v>0.37</v>
+        <v>0.79</v>
       </c>
       <c r="H198" t="n">
-        <v>49.44</v>
-      </c>
-      <c r="I198" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.35</v>
+      </c>
+      <c r="I198" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J198" s="9" t="n">
-        <v>0.773</v>
+        <v>0.658</v>
       </c>
       <c r="K198" s="9" t="n">
-        <v>0.765</v>
+        <v>0.677</v>
       </c>
       <c r="L198" t="inlineStr"/>
       <c r="M198" s="14" t="inlineStr"/>
@@ -9397,39 +9397,39 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>THETA</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D199" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E199" s="17" t="n">
-        <v>0</v>
+        <v>0.92</v>
+      </c>
+      <c r="E199" s="10" t="n">
+        <v>0.011</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>536100</v>
+        <v>549300</v>
       </c>
       <c r="G199" s="12" t="n">
-        <v>0.49</v>
+        <v>0.31</v>
       </c>
       <c r="H199" t="n">
-        <v>45.65</v>
-      </c>
-      <c r="I199" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.47</v>
+      </c>
+      <c r="I199" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J199" s="9" t="n">
-        <v>0.646</v>
+        <v>0.909</v>
       </c>
       <c r="K199" s="9" t="n">
-        <v>0.659</v>
+        <v>0.801</v>
       </c>
       <c r="L199" t="inlineStr"/>
       <c r="M199" s="14" t="inlineStr"/>
@@ -9442,39 +9442,39 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>E&amp;O</t>
         </is>
       </c>
       <c r="D200" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E200" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.77</v>
+      </c>
+      <c r="E200" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>531300</v>
+        <v>540400</v>
       </c>
       <c r="G200" s="12" t="n">
-        <v>0.28</v>
+        <v>0.37</v>
       </c>
       <c r="H200" t="n">
-        <v>39.26</v>
-      </c>
-      <c r="I200" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.44</v>
+      </c>
+      <c r="I200" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J200" s="9" t="n">
-        <v>0.986</v>
+        <v>0.773</v>
       </c>
       <c r="K200" s="9" t="n">
-        <v>1.006</v>
+        <v>0.765</v>
       </c>
       <c r="L200" t="inlineStr"/>
       <c r="M200" s="14" t="inlineStr"/>
@@ -9487,28 +9487,28 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>MKH</t>
+          <t>THETA</t>
         </is>
       </c>
       <c r="D201" s="9" t="n">
-        <v>1.99</v>
+        <v>0.63</v>
       </c>
       <c r="E201" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>527100</v>
+        <v>536100</v>
       </c>
       <c r="G201" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="H201" t="n">
-        <v>65.76000000000001</v>
+        <v>45.65</v>
       </c>
       <c r="I201" s="13" t="inlineStr">
         <is>
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="J201" s="9" t="n">
-        <v>1.989</v>
+        <v>0.646</v>
       </c>
       <c r="K201" s="9" t="n">
-        <v>1.982</v>
+        <v>0.659</v>
       </c>
       <c r="L201" t="inlineStr"/>
       <c r="M201" s="14" t="inlineStr"/>
@@ -9532,28 +9532,28 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D202" s="9" t="n">
-        <v>1.48</v>
+        <v>0.96</v>
       </c>
       <c r="E202" s="10" t="n">
-        <v>0.0068</v>
+        <v>0.0052</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>515800</v>
+        <v>532100</v>
       </c>
       <c r="G202" s="12" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="H202" t="n">
-        <v>30.94</v>
+        <v>39.26</v>
       </c>
       <c r="I202" s="13" t="inlineStr">
         <is>
@@ -9561,10 +9561,10 @@
         </is>
       </c>
       <c r="J202" s="9" t="n">
-        <v>1.54</v>
+        <v>0.986</v>
       </c>
       <c r="K202" s="9" t="n">
-        <v>1.655</v>
+        <v>1.006</v>
       </c>
       <c r="L202" t="inlineStr"/>
       <c r="M202" s="14" t="inlineStr"/>
@@ -9577,28 +9577,28 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D203" s="9" t="n">
-        <v>1.57</v>
+        <v>0.97</v>
       </c>
       <c r="E203" s="16" t="n">
-        <v>-0.0126</v>
+        <v>-0.0051</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>507800</v>
+        <v>520800</v>
       </c>
       <c r="G203" s="12" t="n">
-        <v>0.55</v>
+        <v>0.11</v>
       </c>
       <c r="H203" t="n">
-        <v>40.66</v>
+        <v>29.84</v>
       </c>
       <c r="I203" s="13" t="inlineStr">
         <is>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="J203" s="9" t="n">
-        <v>1.634</v>
+        <v>1.029</v>
       </c>
       <c r="K203" s="9" t="n">
-        <v>1.706</v>
+        <v>1.075</v>
       </c>
       <c r="L203" t="inlineStr"/>
       <c r="M203" s="14" t="inlineStr"/>
@@ -9622,28 +9622,28 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>AEONCR</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D204" s="9" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="E204" s="16" t="n">
-        <v>-0.0179</v>
+        <v>1.48</v>
+      </c>
+      <c r="E204" s="10" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>503100</v>
+        <v>519600</v>
       </c>
       <c r="G204" s="12" t="n">
-        <v>1.13</v>
+        <v>0.22</v>
       </c>
       <c r="H204" t="n">
-        <v>22.07</v>
+        <v>30.94</v>
       </c>
       <c r="I204" s="13" t="inlineStr">
         <is>
@@ -9651,16 +9651,106 @@
         </is>
       </c>
       <c r="J204" s="9" t="n">
-        <v>5.32</v>
+        <v>1.54</v>
       </c>
       <c r="K204" s="9" t="n">
-        <v>5.533</v>
+        <v>1.655</v>
       </c>
       <c r="L204" t="inlineStr"/>
       <c r="M204" s="14" t="inlineStr"/>
     </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>BMGREEN</t>
+        </is>
+      </c>
+      <c r="D205" s="9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E205" s="16" t="n">
+        <v>-0.0126</v>
+      </c>
+      <c r="F205" s="11" t="n">
+        <v>507800</v>
+      </c>
+      <c r="G205" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H205" t="n">
+        <v>40.66</v>
+      </c>
+      <c r="I205" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J205" s="9" t="n">
+        <v>1.634</v>
+      </c>
+      <c r="K205" s="9" t="n">
+        <v>1.706</v>
+      </c>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" s="14" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>5139</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>AEONCR</t>
+        </is>
+      </c>
+      <c r="D206" s="9" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="E206" s="16" t="n">
+        <v>-0.0159</v>
+      </c>
+      <c r="F206" s="11" t="n">
+        <v>504200</v>
+      </c>
+      <c r="G206" s="12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H206" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="I206" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J206" s="9" t="n">
+        <v>5.321</v>
+      </c>
+      <c r="K206" s="9" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M204"/>
+  <autoFilter ref="A1:M206"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>